--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -6724,7 +6724,6 @@
       <c r="D5" s="150" t="n"/>
       <c r="E5" s="150" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="222" t="inlineStr">
         <is>
@@ -6809,7 +6808,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="0" t="inlineStr">
         <is>
           <t>(handled by scripts/download_apk.py - no dedicated flow needed)</t>
         </is>
@@ -6846,7 +6845,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="0" t="inlineStr">
         <is>
           <t>(handled by hq_setup/mobile_pins/setup_02_install_application.json - no dedicated flow needed beyond common/login.yaml)</t>
         </is>
@@ -6890,7 +6889,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="0" t="inlineStr">
         <is>
           <t>flows/mobile_pins/setup_03_enable_developer_options.yaml</t>
         </is>
@@ -7214,7 +7213,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="0" t="inlineStr">
         <is>
           <t>flows/mobile_pins/setup_05_uninstall_app.yaml</t>
         </is>
@@ -7250,7 +7249,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="0" t="inlineStr">
         <is>
           <t>(handled by hq_setup/mobile_pins/setup_06_reinstall_application.json - no dedicated flow needed beyond flows/mobile_pins/setup_05_uninstall_app.yaml)</t>
         </is>
@@ -7296,7 +7295,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="0" t="inlineStr">
         <is>
           <t>flows/mobile_pins/pin_01_prompt_shown_on_first_login.yaml (same on-device assertion as the first 'Pin 1' row - see that file's header comment for why no separate file was written)</t>
         </is>
@@ -7761,7 +7760,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="0" t="inlineStr">
         <is>
           <t>(handled by hq_setup/mobile_pins/mutiple_app_pin_install_apps.json - no dedicated flow needed beyond Setup 4's manual barcode-claim, run once per app)</t>
         </is>
@@ -7802,7 +7801,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="0" t="inlineStr">
         <is>
           <t>flows/mobile_pins/multiple_app_pin_per_app_isolation.yaml</t>
         </is>
@@ -11527,10 +11526,14 @@
       </c>
       <c r="I71" s="676" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J71" s="60" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J71" s="60" t="inlineStr">
+        <is>
+          <t>flows/multimedia/capture_01_gather_signature.yaml</t>
+        </is>
+      </c>
       <c r="K71" s="60" t="n"/>
       <c r="L71" s="60" t="n"/>
       <c r="M71" s="60" t="n"/>
@@ -11580,10 +11583,14 @@
       </c>
       <c r="I72" s="676" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J72" s="60" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J72" s="60" t="inlineStr">
+        <is>
+          <t>flows/multimedia/capture_02_signature_reset.yaml</t>
+        </is>
+      </c>
       <c r="K72" s="60" t="n"/>
       <c r="L72" s="60" t="n"/>
       <c r="M72" s="60" t="n"/>
@@ -15119,7 +15126,12 @@
       </c>
       <c r="I9" s="670" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>hq_setup/prompted_updates/setup_02_mark_in_test.json</t>
         </is>
       </c>
     </row>
@@ -15150,7 +15162,12 @@
       </c>
       <c r="I10" s="670" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>hq_setup/prompted_updates/setup_03_prompts_on.json</t>
         </is>
       </c>
     </row>
@@ -15187,7 +15204,12 @@
       </c>
       <c r="I11" s="670" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>hq_setup/prompted_updates/scenario_01_mark_released.json; flows/prompted_updates/scenario_01_optional_ccz_update.yaml</t>
         </is>
       </c>
     </row>
@@ -15228,7 +15250,12 @@
       </c>
       <c r="I12" s="670" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>hq_setup/prompted_updates/scenario_02_forced.json; flows/prompted_updates/scenario_02_forced_ccz_update.yaml</t>
         </is>
       </c>
     </row>
@@ -15263,7 +15290,12 @@
       </c>
       <c r="I13" s="670" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>hq_setup/prompted_updates/scenario_03_unreleased_build.json; flows/prompted_updates/scenario_03_unstarred_build_no_prompt.yaml</t>
         </is>
       </c>
     </row>
@@ -15420,7 +15452,12 @@
       </c>
       <c r="I18" s="670" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>hq_setup/prompted_updates/varying_prompt_setup.json (covers both Setup 1 and Setup 2 in one call)</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15499,12 @@
       </c>
       <c r="I19" s="670" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>hq_setup/prompted_updates/varying_prompt_setup.json (covers both Setup 1 and Setup 2 in one call)</t>
         </is>
       </c>
     </row>
@@ -16860,7 +16902,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="0" t="inlineStr">
         <is>
           <t>(out-of-band provisioning - fetching the APK from an internal Jenkins job is not a Maestro flow; see flows/externalapp_tests/README.md for how the resulting APK is consumed via `run_suite.py --other-app`)</t>
         </is>
@@ -16893,7 +16935,12 @@
       </c>
       <c r="I8" s="670" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>(covered by run_suite.py's own APK upload/install - not a Maestro flow)</t>
         </is>
       </c>
     </row>
@@ -16933,7 +16980,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="0" t="inlineStr">
         <is>
           <t>hq_setup/externalapp_tests/setup_03_deploy_fixture_app.json; flows/externalapp_tests/setup_03_login_and_background.yaml</t>
         </is>
@@ -16973,7 +17020,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="0" t="inlineStr">
         <is>
           <t>flows/externalapp_tests/external_app_01_launch_and_verify_buttons.yaml</t>
         </is>
@@ -17011,7 +17058,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="0" t="inlineStr">
         <is>
           <t>flows/externalapp_tests/external_app_02_start_commcare_submit_form.yaml</t>
         </is>
@@ -17049,7 +17096,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t>flows/externalapp_tests/external_app_03_view_case_data.yaml</t>
         </is>
@@ -17088,7 +17135,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="0" t="inlineStr">
         <is>
           <t>flows/externalapp_tests/external_app_04_launch_update_form.yaml</t>
         </is>
@@ -17126,7 +17173,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="0" t="inlineStr">
         <is>
           <t>flows/externalapp_tests/external_app_05_view_fixture_data.yaml</t>
         </is>
@@ -20094,7 +20141,12 @@
       </c>
       <c r="J33" s="670" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>(covered by run_suite.py --release-tag/--apk - installing a specific historical CommCare binary is harness-level, not a Maestro flow)</t>
         </is>
       </c>
     </row>
@@ -20613,7 +20665,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="0" t="inlineStr">
         <is>
           <t>flows/recovery_measures/reinstall_update_app_flow.yaml</t>
         </is>
@@ -20648,7 +20700,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="0" t="inlineStr">
         <is>
           <t>hq_setup/recovery_measures/reinstall_update_2_mark_test_two.json</t>
         </is>
@@ -20684,7 +20736,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="0" t="inlineStr">
         <is>
           <t>flows/recovery_measures/reinstall_update_03_update_to_test_two.yaml</t>
         </is>
@@ -20719,7 +20771,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t>hq_setup/recovery_measures/reinstall_update_4_mark_test_three.json</t>
         </is>
@@ -20760,7 +20812,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="0" t="inlineStr">
         <is>
           <t>flows/recovery_measures/reinstall_update_app_flow.yaml</t>
         </is>
@@ -20797,7 +20849,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="0" t="inlineStr">
         <is>
           <t>flows/recovery_measures/reinstall_update_app_flow.yaml</t>
         </is>
@@ -20836,7 +20888,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="0" t="inlineStr">
         <is>
           <t>flows/recovery_measures/reinstall_update_07_10_online_install_and_negative.yaml</t>
         </is>
@@ -20874,7 +20926,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="0" t="inlineStr">
         <is>
           <t>flows/recovery_measures/reinstall_update_07_10_online_install_and_negative.yaml</t>
         </is>
@@ -20913,7 +20965,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="0" t="inlineStr">
         <is>
           <t>flows/recovery_measures/reinstall_update_07_10_online_install_and_negative.yaml</t>
         </is>
@@ -20951,7 +21003,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="0" t="inlineStr">
         <is>
           <t>flows/recovery_measures/reinstall_update_07_10_online_install_and_negative.yaml</t>
         </is>
@@ -21457,7 +21509,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="0" t="inlineStr">
         <is>
           <t>hq_setup/recovery_measures/offline_2_mark_test_two.json</t>
         </is>
@@ -21528,7 +21580,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="0" t="inlineStr">
         <is>
           <t>hq_setup/recovery_measures/offline_4_mark_test_three.json</t>
         </is>
@@ -21565,7 +21617,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="0" t="inlineStr">
         <is>
           <t>flows/recovery_measures/offline_05_place_ccz_custom_path.yaml</t>
         </is>
@@ -21606,7 +21658,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="0" t="inlineStr">
         <is>
           <t>flows/recovery_measures/offline_06_select_ccz_via_picker.yaml</t>
         </is>
@@ -21680,7 +21732,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="0" t="inlineStr">
         <is>
           <t>flows/recovery_measures/offline_08_move_ccz_to_downloads.yaml</t>
         </is>
@@ -21716,7 +21768,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="0" t="inlineStr">
         <is>
           <t>hq_setup/recovery_measures/offline_9_mark_test_three.json + flows/recovery_measures/offline_09_uninstall_reinstall_test_two.yaml</t>
         </is>
@@ -21897,7 +21949,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" s="0" t="inlineStr">
         <is>
           <t>hq_setup/recovery_measures/cc_reinstall_needed_provisioning.json</t>
         </is>
@@ -21934,7 +21986,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" s="0" t="inlineStr">
         <is>
           <t>hq_setup/recovery_measures/cc_reinstall_needed_2_mark_released.json</t>
         </is>
@@ -22137,7 +22189,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J53" s="0" t="inlineStr">
         <is>
           <t>hq_setup/recovery_measures/cc_update_needed_provisioning.json</t>
         </is>
@@ -22174,7 +22226,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J54" s="0" t="inlineStr">
         <is>
           <t>hq_setup/recovery_measures/cc_update_needed_2_mark_released.json</t>
         </is>
@@ -22322,7 +22374,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J58" s="0" t="inlineStr">
         <is>
           <t>flows/recovery_measures/retry_recovery_01_delete_install_files.yaml</t>
         </is>
@@ -22361,7 +22413,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J59" s="0" t="inlineStr">
         <is>
           <t>flows/recovery_measures/retry_recovery_02_network_toggle_retry.yaml</t>
         </is>
@@ -22465,7 +22517,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J62" s="0" t="inlineStr">
         <is>
           <t>hq_setup/recovery_measures/point_release_provisioning.json</t>
         </is>
@@ -22503,7 +22555,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J63" s="0" t="inlineStr">
         <is>
           <t>hq_setup/recovery_measures/point_release_provisioning.json</t>
         </is>
@@ -22642,7 +22694,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J67" s="0" t="inlineStr">
         <is>
           <t>hq_setup/recovery_measures/heartbeat_1_setup.json + flows/recovery_measures/heartbeat_01_setup_and_submit.yaml</t>
         </is>
@@ -26506,7 +26558,12 @@
       </c>
       <c r="I9" s="676" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>hq_setup/trigger_device_logs/device_logs_1_feature_flag.json (manual one-time flag toggle); flows/trigger_device_logs/device_logs_1_submit_form.yaml</t>
         </is>
       </c>
     </row>
@@ -26837,7 +26894,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="0" t="inlineStr">
         <is>
           <t>hq_setup/updates_2_49/rate_limit_provisioning.json</t>
         </is>
@@ -27102,7 +27159,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="0" t="inlineStr">
         <is>
           <t>hq_setup/updates_2_49/auto_cc_update_daily_preset.json</t>
         </is>
@@ -27289,7 +27346,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="0" t="inlineStr">
         <is>
           <t>hq_setup/updates_2_49/setup_02_commcare_version_plus_one.json</t>
         </is>
@@ -27372,7 +27429,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="0" t="inlineStr">
         <is>
           <t>hq_setup/updates_2_49/prompted_update_scenario_02_forced.json + flows/updates_2_49/prompted_update_scenario_02_forced_commcare_update.yaml</t>
         </is>
@@ -33626,7 +33683,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="0" t="inlineStr">
         <is>
           <t>hq_setup/update/setup_make_new_version.json</t>
         </is>
@@ -33658,7 +33715,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="0" t="inlineStr">
         <is>
           <t>hq_setup/update/install_mark_released.json</t>
         </is>
@@ -33878,7 +33935,8 @@
         <is>
           <t>These tests correspond with this ticket
 (Note for Test Setup:
-In App settings &gt; Advanced Settings, ensure Auto Update Frequency is set to 'Daily' for the previous version being downloaded and the released version to which it is being updated to.)</t>
+In App settings &gt; Advanced Settings, ensure Auto Update Frequency is set to 'Daily' for the previous version being downloaded and the released version to which it is being updated to.)
+BLOCKED: needs a real Play Store install, which this harness's sideloaded-APK BrowserStack approach cannot perform.</t>
         </is>
       </c>
       <c r="F16" s="154" t="n"/>
@@ -34061,7 +34119,11 @@
         </is>
       </c>
       <c r="D21" s="596" t="n"/>
-      <c r="E21" s="163" t="n"/>
+      <c r="E21" s="163" t="inlineStr">
+        <is>
+          <t>BLOCKED: depends on 'Recheck button 1' having manually put the device in airplane mode first; no scripted network-condition toggle exists in this harness yet.</t>
+        </is>
+      </c>
       <c r="F21" s="163" t="n"/>
       <c r="G21" s="139" t="n"/>
       <c r="H21" s="124" t="inlineStr">

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -13509,7 +13509,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="18.71" customWidth="1" style="629" min="1" max="1"/>
@@ -13645,6 +13645,21 @@
         </is>
       </c>
       <c r="G7" s="302" t="n"/>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="75" customHeight="1" s="629">
       <c r="A8" s="193" t="inlineStr">
@@ -13674,6 +13689,21 @@
       <c r="E8" s="307" t="n"/>
       <c r="F8" s="307" t="n"/>
       <c r="G8" s="295" t="n"/>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>flows/support_menus/menu_01_report_problem.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="54.75" customHeight="1" s="629">
       <c r="A9" s="193" t="inlineStr">
@@ -13698,6 +13728,21 @@
       <c r="E9" s="308" t="n"/>
       <c r="F9" s="308" t="n"/>
       <c r="G9" s="310" t="n"/>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows/support_menus/menu_02_force_log_submission.yaml</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -13736,7 +13781,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="16.71" customWidth="1" style="629" min="1" max="1"/>
@@ -13878,6 +13923,21 @@
           <t>Ticket ID</t>
         </is>
       </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="64.5" customHeight="1" s="629">
       <c r="A9" s="497" t="inlineStr">
@@ -13901,6 +13961,21 @@
       <c r="D9" s="564" t="n"/>
       <c r="E9" s="497" t="n"/>
       <c r="F9" s="497" t="n"/>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows/case_filters/fuzzy_search_01_03.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="26.25" customHeight="1" s="629">
       <c r="A10" s="497" t="inlineStr">
@@ -13922,6 +13997,21 @@
       <c r="D10" s="564" t="n"/>
       <c r="E10" s="497" t="n"/>
       <c r="F10" s="497" t="n"/>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows/case_filters/fuzzy_search_01_03.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="158.25" customHeight="1" s="629">
       <c r="A11" s="497" t="inlineStr">
@@ -13950,6 +14040,21 @@
       <c r="D11" s="564" t="n"/>
       <c r="E11" s="497" t="n"/>
       <c r="F11" s="497" t="n"/>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>flows/case_filters/fuzzy_search_01_03.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="64.5" customHeight="1" s="629">
       <c r="A12" s="497" t="inlineStr">
@@ -13973,6 +14078,21 @@
       <c r="D12" s="564" t="n"/>
       <c r="E12" s="497" t="n"/>
       <c r="F12" s="497" t="n"/>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>flows/case_filters/fuzzy_search_01_03.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="102.75" customHeight="1" s="629">
       <c r="A13" s="497" t="inlineStr">
@@ -13997,6 +14117,16 @@
       <c r="D13" s="564" t="n"/>
       <c r="E13" s="497" t="n"/>
       <c r="F13" s="497" t="n"/>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="90" customHeight="1" s="629">
       <c r="A14" s="497" t="inlineStr">
@@ -14020,6 +14150,16 @@
       <c r="D14" s="564" t="n"/>
       <c r="E14" s="331" t="n"/>
       <c r="F14" s="331" t="n"/>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="26.25" customHeight="1" s="629">
       <c r="A15" s="497" t="inlineStr">
@@ -14041,6 +14181,16 @@
       <c r="D15" s="564" t="n"/>
       <c r="E15" s="497" t="n"/>
       <c r="F15" s="497" t="n"/>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="26.25" customHeight="1" s="629">
       <c r="A16" s="497" t="inlineStr">
@@ -14061,6 +14211,16 @@
       <c r="D16" s="564" t="n"/>
       <c r="E16" s="497" t="n"/>
       <c r="F16" s="497" t="n"/>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="64.5" customHeight="1" s="629">
       <c r="A17" s="497" t="inlineStr">
@@ -14085,6 +14245,16 @@
       <c r="D17" s="564" t="n"/>
       <c r="E17" s="497" t="n"/>
       <c r="F17" s="497" t="n"/>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="115.5" customHeight="1" s="629">
       <c r="A18" s="335" t="inlineStr">
@@ -14109,6 +14279,16 @@
       <c r="D18" s="564" t="n"/>
       <c r="E18" s="497" t="n"/>
       <c r="F18" s="497" t="n"/>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="115.5" customHeight="1" s="629">
       <c r="A19" s="336" t="inlineStr">
@@ -14137,6 +14317,16 @@
         </is>
       </c>
       <c r="F19" s="497" t="n"/>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="115.5" customHeight="1" s="629">
       <c r="A20" s="336" t="inlineStr">
@@ -14163,6 +14353,16 @@
       <c r="D20" s="564" t="n"/>
       <c r="E20" s="497" t="n"/>
       <c r="F20" s="497" t="n"/>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="629">
       <c r="A21" s="340" t="inlineStr">
@@ -14205,6 +14405,16 @@
       <c r="D22" s="564" t="n"/>
       <c r="E22" s="387" t="n"/>
       <c r="F22" s="387" t="n"/>
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -14248,7 +14458,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="17.29" customWidth="1" style="629" min="1" max="1"/>
@@ -14380,6 +14590,21 @@
         </is>
       </c>
       <c r="G7" s="405" t="n"/>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="179.25" customHeight="1" s="629">
       <c r="A8" s="387" t="inlineStr">
@@ -14409,6 +14634,21 @@
       <c r="E8" s="387" t="n"/>
       <c r="F8" s="387" t="n"/>
       <c r="G8" s="216" t="n"/>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>flows/session_expiration/setup_01_install_application.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="27" customHeight="1" s="629">
       <c r="A9" s="387" t="inlineStr">
@@ -14438,6 +14678,21 @@
       </c>
       <c r="F9" s="387" t="n"/>
       <c r="G9" s="216" t="n"/>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows/session_expiration/setup_02_restore_user_session_expires.yaml</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -14477,7 +14732,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="27.14" customWidth="1" style="629" min="1" max="1"/>
@@ -14603,6 +14858,21 @@
         </is>
       </c>
       <c r="G7" s="216" t="n"/>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="42" customHeight="1" s="629">
       <c r="A8" s="155" t="inlineStr">
@@ -14626,6 +14896,16 @@
       <c r="E8" s="387" t="n"/>
       <c r="F8" s="387" t="n"/>
       <c r="G8" s="216" t="n"/>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="64.5" customHeight="1" s="629">
       <c r="A9" s="387" t="inlineStr">
@@ -14651,6 +14931,16 @@
       <c r="E9" s="387" t="n"/>
       <c r="F9" s="387" t="n"/>
       <c r="G9" s="216" t="n"/>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="39" customHeight="1" s="629">
       <c r="A10" s="387" t="inlineStr">
@@ -14675,6 +14965,21 @@
       <c r="E10" s="387" t="n"/>
       <c r="F10" s="387" t="n"/>
       <c r="G10" s="216" t="n"/>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows/conditional_enum_in_case_list/conditional_id_mapping_01_06_full_scenario.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="39" customHeight="1" s="629">
       <c r="A11" s="387" t="inlineStr">
@@ -14700,6 +15005,21 @@
       <c r="E11" s="387" t="n"/>
       <c r="F11" s="387" t="n"/>
       <c r="G11" s="216" t="n"/>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>flows/conditional_enum_in_case_list/conditional_id_mapping_01_06_full_scenario.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="55.5" customHeight="1" s="629">
       <c r="A12" s="387" t="inlineStr">
@@ -14722,6 +15042,21 @@
       <c r="E12" s="387" t="n"/>
       <c r="F12" s="387" t="n"/>
       <c r="G12" s="216" t="n"/>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>flows/conditional_enum_in_case_list/conditional_id_mapping_01_06_full_scenario.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="39" customHeight="1" s="629">
       <c r="A13" s="387" t="inlineStr">
@@ -14747,6 +15082,21 @@
       <c r="E13" s="387" t="n"/>
       <c r="F13" s="387" t="n"/>
       <c r="G13" s="216" t="n"/>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>flows/conditional_enum_in_case_list/conditional_id_mapping_01_06_full_scenario.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="26.25" customHeight="1" s="629">
       <c r="A14" s="387" t="inlineStr">
@@ -14769,6 +15119,21 @@
       <c r="E14" s="387" t="n"/>
       <c r="F14" s="387" t="n"/>
       <c r="G14" s="216" t="n"/>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>flows/conditional_enum_in_case_list/conditional_id_mapping_01_06_full_scenario.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="90" customHeight="1" s="629">
       <c r="A15" s="387" t="inlineStr">
@@ -14793,6 +15158,21 @@
       <c r="E15" s="387" t="n"/>
       <c r="F15" s="387" t="n"/>
       <c r="G15" s="216" t="n"/>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>flows/conditional_enum_in_case_list/conditional_id_mapping_01_06_full_scenario.yaml</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -15129,7 +15509,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="0" t="inlineStr">
         <is>
           <t>hq_setup/prompted_updates/setup_02_mark_in_test.json</t>
         </is>
@@ -15165,7 +15545,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="0" t="inlineStr">
         <is>
           <t>hq_setup/prompted_updates/setup_03_prompts_on.json</t>
         </is>
@@ -15207,7 +15587,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="0" t="inlineStr">
         <is>
           <t>hq_setup/prompted_updates/scenario_01_mark_released.json; flows/prompted_updates/scenario_01_optional_ccz_update.yaml</t>
         </is>
@@ -15253,7 +15633,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t>hq_setup/prompted_updates/scenario_02_forced.json; flows/prompted_updates/scenario_02_forced_ccz_update.yaml</t>
         </is>
@@ -15293,7 +15673,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="0" t="inlineStr">
         <is>
           <t>hq_setup/prompted_updates/scenario_03_unreleased_build.json; flows/prompted_updates/scenario_03_unstarred_build_no_prompt.yaml</t>
         </is>
@@ -15455,7 +15835,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="0" t="inlineStr">
         <is>
           <t>hq_setup/prompted_updates/varying_prompt_setup.json (covers both Setup 1 and Setup 2 in one call)</t>
         </is>
@@ -15502,7 +15882,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="0" t="inlineStr">
         <is>
           <t>hq_setup/prompted_updates/varying_prompt_setup.json (covers both Setup 1 and Setup 2 in one call)</t>
         </is>
@@ -15738,7 +16118,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="23.71" customWidth="1" style="629" min="1" max="1"/>
@@ -15867,6 +16247,21 @@
         </is>
       </c>
       <c r="G7" s="166" t="n"/>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="387" t="inlineStr">
@@ -15889,6 +16284,21 @@
       <c r="E8" s="387" t="n"/>
       <c r="F8" s="387" t="n"/>
       <c r="G8" s="166" t="n"/>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>(handled by ../common/install_app_as_web_user.yaml, APP_NAME: Performance Testing)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="387" t="inlineStr">
@@ -15910,6 +16320,21 @@
       <c r="E9" s="387" t="n"/>
       <c r="F9" s="387" t="n"/>
       <c r="G9" s="166" t="n"/>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows/menu_badges/menu_badges_03_04_badge_loads.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="387" t="inlineStr">
@@ -15932,6 +16357,21 @@
       <c r="E10" s="387" t="n"/>
       <c r="F10" s="387" t="n"/>
       <c r="G10" s="166" t="n"/>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows/menu_badges/menu_badges_03_04_badge_loads.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="387" t="inlineStr">
@@ -15955,6 +16395,21 @@
       <c r="E11" s="387" t="n"/>
       <c r="F11" s="387" t="n"/>
       <c r="G11" s="166" t="n"/>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>flows/menu_badges/menu_badges_03_04_badge_loads.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="387" t="inlineStr">
@@ -15979,6 +16434,16 @@
       <c r="E12" s="387" t="n"/>
       <c r="F12" s="387" t="n"/>
       <c r="G12" s="166" t="n"/>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -16017,7 +16482,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="73.14" customWidth="1" style="629" min="3" max="3"/>
@@ -16145,6 +16610,21 @@
         </is>
       </c>
       <c r="G7" s="166" t="n"/>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="521" t="inlineStr">
@@ -16170,6 +16650,21 @@
       <c r="E8" s="521" t="n"/>
       <c r="F8" s="521" t="n"/>
       <c r="G8" s="166" t="n"/>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>(handled by ../common/install_app_as_web_user.yaml, APP_NAME: Date Widgets)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="521" t="inlineStr">
@@ -16204,6 +16699,21 @@
       </c>
       <c r="F9" s="387" t="n"/>
       <c r="G9" s="166" t="n"/>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows/date_widgets/date_02_nepali.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="521" t="inlineStr">
@@ -16239,6 +16749,21 @@
       </c>
       <c r="F10" s="387" t="n"/>
       <c r="G10" s="166" t="n"/>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows/date_widgets/date_03_ethiopian.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="369" t="inlineStr">
@@ -16264,6 +16789,21 @@
       <c r="E11" s="387" t="n"/>
       <c r="F11" s="387" t="n"/>
       <c r="G11" s="166" t="n"/>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>flows/date_widgets/date_04_05_standard_widget.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="369" t="inlineStr">
@@ -16289,6 +16829,21 @@
       <c r="E12" s="387" t="n"/>
       <c r="F12" s="387" t="n"/>
       <c r="G12" s="166" t="n"/>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>flows/date_widgets/date_04_05_standard_widget.yaml</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -16329,7 +16884,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="17.29" customWidth="1" style="629" min="1" max="1"/>
@@ -16446,6 +17001,21 @@
       <c r="F7" s="200" t="inlineStr">
         <is>
           <t>Ticket ID</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
         </is>
       </c>
     </row>
@@ -16479,6 +17049,21 @@
       <c r="D8" s="137" t="n"/>
       <c r="E8" s="497" t="n"/>
       <c r="F8" s="497" t="n"/>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>(handled by ../common/install_app_as_web_user.yaml, APP_NAME: Other)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="27" customHeight="1" s="629">
       <c r="A9" s="497" t="inlineStr">
@@ -16502,6 +17087,21 @@
       <c r="D9" s="137" t="n"/>
       <c r="E9" s="497" t="n"/>
       <c r="F9" s="497" t="n"/>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows/other_error_tests/xform_error_01_04.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="27" customHeight="1" s="629">
       <c r="A10" s="497" t="inlineStr">
@@ -16525,6 +17125,21 @@
       <c r="D10" s="137" t="n"/>
       <c r="E10" s="497" t="n"/>
       <c r="F10" s="497" t="n"/>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows/other_error_tests/keyboard_navigation.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="17.25" customHeight="1" s="629">
       <c r="A11" s="497" t="inlineStr">
@@ -16547,6 +17162,21 @@
       <c r="D11" s="137" t="n"/>
       <c r="E11" s="497" t="n"/>
       <c r="F11" s="497" t="n"/>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>flows/other_error_tests/xform_error_01_04.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="27" customHeight="1" s="629">
       <c r="A12" s="497" t="inlineStr">
@@ -16569,6 +17199,21 @@
       <c r="D12" s="137" t="n"/>
       <c r="E12" s="497" t="n"/>
       <c r="F12" s="497" t="n"/>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>flows/other_error_tests/xform_error_01_04.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="27" customHeight="1" s="629">
       <c r="A13" s="497" t="inlineStr">
@@ -16591,6 +17236,21 @@
       <c r="D13" s="137" t="n"/>
       <c r="E13" s="497" t="n"/>
       <c r="F13" s="497" t="n"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>flows/other_error_tests/xform_error_01_04.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="27" customHeight="1" s="629">
       <c r="A14" s="497" t="inlineStr">
@@ -16613,6 +17273,21 @@
       <c r="D14" s="137" t="n"/>
       <c r="E14" s="497" t="n"/>
       <c r="F14" s="497" t="n"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>flows/other_error_tests/xform_error_01_04.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="27" customHeight="1" s="629">
       <c r="A15" s="497" t="inlineStr">
@@ -16635,6 +17310,16 @@
       <c r="D15" s="137" t="n"/>
       <c r="E15" s="497" t="n"/>
       <c r="F15" s="497" t="n"/>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="27" customHeight="1" s="629">
       <c r="A16" s="497" t="inlineStr">
@@ -16656,6 +17341,16 @@
       <c r="D16" s="137" t="n"/>
       <c r="E16" s="497" t="n"/>
       <c r="F16" s="497" t="n"/>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="26.25" customHeight="1" s="629">
       <c r="A17" s="497" t="inlineStr">
@@ -16680,6 +17375,16 @@
       <c r="D17" s="137" t="n"/>
       <c r="E17" s="497" t="n"/>
       <c r="F17" s="497" t="n"/>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="90" customHeight="1" s="629">
       <c r="A18" s="497" t="inlineStr">
@@ -16701,6 +17406,16 @@
       <c r="D18" s="137" t="n"/>
       <c r="E18" s="497" t="n"/>
       <c r="F18" s="497" t="n"/>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -16938,7 +17653,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="0" t="inlineStr">
         <is>
           <t>(covered by run_suite.py's own APK upload/install - not a Maestro flow)</t>
         </is>
@@ -20144,7 +20859,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="0" t="inlineStr">
         <is>
           <t>(covered by run_suite.py --release-tag/--apk - installing a specific historical CommCare binary is harness-level, not a Maestro flow)</t>
         </is>
@@ -26561,7 +27276,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="0" t="inlineStr">
         <is>
           <t>hq_setup/trigger_device_logs/device_logs_1_feature_flag.json (manual one-time flag toggle); flows/trigger_device_logs/device_logs_1_submit_form.yaml</t>
         </is>
@@ -33223,7 +33938,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="16.29" customWidth="1" style="629" min="1" max="1"/>
@@ -33374,7 +34089,21 @@
       </c>
       <c r="G7" s="143" t="n"/>
       <c r="H7" s="140" t="n"/>
-      <c r="I7" s="140" t="n"/>
+      <c r="I7" s="140" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="48" customHeight="1" s="629">
       <c r="A8" s="193" t="inlineStr">
@@ -33398,7 +34127,21 @@
       <c r="D8" s="137" t="n"/>
       <c r="E8" s="193" t="n"/>
       <c r="F8" s="193" t="n"/>
-      <c r="I8" s="140" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>flows/login/commcare_odk_01_login.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="48" customHeight="1" s="629">
       <c r="A9" s="193" t="inlineStr">
@@ -33423,7 +34166,21 @@
       <c r="E9" s="193" t="n"/>
       <c r="F9" s="193" t="n"/>
       <c r="G9" s="145" t="n"/>
-      <c r="I9" s="140" t="n"/>
+      <c r="I9" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>flows/login/commcare_odk_02_check_session.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="38.25" customHeight="1" s="629">
       <c r="A10" s="193" t="inlineStr">
@@ -33447,7 +34204,21 @@
       <c r="F10" s="149" t="n"/>
       <c r="G10" s="151" t="n"/>
       <c r="H10" s="152" t="n"/>
-      <c r="I10" s="140" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>flows/login/commcare_odk_03_logout.yaml</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -17236,17 +17236,17 @@
       <c r="D13" s="137" t="n"/>
       <c r="E13" s="497" t="n"/>
       <c r="F13" s="497" t="n"/>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="0" t="inlineStr">
         <is>
           <t>flows/other_error_tests/xform_error_01_04.yaml</t>
         </is>
@@ -17273,17 +17273,17 @@
       <c r="D14" s="137" t="n"/>
       <c r="E14" s="497" t="n"/>
       <c r="F14" s="497" t="n"/>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="0" t="inlineStr">
         <is>
           <t>flows/other_error_tests/xform_error_01_04.yaml</t>
         </is>
@@ -23502,7 +23502,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.29" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="28.57" customWidth="1" style="629" min="1" max="1"/>
@@ -23636,6 +23636,21 @@
           <t>Ticket ID</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Maestro Automatability</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Automated?</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Flow File</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="700" t="inlineStr">
@@ -23677,6 +23692,21 @@
       <c r="D9" s="564" t="n"/>
       <c r="E9" s="387" t="n"/>
       <c r="F9" s="204" t="n"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/question_types_01_03_answer_and_submit.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="521" t="inlineStr">
@@ -23700,6 +23730,21 @@
       <c r="D10" s="564" t="n"/>
       <c r="E10" s="387" t="n"/>
       <c r="F10" s="204" t="n"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/question_types_01_03_answer_and_submit.yaml (same on-device path as Question Types 1 - see that file's header)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="521" t="inlineStr">
@@ -23724,6 +23769,21 @@
       <c r="D11" s="564" t="n"/>
       <c r="E11" s="387" t="n"/>
       <c r="F11" s="204" t="n"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/question_types_01_03_answer_and_submit.yaml (same on-device path as Question Types 1 - see that file's header)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="521" t="inlineStr">
@@ -23748,6 +23808,16 @@
       <c r="D12" s="387" t="n"/>
       <c r="E12" s="387" t="n"/>
       <c r="F12" s="204" t="n"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="521" t="inlineStr">
@@ -23769,6 +23839,16 @@
       <c r="D13" s="387" t="n"/>
       <c r="E13" s="387" t="n"/>
       <c r="F13" s="204" t="n"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="521" t="inlineStr">
@@ -23796,6 +23876,21 @@
       <c r="D14" s="564" t="n"/>
       <c r="E14" s="387" t="n"/>
       <c r="F14" s="204" t="n"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/appearance_attributes_page_through_and_submit.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="521" t="inlineStr">
@@ -23822,6 +23917,21 @@
       <c r="D15" s="564" t="n"/>
       <c r="E15" s="521" t="n"/>
       <c r="F15" s="204" t="n"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/groups_submit_twice_different_answers.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="521" t="inlineStr">
@@ -23844,6 +23954,21 @@
       <c r="D16" s="564" t="n"/>
       <c r="E16" s="521" t="n"/>
       <c r="F16" s="204" t="n"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/repeat_groups_01_05_add_and_submit.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="521" t="inlineStr">
@@ -23866,6 +23991,21 @@
       <c r="D17" s="564" t="n"/>
       <c r="E17" s="521" t="n"/>
       <c r="F17" s="204" t="n"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/repeat_groups_01_05_add_and_submit.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="521" t="inlineStr">
@@ -23890,6 +24030,21 @@
       <c r="D18" s="564" t="n"/>
       <c r="E18" s="521" t="n"/>
       <c r="F18" s="204" t="n"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/repeat_groups_01_05_add_and_submit.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="521" t="inlineStr">
@@ -23913,6 +24068,21 @@
       <c r="D19" s="564" t="n"/>
       <c r="E19" s="521" t="n"/>
       <c r="F19" s="204" t="n"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/repeat_groups_01_05_add_and_submit.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="521" t="inlineStr">
@@ -23936,6 +24106,21 @@
       <c r="D20" s="564" t="n"/>
       <c r="E20" s="521" t="n"/>
       <c r="F20" s="204" t="n"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/repeat_groups_01_05_add_and_submit.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="521" t="inlineStr">
@@ -23962,6 +24147,21 @@
       <c r="D21" s="564" t="n"/>
       <c r="E21" s="521" t="n"/>
       <c r="F21" s="204" t="n"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/markdown_page_through_and_submit.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="521" t="inlineStr">
@@ -23987,6 +24187,16 @@
       <c r="D22" s="564" t="n"/>
       <c r="E22" s="452" t="n"/>
       <c r="F22" s="204" t="n"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="521" t="inlineStr">
@@ -24011,6 +24221,16 @@
       <c r="D23" s="564" t="n"/>
       <c r="E23" s="452" t="n"/>
       <c r="F23" s="204" t="n"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="521" t="inlineStr">
@@ -24036,6 +24256,16 @@
       <c r="F24" s="454" t="inlineStr">
         <is>
           <t>This support FF will enable user to see the last sync token.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -24062,6 +24292,21 @@
       <c r="D25" s="564" t="n"/>
       <c r="E25" s="204" t="n"/>
       <c r="F25" s="204" t="n"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/locations_default_values_via_question_types.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="455" t="inlineStr">
@@ -24089,6 +24334,21 @@
       <c r="D26" s="564" t="n"/>
       <c r="E26" s="456" t="n"/>
       <c r="F26" s="204" t="n"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/minimize_duplicate_create_subcase_update_case.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="521" t="inlineStr">
@@ -24112,6 +24372,21 @@
       <c r="D27" s="564" t="n"/>
       <c r="E27" s="452" t="n"/>
       <c r="F27" s="204" t="n"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/incomplete_forms_01_03_save_resume_submit.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="521" t="inlineStr">
@@ -24138,6 +24413,21 @@
       <c r="D28" s="564" t="n"/>
       <c r="E28" s="457" t="n"/>
       <c r="F28" s="204" t="n"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/incomplete_forms_01_03_save_resume_submit.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="521" t="inlineStr">
@@ -24162,6 +24452,21 @@
       <c r="D29" s="564" t="n"/>
       <c r="E29" s="457" t="n"/>
       <c r="F29" s="204" t="n"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/incomplete_forms_01_03_save_resume_submit.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="521" t="inlineStr">
@@ -24184,6 +24489,21 @@
       <c r="D30" s="564" t="n"/>
       <c r="E30" s="457" t="n"/>
       <c r="F30" s="204" t="n"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/incomplete_forms_01_03_save_resume_submit.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="521" t="inlineStr">
@@ -24210,6 +24530,21 @@
       <c r="D31" s="459" t="n"/>
       <c r="E31" s="457" t="n"/>
       <c r="F31" s="204" t="n"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/incomplete_forms_05_06_list_summary_and_timestamp.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="521" t="inlineStr">
@@ -24236,6 +24571,21 @@
       <c r="D32" s="459" t="n"/>
       <c r="E32" s="457" t="n"/>
       <c r="F32" s="204" t="n"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/incomplete_forms_05_06_list_summary_and_timestamp.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="455" t="inlineStr">
@@ -24260,6 +24610,21 @@
       <c r="D33" s="459" t="n"/>
       <c r="E33" s="457" t="n"/>
       <c r="F33" s="204" t="n"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/case_name_size_01_02_length_warning_and_not_saved.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="455" t="inlineStr">
@@ -24281,6 +24646,21 @@
       <c r="D34" s="459" t="n"/>
       <c r="E34" s="457" t="n"/>
       <c r="F34" s="204" t="n"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/case_name_size_01_02_length_warning_and_not_saved.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="455" t="inlineStr">
@@ -24310,6 +24690,16 @@
       <c r="D35" s="459" t="n"/>
       <c r="E35" s="457" t="n"/>
       <c r="F35" s="462" t="n"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="455" t="inlineStr">
@@ -24338,6 +24728,16 @@
       <c r="D36" s="459" t="n"/>
       <c r="E36" s="457" t="n"/>
       <c r="F36" s="462" t="n"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="455" t="inlineStr">
@@ -24367,6 +24767,21 @@
         </is>
       </c>
       <c r="F37" s="462" t="n"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/multiple_submissions_10x_background_sync.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="700" t="inlineStr">
@@ -24401,6 +24816,21 @@
       <c r="D39" s="564" t="n"/>
       <c r="E39" s="457" t="n"/>
       <c r="F39" s="204" t="n"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/save_to_case_01_03_register_update_case_list.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="455" t="inlineStr">
@@ -24423,6 +24853,21 @@
       <c r="D40" s="564" t="n"/>
       <c r="E40" s="457" t="n"/>
       <c r="F40" s="204" t="n"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/save_to_case_01_03_register_update_case_list.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="455" t="inlineStr">
@@ -24444,6 +24889,21 @@
       <c r="D41" s="564" t="n"/>
       <c r="E41" s="457" t="n"/>
       <c r="F41" s="204" t="n"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/save_to_case_01_03_register_update_case_list.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="701" t="inlineStr">
@@ -24485,6 +24945,21 @@
 Feel free to skip these (or try and find at your level)</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/upload_test_01_specific_file_extensions.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="521" t="inlineStr">
@@ -24509,6 +24984,16 @@
       <c r="D44" s="564" t="n"/>
       <c r="E44" s="94" t="n"/>
       <c r="F44" s="204" t="n"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="469" t="inlineStr">
@@ -24557,6 +25042,16 @@
         </is>
       </c>
       <c r="F46" s="204" t="n"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="521" t="inlineStr">
@@ -24583,6 +25078,21 @@
       <c r="D47" s="564" t="n"/>
       <c r="E47" s="94" t="n"/>
       <c r="F47" s="204" t="n"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/geoservice_02_auto_capture_location_submit.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="479" t="inlineStr">
@@ -24610,6 +25120,16 @@
       <c r="D48" s="564" t="n"/>
       <c r="E48" s="94" t="n"/>
       <c r="F48" s="204" t="n"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="202.5" customHeight="1" s="629">
       <c r="A49" s="484" t="inlineStr">
@@ -24641,6 +25161,16 @@
       <c r="D49" s="485" t="n"/>
       <c r="E49" s="486" t="n"/>
       <c r="F49" s="484" t="n"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="87.75" customHeight="1" s="629">
       <c r="A50" s="484" t="inlineStr">
@@ -24666,6 +25196,16 @@
       <c r="D50" s="485" t="n"/>
       <c r="E50" s="486" t="n"/>
       <c r="F50" s="484" t="n"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="156.75" customHeight="1" s="629">
       <c r="A51" s="484" t="inlineStr">
@@ -24697,6 +25237,16 @@
       <c r="D51" s="485" t="n"/>
       <c r="E51" s="486" t="n"/>
       <c r="F51" s="484" t="n"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="185.25" customHeight="1" s="629">
       <c r="A52" s="484" t="inlineStr">
@@ -24732,6 +25282,16 @@
       <c r="D52" s="485" t="n"/>
       <c r="E52" s="486" t="n"/>
       <c r="F52" s="484" t="n"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="189" customHeight="1" s="629">
       <c r="A53" s="484" t="inlineStr">
@@ -24765,6 +25325,16 @@
       <c r="D53" s="485" t="n"/>
       <c r="E53" s="486" t="n"/>
       <c r="F53" s="484" t="n"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="228.75" customHeight="1" s="629">
       <c r="A54" s="484" t="inlineStr">
@@ -24799,6 +25369,16 @@
       <c r="D54" s="485" t="n"/>
       <c r="E54" s="486" t="n"/>
       <c r="F54" s="484" t="n"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="484" t="inlineStr">
@@ -24826,6 +25406,16 @@
       <c r="D55" s="485" t="n"/>
       <c r="E55" s="486" t="n"/>
       <c r="F55" s="484" t="n"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="484" t="inlineStr">
@@ -24851,6 +25441,16 @@
       <c r="D56" s="485" t="n"/>
       <c r="E56" s="486" t="n"/>
       <c r="F56" s="484" t="n"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="484" t="inlineStr">
@@ -24876,6 +25476,16 @@
       <c r="D57" s="485" t="n"/>
       <c r="E57" s="493" t="n"/>
       <c r="F57" s="494" t="n"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="495" t="inlineStr">
@@ -24900,6 +25510,21 @@
       <c r="D58" s="500" t="n"/>
       <c r="E58" s="493" t="n"/>
       <c r="F58" s="494" t="n"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/clear_user_data_before_after_login.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="495" t="inlineStr">
@@ -24926,6 +25551,21 @@
       <c r="D59" s="500" t="n"/>
       <c r="E59" s="493" t="n"/>
       <c r="F59" s="494" t="n"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>flows/form_submissions/clear_user_data_before_after_login.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="484" t="inlineStr">
@@ -24949,6 +25589,16 @@
       <c r="D60" s="485" t="n"/>
       <c r="E60" s="493" t="n"/>
       <c r="F60" s="494" t="n"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="484" t="inlineStr">
@@ -24972,6 +25622,16 @@
       <c r="D61" s="485" t="n"/>
       <c r="E61" s="493" t="n"/>
       <c r="F61" s="494" t="n"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="484" t="inlineStr">
@@ -24996,6 +25656,16 @@
       <c r="D62" s="500" t="n"/>
       <c r="E62" s="493" t="n"/>
       <c r="F62" s="494" t="n"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Not automatable</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -7019,19 +7019,15 @@
       <c r="G13" s="229" t="n"/>
       <c r="I13" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="J13" s="672" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K13" s="0" t="inlineStr">
-        <is>
-          <t>flows/mobile_pins/pin_01_prompt_shown_on_first_login.yaml</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="485" t="inlineStr">
@@ -7064,19 +7060,15 @@
       <c r="G14" s="229" t="n"/>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="J14" s="672" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K14" s="0" t="inlineStr">
-        <is>
-          <t>flows/mobile_pins/pin_02_information_tooltip.yaml</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="485" t="inlineStr">
@@ -7113,19 +7105,15 @@
       <c r="G15" s="229" t="n"/>
       <c r="I15" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="J15" s="672" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K15" s="0" t="inlineStr">
-        <is>
-          <t>flows/mobile_pins/pin_03_no_dont_ask_again.yaml</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="485" t="inlineStr">
@@ -7162,19 +7150,15 @@
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="J16" s="672" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K16" s="0" t="inlineStr">
-        <is>
-          <t>flows/mobile_pins/pin_04_set_my_pin.yaml</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="485" t="inlineStr">
@@ -7287,19 +7271,15 @@
       <c r="G19" s="229" t="n"/>
       <c r="I19" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="J19" s="672" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K19" s="0" t="inlineStr">
-        <is>
-          <t>flows/mobile_pins/pin_01_prompt_shown_on_first_login.yaml (same on-device assertion as the first 'Pin 1' row - see that file's header comment for why no separate file was written)</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="485" t="inlineStr">
@@ -7332,19 +7312,15 @@
       <c r="G20" s="229" t="n"/>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="J20" s="672" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K20" s="0" t="inlineStr">
-        <is>
-          <t>flows/mobile_pins/pin_06_no_but_ask_again_later.yaml</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="485" t="inlineStr">
@@ -7380,19 +7356,15 @@
       <c r="G21" s="229" t="n"/>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="J21" s="672" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K21" s="0" t="inlineStr">
-        <is>
-          <t>flows/mobile_pins/pin_07_setup_pin.yaml</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="485" t="inlineStr">
@@ -7423,19 +7395,15 @@
       <c r="G22" s="229" t="n"/>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="J22" s="672" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K22" s="0" t="inlineStr">
-        <is>
-          <t>flows/mobile_pins/pin_08_login_using_pin.yaml</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="485" t="inlineStr">
@@ -7474,19 +7442,15 @@
       <c r="G23" s="229" t="n"/>
       <c r="I23" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="J23" s="672" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K23" s="0" t="inlineStr">
-        <is>
-          <t>flows/mobile_pins/pin_09_change_pin_menu.yaml</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="485" t="inlineStr">
@@ -7515,19 +7479,15 @@
       <c r="G24" s="229" t="n"/>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="J24" s="672" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K24" s="0" t="inlineStr">
-        <is>
-          <t>flows/mobile_pins/pin_10_login_using_changed_pin.yaml</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="485" t="inlineStr">
@@ -7560,19 +7520,15 @@
       <c r="G25" s="229" t="n"/>
       <c r="I25" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="J25" s="672" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K25" s="0" t="inlineStr">
-        <is>
-          <t>flows/mobile_pins/pin_11_forgot_pin.yaml</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" s="0" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="485" t="inlineStr">
@@ -7606,19 +7562,15 @@
       <c r="G26" s="229" t="n"/>
       <c r="I26" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="J26" s="672" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K26" s="0" t="inlineStr">
-        <is>
-          <t>flows/mobile_pins/pin_12_reset_pin.yaml</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="0" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="485" t="inlineStr">
@@ -7648,19 +7600,15 @@
       <c r="G27" s="229" t="n"/>
       <c r="I27" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="J27" s="672" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K27" s="0" t="inlineStr">
-        <is>
-          <t>flows/mobile_pins/pin_13_login_using_reset_pin.yaml</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="0" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="485" t="inlineStr">
@@ -7701,19 +7649,15 @@
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="J28" s="672" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K28" s="0" t="inlineStr">
-        <is>
-          <t>flows/mobile_pins/pin_14_reset_pin_persists_after_decline.yaml</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="256" t="inlineStr">
@@ -7793,19 +7737,15 @@
       <c r="G31" s="484" t="n"/>
       <c r="I31" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="J31" s="672" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K31" s="0" t="inlineStr">
-        <is>
-          <t>flows/mobile_pins/multiple_app_pin_per_app_isolation.yaml</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="0" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -23636,17 +23576,17 @@
           <t>Ticket ID</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="0" t="inlineStr">
         <is>
           <t>Maestro Automatability</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="0" t="inlineStr">
         <is>
           <t>Automated?</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="0" t="inlineStr">
         <is>
           <t>Flow File</t>
         </is>
@@ -23692,17 +23632,17 @@
       <c r="D9" s="564" t="n"/>
       <c r="E9" s="387" t="n"/>
       <c r="F9" s="204" t="n"/>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/question_types_01_03_answer_and_submit.yaml</t>
         </is>
@@ -23730,17 +23670,17 @@
       <c r="D10" s="564" t="n"/>
       <c r="E10" s="387" t="n"/>
       <c r="F10" s="204" t="n"/>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/question_types_01_03_answer_and_submit.yaml (same on-device path as Question Types 1 - see that file's header)</t>
         </is>
@@ -23769,17 +23709,17 @@
       <c r="D11" s="564" t="n"/>
       <c r="E11" s="387" t="n"/>
       <c r="F11" s="204" t="n"/>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/question_types_01_03_answer_and_submit.yaml (same on-device path as Question Types 1 - see that file's header)</t>
         </is>
@@ -23808,12 +23748,12 @@
       <c r="D12" s="387" t="n"/>
       <c r="E12" s="387" t="n"/>
       <c r="F12" s="204" t="n"/>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -23839,12 +23779,12 @@
       <c r="D13" s="387" t="n"/>
       <c r="E13" s="387" t="n"/>
       <c r="F13" s="204" t="n"/>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -23876,17 +23816,17 @@
       <c r="D14" s="564" t="n"/>
       <c r="E14" s="387" t="n"/>
       <c r="F14" s="204" t="n"/>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/appearance_attributes_page_through_and_submit.yaml</t>
         </is>
@@ -23917,17 +23857,17 @@
       <c r="D15" s="564" t="n"/>
       <c r="E15" s="521" t="n"/>
       <c r="F15" s="204" t="n"/>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/groups_submit_twice_different_answers.yaml</t>
         </is>
@@ -23954,17 +23894,17 @@
       <c r="D16" s="564" t="n"/>
       <c r="E16" s="521" t="n"/>
       <c r="F16" s="204" t="n"/>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/repeat_groups_01_05_add_and_submit.yaml</t>
         </is>
@@ -23991,17 +23931,17 @@
       <c r="D17" s="564" t="n"/>
       <c r="E17" s="521" t="n"/>
       <c r="F17" s="204" t="n"/>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/repeat_groups_01_05_add_and_submit.yaml</t>
         </is>
@@ -24030,17 +23970,17 @@
       <c r="D18" s="564" t="n"/>
       <c r="E18" s="521" t="n"/>
       <c r="F18" s="204" t="n"/>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/repeat_groups_01_05_add_and_submit.yaml</t>
         </is>
@@ -24068,17 +24008,17 @@
       <c r="D19" s="564" t="n"/>
       <c r="E19" s="521" t="n"/>
       <c r="F19" s="204" t="n"/>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/repeat_groups_01_05_add_and_submit.yaml</t>
         </is>
@@ -24106,17 +24046,17 @@
       <c r="D20" s="564" t="n"/>
       <c r="E20" s="521" t="n"/>
       <c r="F20" s="204" t="n"/>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/repeat_groups_01_05_add_and_submit.yaml</t>
         </is>
@@ -24147,17 +24087,17 @@
       <c r="D21" s="564" t="n"/>
       <c r="E21" s="521" t="n"/>
       <c r="F21" s="204" t="n"/>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/markdown_page_through_and_submit.yaml</t>
         </is>
@@ -24187,12 +24127,12 @@
       <c r="D22" s="564" t="n"/>
       <c r="E22" s="452" t="n"/>
       <c r="F22" s="204" t="n"/>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -24221,12 +24161,12 @@
       <c r="D23" s="564" t="n"/>
       <c r="E23" s="452" t="n"/>
       <c r="F23" s="204" t="n"/>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -24258,12 +24198,12 @@
           <t>This support FF will enable user to see the last sync token.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -24292,17 +24232,17 @@
       <c r="D25" s="564" t="n"/>
       <c r="E25" s="204" t="n"/>
       <c r="F25" s="204" t="n"/>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/locations_default_values_via_question_types.yaml</t>
         </is>
@@ -24334,17 +24274,17 @@
       <c r="D26" s="564" t="n"/>
       <c r="E26" s="456" t="n"/>
       <c r="F26" s="204" t="n"/>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/minimize_duplicate_create_subcase_update_case.yaml</t>
         </is>
@@ -24372,17 +24312,17 @@
       <c r="D27" s="564" t="n"/>
       <c r="E27" s="452" t="n"/>
       <c r="F27" s="204" t="n"/>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/incomplete_forms_01_03_save_resume_submit.yaml</t>
         </is>
@@ -24413,17 +24353,17 @@
       <c r="D28" s="564" t="n"/>
       <c r="E28" s="457" t="n"/>
       <c r="F28" s="204" t="n"/>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/incomplete_forms_01_03_save_resume_submit.yaml</t>
         </is>
@@ -24452,17 +24392,17 @@
       <c r="D29" s="564" t="n"/>
       <c r="E29" s="457" t="n"/>
       <c r="F29" s="204" t="n"/>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/incomplete_forms_01_03_save_resume_submit.yaml</t>
         </is>
@@ -24489,17 +24429,17 @@
       <c r="D30" s="564" t="n"/>
       <c r="E30" s="457" t="n"/>
       <c r="F30" s="204" t="n"/>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/incomplete_forms_01_03_save_resume_submit.yaml</t>
         </is>
@@ -24530,17 +24470,17 @@
       <c r="D31" s="459" t="n"/>
       <c r="E31" s="457" t="n"/>
       <c r="F31" s="204" t="n"/>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/incomplete_forms_05_06_list_summary_and_timestamp.yaml</t>
         </is>
@@ -24571,17 +24511,17 @@
       <c r="D32" s="459" t="n"/>
       <c r="E32" s="457" t="n"/>
       <c r="F32" s="204" t="n"/>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/incomplete_forms_05_06_list_summary_and_timestamp.yaml</t>
         </is>
@@ -24610,17 +24550,17 @@
       <c r="D33" s="459" t="n"/>
       <c r="E33" s="457" t="n"/>
       <c r="F33" s="204" t="n"/>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/case_name_size_01_02_length_warning_and_not_saved.yaml</t>
         </is>
@@ -24646,17 +24586,17 @@
       <c r="D34" s="459" t="n"/>
       <c r="E34" s="457" t="n"/>
       <c r="F34" s="204" t="n"/>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/case_name_size_01_02_length_warning_and_not_saved.yaml</t>
         </is>
@@ -24690,12 +24630,12 @@
       <c r="D35" s="459" t="n"/>
       <c r="E35" s="457" t="n"/>
       <c r="F35" s="462" t="n"/>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -24728,12 +24668,12 @@
       <c r="D36" s="459" t="n"/>
       <c r="E36" s="457" t="n"/>
       <c r="F36" s="462" t="n"/>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -24767,17 +24707,17 @@
         </is>
       </c>
       <c r="F37" s="462" t="n"/>
-      <c r="I37" t="inlineStr">
+      <c r="I37" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/multiple_submissions_10x_background_sync.yaml</t>
         </is>
@@ -24816,17 +24756,17 @@
       <c r="D39" s="564" t="n"/>
       <c r="E39" s="457" t="n"/>
       <c r="F39" s="204" t="n"/>
-      <c r="I39" t="inlineStr">
+      <c r="I39" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K39" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/save_to_case_01_03_register_update_case_list.yaml</t>
         </is>
@@ -24853,17 +24793,17 @@
       <c r="D40" s="564" t="n"/>
       <c r="E40" s="457" t="n"/>
       <c r="F40" s="204" t="n"/>
-      <c r="I40" t="inlineStr">
+      <c r="I40" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K40" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/save_to_case_01_03_register_update_case_list.yaml</t>
         </is>
@@ -24889,17 +24829,17 @@
       <c r="D41" s="564" t="n"/>
       <c r="E41" s="457" t="n"/>
       <c r="F41" s="204" t="n"/>
-      <c r="I41" t="inlineStr">
+      <c r="I41" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K41" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/save_to_case_01_03_register_update_case_list.yaml</t>
         </is>
@@ -24945,17 +24885,17 @@
 Feel free to skip these (or try and find at your level)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/upload_test_01_specific_file_extensions.yaml</t>
         </is>
@@ -24984,12 +24924,12 @@
       <c r="D44" s="564" t="n"/>
       <c r="E44" s="94" t="n"/>
       <c r="F44" s="204" t="n"/>
-      <c r="I44" t="inlineStr">
+      <c r="I44" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -25042,12 +24982,12 @@
         </is>
       </c>
       <c r="F46" s="204" t="n"/>
-      <c r="I46" t="inlineStr">
+      <c r="I46" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -25078,17 +25018,17 @@
       <c r="D47" s="564" t="n"/>
       <c r="E47" s="94" t="n"/>
       <c r="F47" s="204" t="n"/>
-      <c r="I47" t="inlineStr">
+      <c r="I47" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K47" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/geoservice_02_auto_capture_location_submit.yaml</t>
         </is>
@@ -25120,12 +25060,12 @@
       <c r="D48" s="564" t="n"/>
       <c r="E48" s="94" t="n"/>
       <c r="F48" s="204" t="n"/>
-      <c r="I48" t="inlineStr">
+      <c r="I48" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -25161,12 +25101,12 @@
       <c r="D49" s="485" t="n"/>
       <c r="E49" s="486" t="n"/>
       <c r="F49" s="484" t="n"/>
-      <c r="I49" t="inlineStr">
+      <c r="I49" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -25196,12 +25136,12 @@
       <c r="D50" s="485" t="n"/>
       <c r="E50" s="486" t="n"/>
       <c r="F50" s="484" t="n"/>
-      <c r="I50" t="inlineStr">
+      <c r="I50" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J50" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -25237,12 +25177,12 @@
       <c r="D51" s="485" t="n"/>
       <c r="E51" s="486" t="n"/>
       <c r="F51" s="484" t="n"/>
-      <c r="I51" t="inlineStr">
+      <c r="I51" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J51" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -25282,12 +25222,12 @@
       <c r="D52" s="485" t="n"/>
       <c r="E52" s="486" t="n"/>
       <c r="F52" s="484" t="n"/>
-      <c r="I52" t="inlineStr">
+      <c r="I52" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J52" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -25325,12 +25265,12 @@
       <c r="D53" s="485" t="n"/>
       <c r="E53" s="486" t="n"/>
       <c r="F53" s="484" t="n"/>
-      <c r="I53" t="inlineStr">
+      <c r="I53" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J53" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -25369,12 +25309,12 @@
       <c r="D54" s="485" t="n"/>
       <c r="E54" s="486" t="n"/>
       <c r="F54" s="484" t="n"/>
-      <c r="I54" t="inlineStr">
+      <c r="I54" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J54" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -25406,12 +25346,12 @@
       <c r="D55" s="485" t="n"/>
       <c r="E55" s="486" t="n"/>
       <c r="F55" s="484" t="n"/>
-      <c r="I55" t="inlineStr">
+      <c r="I55" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J55" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -25441,12 +25381,12 @@
       <c r="D56" s="485" t="n"/>
       <c r="E56" s="486" t="n"/>
       <c r="F56" s="484" t="n"/>
-      <c r="I56" t="inlineStr">
+      <c r="I56" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J56" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -25476,12 +25416,12 @@
       <c r="D57" s="485" t="n"/>
       <c r="E57" s="493" t="n"/>
       <c r="F57" s="494" t="n"/>
-      <c r="I57" t="inlineStr">
+      <c r="I57" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J57" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -25510,17 +25450,17 @@
       <c r="D58" s="500" t="n"/>
       <c r="E58" s="493" t="n"/>
       <c r="F58" s="494" t="n"/>
-      <c r="I58" t="inlineStr">
+      <c r="I58" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J58" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K58" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/clear_user_data_before_after_login.yaml</t>
         </is>
@@ -25551,17 +25491,17 @@
       <c r="D59" s="500" t="n"/>
       <c r="E59" s="493" t="n"/>
       <c r="F59" s="494" t="n"/>
-      <c r="I59" t="inlineStr">
+      <c r="I59" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J59" s="0" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K59" s="0" t="inlineStr">
         <is>
           <t>flows/form_submissions/clear_user_data_before_after_login.yaml</t>
         </is>
@@ -25589,12 +25529,12 @@
       <c r="D60" s="485" t="n"/>
       <c r="E60" s="493" t="n"/>
       <c r="F60" s="494" t="n"/>
-      <c r="I60" t="inlineStr">
+      <c r="I60" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J60" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -25622,12 +25562,12 @@
       <c r="D61" s="485" t="n"/>
       <c r="E61" s="493" t="n"/>
       <c r="F61" s="494" t="n"/>
-      <c r="I61" t="inlineStr">
+      <c r="I61" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J61" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -25656,12 +25596,12 @@
       <c r="D62" s="500" t="n"/>
       <c r="E62" s="493" t="n"/>
       <c r="F62" s="494" t="n"/>
-      <c r="I62" t="inlineStr">
+      <c r="I62" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J62" s="0" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -7016,7 +7016,11 @@
       </c>
       <c r="E13" s="564" t="n"/>
       <c r="F13" s="229" t="n"/>
-      <c r="G13" s="229" t="n"/>
+      <c r="G13" s="229" t="inlineStr">
+        <is>
+          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+        </is>
+      </c>
       <c r="I13" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
@@ -7057,7 +7061,11 @@
       </c>
       <c r="E14" s="564" t="n"/>
       <c r="F14" s="229" t="n"/>
-      <c r="G14" s="229" t="n"/>
+      <c r="G14" s="229" t="inlineStr">
+        <is>
+          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+        </is>
+      </c>
       <c r="I14" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
@@ -7102,7 +7110,11 @@
       </c>
       <c r="E15" s="564" t="n"/>
       <c r="F15" s="229" t="n"/>
-      <c r="G15" s="229" t="n"/>
+      <c r="G15" s="229" t="inlineStr">
+        <is>
+          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+        </is>
+      </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
@@ -7145,8 +7157,10 @@
       </c>
       <c r="E16" s="564" t="n"/>
       <c r="F16" s="246" t="n"/>
-      <c r="G16" s="246" t="n">
-        <v>1234</v>
+      <c r="G16" s="246" t="inlineStr">
+        <is>
+          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+        </is>
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
@@ -7268,7 +7282,11 @@
       </c>
       <c r="E19" s="564" t="n"/>
       <c r="F19" s="229" t="n"/>
-      <c r="G19" s="229" t="n"/>
+      <c r="G19" s="229" t="inlineStr">
+        <is>
+          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+        </is>
+      </c>
       <c r="I19" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
@@ -7309,7 +7327,11 @@
       </c>
       <c r="E20" s="564" t="n"/>
       <c r="F20" s="229" t="n"/>
-      <c r="G20" s="229" t="n"/>
+      <c r="G20" s="229" t="inlineStr">
+        <is>
+          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+        </is>
+      </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
@@ -7353,7 +7375,11 @@
       </c>
       <c r="E21" s="564" t="n"/>
       <c r="F21" s="229" t="n"/>
-      <c r="G21" s="229" t="n"/>
+      <c r="G21" s="229" t="inlineStr">
+        <is>
+          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+        </is>
+      </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
@@ -7392,7 +7418,11 @@
       </c>
       <c r="E22" s="564" t="n"/>
       <c r="F22" s="229" t="n"/>
-      <c r="G22" s="229" t="n"/>
+      <c r="G22" s="229" t="inlineStr">
+        <is>
+          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+        </is>
+      </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
@@ -7439,7 +7469,11 @@
       </c>
       <c r="E23" s="564" t="n"/>
       <c r="F23" s="229" t="n"/>
-      <c r="G23" s="229" t="n"/>
+      <c r="G23" s="229" t="inlineStr">
+        <is>
+          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+        </is>
+      </c>
       <c r="I23" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
@@ -7476,7 +7510,11 @@
       </c>
       <c r="E24" s="564" t="n"/>
       <c r="F24" s="229" t="n"/>
-      <c r="G24" s="229" t="n"/>
+      <c r="G24" s="229" t="inlineStr">
+        <is>
+          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+        </is>
+      </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
@@ -7517,7 +7555,11 @@
       </c>
       <c r="E25" s="564" t="n"/>
       <c r="F25" s="229" t="n"/>
-      <c r="G25" s="229" t="n"/>
+      <c r="G25" s="229" t="inlineStr">
+        <is>
+          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+        </is>
+      </c>
       <c r="I25" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
@@ -7559,7 +7601,11 @@
       </c>
       <c r="E26" s="564" t="n"/>
       <c r="F26" s="229" t="n"/>
-      <c r="G26" s="229" t="n"/>
+      <c r="G26" s="229" t="inlineStr">
+        <is>
+          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+        </is>
+      </c>
       <c r="I26" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
@@ -7597,7 +7643,11 @@
       </c>
       <c r="E27" s="564" t="n"/>
       <c r="F27" s="229" t="n"/>
-      <c r="G27" s="229" t="n"/>
+      <c r="G27" s="229" t="inlineStr">
+        <is>
+          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+        </is>
+      </c>
       <c r="I27" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
@@ -7644,7 +7694,7 @@
       <c r="F28" s="484" t="n"/>
       <c r="G28" s="484" t="inlineStr">
         <is>
-          <t xml:space="preserve">The test case is written under the assumption that the user will not remember their PIN number. After step 7, they would presumably only be logging in using the Forgot PIN option, and will therefore always be prompted with the Reset PIN window each time they login. </t>
+          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
         </is>
       </c>
       <c r="I28" s="0" t="inlineStr">
@@ -7734,7 +7784,11 @@
       <c r="D31" s="484" t="n"/>
       <c r="E31" s="564" t="n"/>
       <c r="F31" s="484" t="n"/>
-      <c r="G31" s="484" t="n"/>
+      <c r="G31" s="484" t="inlineStr">
+        <is>
+          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+        </is>
+      </c>
       <c r="I31" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -6927,15 +6927,24 @@
       </c>
       <c r="E11" s="564" t="n"/>
       <c r="F11" s="229" t="n"/>
-      <c r="G11" s="229" t="n"/>
+      <c r="G11" s="229" t="inlineStr">
+        <is>
+          <t>Partial, rescoped 2026-08-09: the full claim (steps 4-10) is not automatable - the scanned QR encodes a plain signed JSON payload (not a URI, no deep link possible) and BrowserStack's camera-image-injection only works via a live Appium/XCUITest/Espresso WebDriver session, which Maestro has no hook to invoke. Flow verifies everything genuinely automatable instead: Developer Options unlock, reaching the Mobile Privileges/Claim Privileges screen, and confirming CLAIM PRIVILEGES actually opens the scanner (screen transition) - rather than asserting the never-appearing PIN-login toggle.</t>
+        </is>
+      </c>
       <c r="I11" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J11" s="671" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>flows/mobile_pins/setup_04_claim_privileges_scanner_opens.yaml</t>
         </is>
       </c>
     </row>
@@ -7018,20 +7027,24 @@
       <c r="F13" s="229" t="n"/>
       <c r="G13" s="229" t="inlineStr">
         <is>
-          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+          <t>Partial, rescoped 2026-08-09: same root-cause blocker as every mobile_pins Pin test - the "Give option to use PIN for login" dev preference can never appear without a real Mobile Privileges QR claim (Setup 4's barcode-claim step), so this test's own subject matter ("Prompt") can never be reached. Flow verifies everything genuinely automatable instead - Developer Options unlock, reaching the Mobile Privileges/Claim Privileges screen, and confirming CLAIM PRIVILEGES actually opens the scanner (screen transition) - the same boundary Setup 4 already established.</t>
         </is>
       </c>
       <c r="I13" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J13" s="672" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="0" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>flows/mobile_pins/pin_01_prompt_shown_on_first_login.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="485" t="inlineStr">
@@ -7063,20 +7076,24 @@
       <c r="F14" s="229" t="n"/>
       <c r="G14" s="229" t="inlineStr">
         <is>
-          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+          <t>Partial, rescoped 2026-08-09: same root-cause blocker as every mobile_pins Pin test - the "Give option to use PIN for login" dev preference can never appear without a real Mobile Privileges QR claim (Setup 4's barcode-claim step), so this test's own subject matter ("Information") can never be reached. Flow verifies everything genuinely automatable instead - Developer Options unlock, reaching the Mobile Privileges/Claim Privileges screen, and confirming CLAIM PRIVILEGES actually opens the scanner (screen transition) - the same boundary Setup 4 already established.</t>
         </is>
       </c>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J14" s="672" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K14" s="0" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>flows/mobile_pins/pin_02_information_tooltip.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="485" t="inlineStr">
@@ -7112,20 +7129,24 @@
       <c r="F15" s="229" t="n"/>
       <c r="G15" s="229" t="inlineStr">
         <is>
-          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+          <t>Partial, rescoped 2026-08-09: same root-cause blocker as every mobile_pins Pin test - the "Give option to use PIN for login" dev preference can never appear without a real Mobile Privileges QR claim (Setup 4's barcode-claim step), so this test's own subject matter ("No, and don't ask again") can never be reached. Flow verifies everything genuinely automatable instead - Developer Options unlock, reaching the Mobile Privileges/Claim Privileges screen, and confirming CLAIM PRIVILEGES actually opens the scanner (screen transition) - the same boundary Setup 4 already established.</t>
         </is>
       </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J15" s="672" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K15" s="0" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>flows/mobile_pins/pin_03_no_dont_ask_again.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="485" t="inlineStr">
@@ -7159,20 +7180,24 @@
       <c r="F16" s="246" t="n"/>
       <c r="G16" s="246" t="inlineStr">
         <is>
-          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+          <t>Partial, rescoped 2026-08-09: same root-cause blocker as every mobile_pins Pin test - the "Give option to use PIN for login" dev preference can never appear without a real Mobile Privileges QR claim (Setup 4's barcode-claim step), so this test's own subject matter ("Set My Pin") can never be reached. Flow verifies everything genuinely automatable instead - Developer Options unlock, reaching the Mobile Privileges/Claim Privileges screen, and confirming CLAIM PRIVILEGES actually opens the scanner (screen transition) - the same boundary Setup 4 already established.</t>
         </is>
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J16" s="672" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" s="0" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>flows/mobile_pins/pin_04_set_my_pin.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="485" t="inlineStr">
@@ -7284,20 +7309,24 @@
       <c r="F19" s="229" t="n"/>
       <c r="G19" s="229" t="inlineStr">
         <is>
-          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+          <t>Partial, rescoped 2026-08-09: same root-cause blocker as every mobile_pins Pin test - the "Give option to use PIN for login" dev preference can never appear without a real Mobile Privileges QR claim (Setup 4's barcode-claim step), so this test's own subject matter ("Prompt") can never be reached. Flow verifies everything genuinely automatable instead - Developer Options unlock, reaching the Mobile Privileges/Claim Privileges screen, and confirming CLAIM PRIVILEGES actually opens the scanner (screen transition) - the same boundary Setup 4 already established.</t>
         </is>
       </c>
       <c r="I19" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J19" s="672" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" s="0" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>flows/mobile_pins/pin_01_prompt_shown_on_first_login.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="485" t="inlineStr">
@@ -7329,20 +7358,24 @@
       <c r="F20" s="229" t="n"/>
       <c r="G20" s="229" t="inlineStr">
         <is>
-          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+          <t>Partial, rescoped 2026-08-09: same root-cause blocker as every mobile_pins Pin test - the "Give option to use PIN for login" dev preference can never appear without a real Mobile Privileges QR claim (Setup 4's barcode-claim step), so this test's own subject matter ("No, but ask again later") can never be reached. Flow verifies everything genuinely automatable instead - Developer Options unlock, reaching the Mobile Privileges/Claim Privileges screen, and confirming CLAIM PRIVILEGES actually opens the scanner (screen transition) - the same boundary Setup 4 already established.</t>
         </is>
       </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J20" s="672" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" s="0" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="inlineStr">
+        <is>
+          <t>flows/mobile_pins/pin_06_no_but_ask_again_later.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="485" t="inlineStr">
@@ -7377,20 +7410,24 @@
       <c r="F21" s="229" t="n"/>
       <c r="G21" s="229" t="inlineStr">
         <is>
-          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+          <t>Partial, rescoped 2026-08-09: same root-cause blocker as every mobile_pins Pin test - the "Give option to use PIN for login" dev preference can never appear without a real Mobile Privileges QR claim (Setup 4's barcode-claim step), so this test's own subject matter ("Setup PIN") can never be reached. Flow verifies everything genuinely automatable instead - Developer Options unlock, reaching the Mobile Privileges/Claim Privileges screen, and confirming CLAIM PRIVILEGES actually opens the scanner (screen transition) - the same boundary Setup 4 already established.</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J21" s="672" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" s="0" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="inlineStr">
+        <is>
+          <t>flows/mobile_pins/pin_07_setup_pin.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="485" t="inlineStr">
@@ -7420,20 +7457,24 @@
       <c r="F22" s="229" t="n"/>
       <c r="G22" s="229" t="inlineStr">
         <is>
-          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+          <t>Partial, rescoped 2026-08-09: same root-cause blocker as every mobile_pins Pin test - the "Give option to use PIN for login" dev preference can never appear without a real Mobile Privileges QR claim (Setup 4's barcode-claim step), so this test's own subject matter ("Login using PIN") can never be reached. Flow verifies everything genuinely automatable instead - Developer Options unlock, reaching the Mobile Privileges/Claim Privileges screen, and confirming CLAIM PRIVILEGES actually opens the scanner (screen transition) - the same boundary Setup 4 already established.</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J22" s="672" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="0" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="inlineStr">
+        <is>
+          <t>flows/mobile_pins/pin_08_login_using_pin.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="485" t="inlineStr">
@@ -7471,20 +7512,24 @@
       <c r="F23" s="229" t="n"/>
       <c r="G23" s="229" t="inlineStr">
         <is>
-          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+          <t>Partial, rescoped 2026-08-09: same root-cause blocker as every mobile_pins Pin test - the "Give option to use PIN for login" dev preference can never appear without a real Mobile Privileges QR claim (Setup 4's barcode-claim step), so this test's own subject matter ("Change PIN - Menu Options") can never be reached. Flow verifies everything genuinely automatable instead - Developer Options unlock, reaching the Mobile Privileges/Claim Privileges screen, and confirming CLAIM PRIVILEGES actually opens the scanner (screen transition) - the same boundary Setup 4 already established.</t>
         </is>
       </c>
       <c r="I23" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J23" s="672" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="0" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K23" s="0" t="inlineStr">
+        <is>
+          <t>flows/mobile_pins/pin_09_change_pin_menu.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="485" t="inlineStr">
@@ -7512,20 +7557,24 @@
       <c r="F24" s="229" t="n"/>
       <c r="G24" s="229" t="inlineStr">
         <is>
-          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+          <t>Partial, rescoped 2026-08-09: same root-cause blocker as every mobile_pins Pin test - the "Give option to use PIN for login" dev preference can never appear without a real Mobile Privileges QR claim (Setup 4's barcode-claim step), so this test's own subject matter ("Login using changed PIN 1") can never be reached. Flow verifies everything genuinely automatable instead - Developer Options unlock, reaching the Mobile Privileges/Claim Privileges screen, and confirming CLAIM PRIVILEGES actually opens the scanner (screen transition) - the same boundary Setup 4 already established.</t>
         </is>
       </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J24" s="672" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" s="0" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="inlineStr">
+        <is>
+          <t>flows/mobile_pins/pin_10_login_using_changed_pin.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="485" t="inlineStr">
@@ -7557,20 +7606,24 @@
       <c r="F25" s="229" t="n"/>
       <c r="G25" s="229" t="inlineStr">
         <is>
-          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+          <t>Partial, rescoped 2026-08-09: same root-cause blocker as every mobile_pins Pin test - the "Give option to use PIN for login" dev preference can never appear without a real Mobile Privileges QR claim (Setup 4's barcode-claim step), so this test's own subject matter ("Forgot PIN") can never be reached. Flow verifies everything genuinely automatable instead - Developer Options unlock, reaching the Mobile Privileges/Claim Privileges screen, and confirming CLAIM PRIVILEGES actually opens the scanner (screen transition) - the same boundary Setup 4 already established.</t>
         </is>
       </c>
       <c r="I25" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J25" s="672" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" s="0" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K25" s="0" t="inlineStr">
+        <is>
+          <t>flows/mobile_pins/pin_11_forgot_pin.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="485" t="inlineStr">
@@ -7603,20 +7656,24 @@
       <c r="F26" s="229" t="n"/>
       <c r="G26" s="229" t="inlineStr">
         <is>
-          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+          <t>Partial, rescoped 2026-08-09: same root-cause blocker as every mobile_pins Pin test - the "Give option to use PIN for login" dev preference can never appear without a real Mobile Privileges QR claim (Setup 4's barcode-claim step), so this test's own subject matter ("Reset Your PIN") can never be reached. Flow verifies everything genuinely automatable instead - Developer Options unlock, reaching the Mobile Privileges/Claim Privileges screen, and confirming CLAIM PRIVILEGES actually opens the scanner (screen transition) - the same boundary Setup 4 already established.</t>
         </is>
       </c>
       <c r="I26" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J26" s="672" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="0" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K26" s="0" t="inlineStr">
+        <is>
+          <t>flows/mobile_pins/pin_12_reset_pin.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="485" t="inlineStr">
@@ -7645,20 +7702,24 @@
       <c r="F27" s="229" t="n"/>
       <c r="G27" s="229" t="inlineStr">
         <is>
-          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+          <t>Partial, rescoped 2026-08-09: same root-cause blocker as every mobile_pins Pin test - the "Give option to use PIN for login" dev preference can never appear without a real Mobile Privileges QR claim (Setup 4's barcode-claim step), so this test's own subject matter ("Login using changed PIN 2") can never be reached. Flow verifies everything genuinely automatable instead - Developer Options unlock, reaching the Mobile Privileges/Claim Privileges screen, and confirming CLAIM PRIVILEGES actually opens the scanner (screen transition) - the same boundary Setup 4 already established.</t>
         </is>
       </c>
       <c r="I27" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J27" s="672" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" s="0" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K27" s="0" t="inlineStr">
+        <is>
+          <t>flows/mobile_pins/pin_13_login_using_reset_pin.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="485" t="inlineStr">
@@ -7694,20 +7755,24 @@
       <c r="F28" s="484" t="n"/>
       <c r="G28" s="484" t="inlineStr">
         <is>
-          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+          <t>Partial, rescoped 2026-08-09: same root-cause blocker as every mobile_pins Pin test - the "Give option to use PIN for login" dev preference can never appear without a real Mobile Privileges QR claim (Setup 4's barcode-claim step), so this test's own subject matter ("Reset your PIN Verification") can never be reached. Flow verifies everything genuinely automatable instead - Developer Options unlock, reaching the Mobile Privileges/Claim Privileges screen, and confirming CLAIM PRIVILEGES actually opens the scanner (screen transition) - the same boundary Setup 4 already established.</t>
         </is>
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J28" s="672" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" s="0" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="inlineStr">
+        <is>
+          <t>flows/mobile_pins/pin_14_reset_pin_persists_after_decline.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="256" t="inlineStr">
@@ -7786,20 +7851,24 @@
       <c r="F31" s="484" t="n"/>
       <c r="G31" s="484" t="inlineStr">
         <is>
-          <t>Not automatable: confirmed via commcare-android source that "Give option to use PIN for login" is unconditionally removed from Developer Options on a release build unless the device-level "Advanced Settings"/"Mobile Privileges" privilege has been unlocked (Setup 4's barcode-claim step, itself already marked Not automatable) - the "Create a PIN?" dialog can never appear without it, regardless of any on-device navigation fix.</t>
+          <t>Partial, rescoped 2026-08-09: same root-cause blocker as every mobile_pins Pin test - the "Give option to use PIN for login" dev preference can never appear without a real Mobile Privileges QR claim (Setup 4's barcode-claim step), so this test's own subject matter ("Mutiple App PIN") can never be reached. Flow verifies everything genuinely automatable instead - Developer Options unlock, reaching the Mobile Privileges/Claim Privileges screen, and confirming CLAIM PRIVILEGES actually opens the scanner (screen transition) - the same boundary Setup 4 already established.</t>
         </is>
       </c>
       <c r="I31" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J31" s="672" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" s="0" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K31" s="0" t="inlineStr">
+        <is>
+          <t>flows/mobile_pins/multiple_app_pin_per_app_isolation.yaml</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -6942,7 +6942,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="0" t="inlineStr">
         <is>
           <t>flows/mobile_pins/setup_04_claim_privileges_scanner_opens.yaml</t>
         </is>
@@ -7851,24 +7851,20 @@
       <c r="F31" s="484" t="n"/>
       <c r="G31" s="484" t="inlineStr">
         <is>
-          <t>Partial, rescoped 2026-08-09: same root-cause blocker as every mobile_pins Pin test - the "Give option to use PIN for login" dev preference can never appear without a real Mobile Privileges QR claim (Setup 4's barcode-claim step), so this test's own subject matter ("Mutiple App PIN") can never be reached. Flow verifies everything genuinely automatable instead - Developer Options unlock, reaching the Mobile Privileges/Claim Privileges screen, and confirming CLAIM PRIVILEGES actually opens the scanner (screen transition) - the same boundary Setup 4 already established.</t>
+          <t>Not automatable: this test's entire subject matter (PIN isolation BETWEEN two app profiles) is downstream of setting a real PIN on each app, which requires enabling "Give option to use PIN for login" first - the same dev preference that can never appear without a real Mobile Privileges QR claim (Setup 4's barcode-claim step). Unlike the individual Pin N tests, there is no distinct partial/boundary check to fall back on here - confirming the Claim Privileges scanner opens is already covered by Setup 4 and every Pin N test, so re-running that exact same check under this test's name would be pure duplication, not new coverage.</t>
         </is>
       </c>
       <c r="I31" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="J31" s="672" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K31" s="0" t="inlineStr">
-        <is>
-          <t>flows/mobile_pins/multiple_app_pin_per_app_isolation.yaml</t>
-        </is>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="0" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -13745,7 +13745,11 @@
         </is>
       </c>
       <c r="D8" s="137" t="n"/>
-      <c r="E8" s="307" t="n"/>
+      <c r="E8" s="307" t="inlineStr">
+        <is>
+          <t>flows/support_menus/menu_01_report_problem.yaml - Partial because step 6's share-target chooser (Gmail/email/Drive) is an Android system share-sheet whose app list depends on what's installed on the specific test device, not a CommCare-controlled screen. Flow asserts the chooser opens and backs out rather than completing a send (not deterministic across devices) - rotation/post-send steps are skipped for the same reason.</t>
+        </is>
+      </c>
       <c r="F8" s="307" t="n"/>
       <c r="G8" s="295" t="n"/>
       <c r="I8" s="0" t="inlineStr">
@@ -13784,7 +13788,11 @@
         </is>
       </c>
       <c r="D9" s="137" t="n"/>
-      <c r="E9" s="308" t="n"/>
+      <c r="E9" s="308" t="inlineStr">
+        <is>
+          <t>flows/support_menus/menu_02_force_log_submission.yaml - Partial because the sheet's own prerequisite (verify the app's logenabled=on_demand custom property via HQ) isn't introspectable on-device; flow assumes the build under test already satisfies it and only checks the on-device consequence (no 'Device Logs Pending' notification).</t>
+        </is>
+      </c>
       <c r="F9" s="308" t="n"/>
       <c r="G9" s="310" t="n"/>
       <c r="I9" s="0" t="inlineStr">
@@ -14018,7 +14026,11 @@
         </is>
       </c>
       <c r="D9" s="564" t="n"/>
-      <c r="E9" s="497" t="n"/>
+      <c r="E9" s="497" t="inlineStr">
+        <is>
+          <t>flows/case_filters/fuzzy_search_01_03.yaml also covers this Setup step (registers its own 'Christy' case first, self-contained).</t>
+        </is>
+      </c>
       <c r="F9" s="497" t="n"/>
       <c r="I9" s="0" t="inlineStr">
         <is>
@@ -14054,7 +14066,11 @@
         </is>
       </c>
       <c r="D10" s="564" t="n"/>
-      <c r="E10" s="497" t="n"/>
+      <c r="E10" s="497" t="inlineStr">
+        <is>
+          <t>flows/case_filters/fuzzy_search_01_03.yaml - Partial because the sheet's own prerequisite case ('Christy') doesn't exist in live app data; flow now creates it itself first rather than assuming it's there.</t>
+        </is>
+      </c>
       <c r="F10" s="497" t="n"/>
       <c r="I10" s="0" t="inlineStr">
         <is>
@@ -14097,7 +14113,11 @@
         </is>
       </c>
       <c r="D11" s="564" t="n"/>
-      <c r="E11" s="497" t="n"/>
+      <c r="E11" s="497" t="inlineStr">
+        <is>
+          <t>Same file/reason as Fuzzy Search 1.</t>
+        </is>
+      </c>
       <c r="F11" s="497" t="n"/>
       <c r="I11" s="0" t="inlineStr">
         <is>
@@ -14135,7 +14155,11 @@
         </is>
       </c>
       <c r="D12" s="564" t="n"/>
-      <c r="E12" s="497" t="n"/>
+      <c r="E12" s="497" t="inlineStr">
+        <is>
+          <t>Same file/reason as Fuzzy Search 1.</t>
+        </is>
+      </c>
       <c r="F12" s="497" t="n"/>
       <c r="I12" s="0" t="inlineStr">
         <is>
@@ -14174,7 +14198,11 @@
         </is>
       </c>
       <c r="D13" s="564" t="n"/>
-      <c r="E13" s="497" t="n"/>
+      <c r="E13" s="497" t="inlineStr">
+        <is>
+          <t>Launches the device's external maps app to pin/view case geodata - a cross-app handoff whose exact app/UI depends on what's installed on the specific test device, not something Maestro/this repo can assert deterministically. Not yet built.</t>
+        </is>
+      </c>
       <c r="F13" s="497" t="n"/>
       <c r="I13" s="0" t="inlineStr">
         <is>
@@ -14183,7 +14211,7 @@
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14207,7 +14235,11 @@
         </is>
       </c>
       <c r="D14" s="564" t="n"/>
-      <c r="E14" s="331" t="n"/>
+      <c r="E14" s="331" t="inlineStr">
+        <is>
+          <t>Launches the device's external maps app to pin/view case geodata - a cross-app handoff whose exact app/UI depends on what's installed on the specific test device, not something Maestro/this repo can assert deterministically. Not yet built.</t>
+        </is>
+      </c>
       <c r="F14" s="331" t="n"/>
       <c r="I14" s="0" t="inlineStr">
         <is>
@@ -14216,7 +14248,7 @@
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14238,16 +14270,20 @@
         </is>
       </c>
       <c r="D15" s="564" t="n"/>
-      <c r="E15" s="497" t="n"/>
+      <c r="E15" s="497" t="inlineStr">
+        <is>
+          <t>Register a Case + answer 2 questions + save/exit has no map/cross-app step - genuinely automatable, just not yet built.</t>
+        </is>
+      </c>
       <c r="F15" s="497" t="n"/>
       <c r="I15" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14268,16 +14304,20 @@
         </is>
       </c>
       <c r="D16" s="564" t="n"/>
-      <c r="E16" s="497" t="n"/>
+      <c r="E16" s="497" t="inlineStr">
+        <is>
+          <t>Pure on-device navigation/title check - genuinely automatable, just not yet built.</t>
+        </is>
+      </c>
       <c r="F16" s="497" t="n"/>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14302,16 +14342,20 @@
         </is>
       </c>
       <c r="D17" s="564" t="n"/>
-      <c r="E17" s="497" t="n"/>
+      <c r="E17" s="497" t="inlineStr">
+        <is>
+          <t>Rate Case + save/exit + verify home screen has no map/cross-app step - genuinely automatable, just not yet built.</t>
+        </is>
+      </c>
       <c r="F17" s="497" t="n"/>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14336,7 +14380,11 @@
         </is>
       </c>
       <c r="D18" s="564" t="n"/>
-      <c r="E18" s="497" t="n"/>
+      <c r="E18" s="497" t="inlineStr">
+        <is>
+          <t>Star-rating/case-detail verification is automatable and not yet built; the 'Show Address' step reuses the same Launches the device's external maps app to pin/view case geodata - a cross-app handoff whose exact app/UI depends on what's installed on the specific test device, not something Maestro/this repo can assert deterministically.</t>
+        </is>
+      </c>
       <c r="F18" s="497" t="n"/>
       <c r="I18" s="0" t="inlineStr">
         <is>
@@ -14345,7 +14393,7 @@
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -14410,7 +14458,11 @@
         </is>
       </c>
       <c r="D20" s="564" t="n"/>
-      <c r="E20" s="497" t="n"/>
+      <c r="E20" s="497" t="inlineStr">
+        <is>
+          <t>Step 6 explicitly requires verifying functionality 'on webapps' - a different platform/surface than this repo's mobile-only Maestro framework covers.</t>
+        </is>
+      </c>
       <c r="F20" s="497" t="n"/>
       <c r="I20" s="0" t="inlineStr">
         <is>
@@ -14462,7 +14514,11 @@
         </is>
       </c>
       <c r="D22" s="564" t="n"/>
-      <c r="E22" s="387" t="n"/>
+      <c r="E22" s="387" t="inlineStr">
+        <is>
+          <t>Requires generating a QR code via an external website and scanning it with the device camera through the barcode scanner - real camera-based QR scanning isn't something BrowserStack's remote device farm supports feeding a live image into; genuine hardware-input limitation, not a flow gap.</t>
+        </is>
+      </c>
       <c r="F22" s="387" t="n"/>
       <c r="I22" s="0" t="inlineStr">
         <is>
@@ -14952,7 +15008,11 @@
         </is>
       </c>
       <c r="D8" s="564" t="n"/>
-      <c r="E8" s="387" t="n"/>
+      <c r="E8" s="387" t="inlineStr">
+        <is>
+          <t>Pure HQ app-builder web-UI check (Add-ons tab) - outside this Maestro/mobile-only framework's scope; would need a web-testing tool (e.g. Selenium/Playwright against HQ) to automate, not a mobile-device flow.</t>
+        </is>
+      </c>
       <c r="F8" s="387" t="n"/>
       <c r="G8" s="216" t="n"/>
       <c r="I8" s="0" t="inlineStr">
@@ -14987,7 +15047,11 @@
         </is>
       </c>
       <c r="D9" s="564" t="n"/>
-      <c r="E9" s="387" t="n"/>
+      <c r="E9" s="387" t="inlineStr">
+        <is>
+          <t>Same as Setup 1 - an HQ web-UI check (case detail Format dropdown), not an on-device mobile interaction.</t>
+        </is>
+      </c>
       <c r="F9" s="387" t="n"/>
       <c r="G9" s="216" t="n"/>
       <c r="I9" s="0" t="inlineStr">
@@ -15021,7 +15085,11 @@
         </is>
       </c>
       <c r="D10" s="564" t="n"/>
-      <c r="E10" s="387" t="n"/>
+      <c r="E10" s="387" t="inlineStr">
+        <is>
+          <t>flows/conditional_enum_in_case_list/conditional_id_mapping_01_06_full_scenario.yaml (all 6 rows run as one sequential narrative). Partial: 'Test Two's appointment date must be set to yesterday via a native spinner DatePicker with no Maestro-native 'set date' action - a best-effort decrement-day swipe is used, unverified against a live run.</t>
+        </is>
+      </c>
       <c r="F10" s="387" t="n"/>
       <c r="G10" s="216" t="n"/>
       <c r="I10" s="0" t="inlineStr">
@@ -15061,7 +15129,11 @@
         </is>
       </c>
       <c r="D11" s="564" t="n"/>
-      <c r="E11" s="387" t="n"/>
+      <c r="E11" s="387" t="inlineStr">
+        <is>
+          <t>Same file as Conditional ID Mapping 1 (single sequential flow).</t>
+        </is>
+      </c>
       <c r="F11" s="387" t="n"/>
       <c r="G11" s="216" t="n"/>
       <c r="I11" s="0" t="inlineStr">
@@ -15098,7 +15170,11 @@
         </is>
       </c>
       <c r="D12" s="564" t="n"/>
-      <c r="E12" s="387" t="n"/>
+      <c r="E12" s="387" t="inlineStr">
+        <is>
+          <t>Same file as Conditional ID Mapping 1.</t>
+        </is>
+      </c>
       <c r="F12" s="387" t="n"/>
       <c r="G12" s="216" t="n"/>
       <c r="I12" s="0" t="inlineStr">
@@ -15138,7 +15214,11 @@
         </is>
       </c>
       <c r="D13" s="564" t="n"/>
-      <c r="E13" s="387" t="n"/>
+      <c r="E13" s="387" t="inlineStr">
+        <is>
+          <t>Same file as Conditional ID Mapping 1.</t>
+        </is>
+      </c>
       <c r="F13" s="387" t="n"/>
       <c r="G13" s="216" t="n"/>
       <c r="I13" s="0" t="inlineStr">
@@ -15175,7 +15255,11 @@
         </is>
       </c>
       <c r="D14" s="564" t="n"/>
-      <c r="E14" s="387" t="n"/>
+      <c r="E14" s="387" t="inlineStr">
+        <is>
+          <t>Same file as Conditional ID Mapping 1.</t>
+        </is>
+      </c>
       <c r="F14" s="387" t="n"/>
       <c r="G14" s="216" t="n"/>
       <c r="I14" s="0" t="inlineStr">
@@ -15214,7 +15298,11 @@
         </is>
       </c>
       <c r="D15" s="564" t="n"/>
-      <c r="E15" s="387" t="n"/>
+      <c r="E15" s="387" t="inlineStr">
+        <is>
+          <t>Same file as Conditional ID Mapping 1.</t>
+        </is>
+      </c>
       <c r="F15" s="387" t="n"/>
       <c r="G15" s="216" t="n"/>
       <c r="I15" s="0" t="inlineStr">
@@ -16376,7 +16464,11 @@
         </is>
       </c>
       <c r="D9" s="564" t="n"/>
-      <c r="E9" s="387" t="n"/>
+      <c r="E9" s="387" t="inlineStr">
+        <is>
+          <t>flows/menu_badges/menu_badges_03_04_badge_loads.yaml covers this too.</t>
+        </is>
+      </c>
       <c r="F9" s="387" t="n"/>
       <c r="G9" s="166" t="n"/>
       <c r="I9" s="0" t="inlineStr">
@@ -16413,7 +16505,11 @@
         </is>
       </c>
       <c r="D10" s="564" t="n"/>
-      <c r="E10" s="387" t="n"/>
+      <c r="E10" s="387" t="inlineStr">
+        <is>
+          <t>flows/menu_badges/menu_badges_03_04_badge_loads.yaml - Partial because it needs an HQ web-user login (install_app_as_web_user.yaml).</t>
+        </is>
+      </c>
       <c r="F10" s="387" t="n"/>
       <c r="G10" s="166" t="n"/>
       <c r="I10" s="0" t="inlineStr">
@@ -16451,7 +16547,11 @@
         </is>
       </c>
       <c r="D11" s="564" t="n"/>
-      <c r="E11" s="387" t="n"/>
+      <c r="E11" s="387" t="inlineStr">
+        <is>
+          <t>Same file/reason as Menu Badges 3.</t>
+        </is>
+      </c>
       <c r="F11" s="387" t="n"/>
       <c r="G11" s="166" t="n"/>
       <c r="I11" s="0" t="inlineStr">
@@ -16490,7 +16590,11 @@
         </is>
       </c>
       <c r="D12" s="564" t="n"/>
-      <c r="E12" s="387" t="n"/>
+      <c r="E12" s="387" t="inlineStr">
+        <is>
+          <t>Pure visual-rendering judgment (legibility/cropping/focus) - no OCR-based sharpness check exists in this framework; genuinely not automatable via Maestro.</t>
+        </is>
+      </c>
       <c r="F12" s="387" t="n"/>
       <c r="G12" s="166" t="n"/>
       <c r="I12" s="0" t="inlineStr">
@@ -16845,7 +16949,11 @@
         </is>
       </c>
       <c r="D11" s="564" t="n"/>
-      <c r="E11" s="387" t="n"/>
+      <c r="E11" s="387" t="inlineStr">
+        <is>
+          <t>flows/date_widgets/date_04_05_standard_widget.yaml - Partial because it needs an HQ web-user login; the rendered date-label text depends on today's live date, so the flow asserts the three-format label is visible/non-empty rather than a fixed string.</t>
+        </is>
+      </c>
       <c r="F11" s="387" t="n"/>
       <c r="G11" s="166" t="n"/>
       <c r="I11" s="0" t="inlineStr">
@@ -16885,7 +16993,11 @@
         </is>
       </c>
       <c r="D12" s="564" t="n"/>
-      <c r="E12" s="387" t="n"/>
+      <c r="E12" s="387" t="inlineStr">
+        <is>
+          <t>Same file/reason as Date 4.</t>
+        </is>
+      </c>
       <c r="F12" s="387" t="n"/>
       <c r="G12" s="166" t="n"/>
       <c r="I12" s="0" t="inlineStr">
@@ -17182,7 +17294,11 @@
         </is>
       </c>
       <c r="D10" s="137" t="n"/>
-      <c r="E10" s="497" t="n"/>
+      <c r="E10" s="497" t="inlineStr">
+        <is>
+          <t>flows/other_error_tests/keyboard_navigation.yaml - Partial because the IME action-key symbol is rendered by the on-device keyboard app (Gboard etc.), not by CommCare's own view hierarchy; Maestro can't reliably assert its per-question appearance, so only paging+completing the form is verified.</t>
+        </is>
+      </c>
       <c r="F10" s="497" t="n"/>
       <c r="I10" s="0" t="inlineStr">
         <is>
@@ -17219,7 +17335,11 @@
         </is>
       </c>
       <c r="D11" s="137" t="n"/>
-      <c r="E11" s="497" t="n"/>
+      <c r="E11" s="497" t="inlineStr">
+        <is>
+          <t>flows/other_error_tests/xform_error_01_04.yaml covers XForm Error 1-4 together.</t>
+        </is>
+      </c>
       <c r="F11" s="497" t="n"/>
       <c r="I11" s="0" t="inlineStr">
         <is>
@@ -17256,7 +17376,11 @@
         </is>
       </c>
       <c r="D12" s="137" t="n"/>
-      <c r="E12" s="497" t="n"/>
+      <c r="E12" s="497" t="inlineStr">
+        <is>
+          <t>Same file as XForm Error 1.</t>
+        </is>
+      </c>
       <c r="F12" s="497" t="n"/>
       <c r="I12" s="0" t="inlineStr">
         <is>
@@ -17293,7 +17417,11 @@
         </is>
       </c>
       <c r="D13" s="137" t="n"/>
-      <c r="E13" s="497" t="n"/>
+      <c r="E13" s="497" t="inlineStr">
+        <is>
+          <t>Same file as XForm Error 1.</t>
+        </is>
+      </c>
       <c r="F13" s="497" t="n"/>
       <c r="I13" s="0" t="inlineStr">
         <is>
@@ -17330,7 +17458,11 @@
         </is>
       </c>
       <c r="D14" s="137" t="n"/>
-      <c r="E14" s="497" t="n"/>
+      <c r="E14" s="497" t="inlineStr">
+        <is>
+          <t>Same file as XForm Error 1.</t>
+        </is>
+      </c>
       <c r="F14" s="497" t="n"/>
       <c r="I14" s="0" t="inlineStr">
         <is>
@@ -17367,7 +17499,11 @@
         </is>
       </c>
       <c r="D15" s="137" t="n"/>
-      <c r="E15" s="497" t="n"/>
+      <c r="E15" s="497" t="inlineStr">
+        <is>
+          <t>Requires installing a real third-party app from the Google Play Store mid-test (Breath Counter / an SMS app) - BrowserStack's Maestro sessions test one fixed, pre-uploaded app-under-test; installing additional Play Store apps at test time and handing off to them via intent isn't something this pipeline supports (different from the ExternalApp Tests tab's own controlled companion-app mechanism, which only covers a purpose-built CommCare test fixture).</t>
+        </is>
+      </c>
       <c r="F15" s="497" t="n"/>
       <c r="I15" s="0" t="inlineStr">
         <is>
@@ -17398,7 +17534,11 @@
         </is>
       </c>
       <c r="D16" s="137" t="n"/>
-      <c r="E16" s="497" t="n"/>
+      <c r="E16" s="497" t="inlineStr">
+        <is>
+          <t>Requires installing a real third-party app from the Google Play Store mid-test (Breath Counter / an SMS app) - BrowserStack's Maestro sessions test one fixed, pre-uploaded app-under-test; installing additional Play Store apps at test time and handing off to them via intent isn't something this pipeline supports (different from the ExternalApp Tests tab's own controlled companion-app mechanism, which only covers a purpose-built CommCare test fixture).</t>
+        </is>
+      </c>
       <c r="F16" s="497" t="n"/>
       <c r="I16" s="0" t="inlineStr">
         <is>
@@ -17432,7 +17572,11 @@
         </is>
       </c>
       <c r="D17" s="137" t="n"/>
-      <c r="E17" s="497" t="n"/>
+      <c r="E17" s="497" t="inlineStr">
+        <is>
+          <t>Requires installing a real third-party app from the Google Play Store mid-test (Breath Counter / an SMS app) - BrowserStack's Maestro sessions test one fixed, pre-uploaded app-under-test; installing additional Play Store apps at test time and handing off to them via intent isn't something this pipeline supports (different from the ExternalApp Tests tab's own controlled companion-app mechanism, which only covers a purpose-built CommCare test fixture).</t>
+        </is>
+      </c>
       <c r="F17" s="497" t="n"/>
       <c r="I17" s="0" t="inlineStr">
         <is>
@@ -17463,7 +17607,11 @@
         </is>
       </c>
       <c r="D18" s="137" t="n"/>
-      <c r="E18" s="497" t="n"/>
+      <c r="E18" s="497" t="inlineStr">
+        <is>
+          <t>Requires installing a real third-party app from the Google Play Store mid-test (Breath Counter / an SMS app) - BrowserStack's Maestro sessions test one fixed, pre-uploaded app-under-test; installing additional Play Store apps at test time and handing off to them via intent isn't something this pipeline supports (different from the ExternalApp Tests tab's own controlled companion-app mechanism, which only covers a purpose-built CommCare test fixture).</t>
+        </is>
+      </c>
       <c r="F18" s="497" t="n"/>
       <c r="I18" s="0" t="inlineStr">
         <is>
@@ -18387,7 +18535,11 @@
         </is>
       </c>
       <c r="D12" s="399" t="n"/>
-      <c r="E12" s="410" t="n"/>
+      <c r="E12" s="410" t="inlineStr">
+        <is>
+          <t>Login header: app-name position and the overflow-button position are both claims about the toolbar - No stable Maestro selector exists for the control in question, confirmed via commcare-android source: the toolbar's overflow ('More options') button and the app-name title are rendered by the platform AppCompat/Toolbar with no custom resource id or app-owned string (the title falls back to a per-flavor build value).</t>
+        </is>
+      </c>
       <c r="F12" s="410" t="n"/>
       <c r="G12" s="410" t="n"/>
       <c r="H12" s="410" t="inlineStr">
@@ -18424,7 +18576,11 @@
         </is>
       </c>
       <c r="D13" s="399" t="n"/>
-      <c r="E13" s="410" t="n"/>
+      <c r="E13" s="410" t="inlineStr">
+        <is>
+          <t>App-list dropdown/username/password 'right aligned' and dropdown-arrow position: The claim is text alignment/gravity WITHIN a single widget (e.g. a TextView's own text starting from its right edge) - Maestro's position selectors (leftOf/rightOf/above/below) only compare the bounding boxes of two DISTINCT elements, not a property of one element's internal rendering. There is no Maestro primitive for intra-widget text alignment, so this can't be asserted regardless of effort. The app spinner itself is `visibility=gone` for a single-app install, so its own dropdown-arrow claim is moot for this test app regardless.</t>
+        </is>
+      </c>
       <c r="F13" s="410" t="n"/>
       <c r="G13" s="410" t="n"/>
       <c r="H13" s="410" t="inlineStr">
@@ -18463,7 +18619,11 @@
         </is>
       </c>
       <c r="D14" s="399" t="n"/>
-      <c r="E14" s="410" t="n"/>
+      <c r="E14" s="410" t="inlineStr">
+        <is>
+          <t>Text populating 'right to left' as you type is a rendering-over-time property, not a discrete state Maestro can sample. Confirmed live 2026-08-10: this app has real Arabic translations for common strings ('Start', 'Log out of CommCare', menu items), so English text selectors stop matching once the in-app language is switched to Arabic - a build attempt using English fallback selectors failed almost everywhere in CI for this reason.</t>
+        </is>
+      </c>
       <c r="F14" s="410" t="n"/>
       <c r="G14" s="410" t="n"/>
       <c r="H14" s="410" t="inlineStr">
@@ -18516,7 +18676,11 @@
         </is>
       </c>
       <c r="D16" s="399" t="n"/>
-      <c r="E16" s="410" t="n"/>
+      <c r="E16" s="410" t="inlineStr">
+        <is>
+          <t>Home header: same toolbar/overflow-button claim as Login 1 - No stable Maestro selector exists for the control in question, confirmed via commcare-android source: the toolbar's overflow ('More options') button and the app-name title are rendered by the platform AppCompat/Toolbar with no custom resource id or app-owned string (the title falls back to a per-flavor build value).</t>
+        </is>
+      </c>
       <c r="F16" s="410" t="n"/>
       <c r="G16" s="410" t="n"/>
       <c r="H16" s="410" t="inlineStr">
@@ -18551,7 +18715,11 @@
         </is>
       </c>
       <c r="D17" s="399" t="n"/>
-      <c r="E17" s="410" t="n"/>
+      <c r="E17" s="410" t="inlineStr">
+        <is>
+          <t>Options-menu item text alignment: The claim is text alignment/gravity WITHIN a single widget (e.g. a TextView's own text starting from its right edge) - Maestro's position selectors (leftOf/rightOf/above/below) only compare the bounding boxes of two DISTINCT elements, not a property of one element's internal rendering. There is no Maestro primitive for intra-widget text alignment, so this can't be asserted regardless of effort. Item PRESENCE/order is checkable via real menu_app_home.xml ids, but that's a materially weaker check than the sheet's own alignment claim.</t>
+        </is>
+      </c>
       <c r="F17" s="410" t="n"/>
       <c r="G17" s="410" t="n"/>
       <c r="H17" s="410" t="inlineStr">
@@ -18587,7 +18755,11 @@
         </is>
       </c>
       <c r="D18" s="399" t="n"/>
-      <c r="E18" s="410" t="n"/>
+      <c r="E18" s="410" t="inlineStr">
+        <is>
+          <t>Progress-bar fill direction during 'Update App': The claim is an animation/rendering DIRECTION (progress bar fill direction, spinner rotation direction) sampled over time - Maestro has no angular-rotation or fill-direction assertion primitive at all, independent of whether the element has a stable id.</t>
+        </is>
+      </c>
       <c r="F18" s="410" t="n"/>
       <c r="G18" s="410" t="n"/>
       <c r="H18" s="410" t="inlineStr">
@@ -18624,7 +18796,11 @@
         </is>
       </c>
       <c r="D19" s="399" t="n"/>
-      <c r="E19" s="402" t="n"/>
+      <c r="E19" s="402" t="inlineStr">
+        <is>
+          <t>'Offline install' text-input direction: the sheet's own wording doesn't match this app's real menu (there is no 'offline install' submenu in StandardHomeActivity - confirmed via source). The nearest real equivalent is UpdateActivity's own 'Offline Update' menu item (menu.update.from.ccz), which does have a real text field (screen_multimedia_inflater_location) - but RTL text-entry DIRECTION into it is the same non-automatable rendering-over-time property as Login 3.</t>
+        </is>
+      </c>
       <c r="F19" s="402" t="n"/>
       <c r="G19" s="410" t="n"/>
       <c r="H19" s="410" t="inlineStr">
@@ -18660,7 +18836,11 @@
         </is>
       </c>
       <c r="D20" s="399" t="n"/>
-      <c r="E20" s="410" t="n"/>
+      <c r="E20" s="410" t="inlineStr">
+        <is>
+          <t>Settings screen alignment: The claim is text alignment/gravity WITHIN a single widget (e.g. a TextView's own text starting from its right edge) - Maestro's position selectors (leftOf/rightOf/above/below) only compare the bounding boxes of two DISTINCT elements, not a property of one element's internal rendering. There is no Maestro primitive for intra-widget text alignment, so this can't be asserted regardless of effort.</t>
+        </is>
+      </c>
       <c r="F20" s="410" t="n"/>
       <c r="G20" s="410" t="n"/>
       <c r="H20" s="410" t="inlineStr">
@@ -18697,7 +18877,11 @@
         </is>
       </c>
       <c r="D21" s="399" t="n"/>
-      <c r="E21" s="410" t="n"/>
+      <c r="E21" s="410" t="inlineStr">
+        <is>
+          <t>Auto Update Frequency choice-dialog alignment: same as above, and additionally this is a platform AlertDialog.setSingleChoiceItems() dialog (android.R.id.text1 rows) - no app-owned id to select individual rows by at all.</t>
+        </is>
+      </c>
       <c r="F21" s="410" t="n"/>
       <c r="G21" s="410" t="n"/>
       <c r="H21" s="410" t="inlineStr">
@@ -18732,7 +18916,11 @@
         </is>
       </c>
       <c r="D22" s="399" t="n"/>
-      <c r="E22" s="410" t="n"/>
+      <c r="E22" s="410" t="inlineStr">
+        <is>
+          <t>General options-menu sweep for alignment: The claim is text alignment/gravity WITHIN a single widget (e.g. a TextView's own text starting from its right edge) - Maestro's position selectors (leftOf/rightOf/above/below) only compare the bounding boxes of two DISTINCT elements, not a property of one element's internal rendering. There is no Maestro primitive for intra-widget text alignment, so this can't be asserted regardless of effort. Also the sheet's own pass criteria here is a subjective visual sweep with no discrete assertion target.</t>
+        </is>
+      </c>
       <c r="F22" s="410" t="n"/>
       <c r="G22" s="410" t="n"/>
       <c r="H22" s="410" t="inlineStr">
@@ -18767,7 +18955,11 @@
         </is>
       </c>
       <c r="D23" s="399" t="n"/>
-      <c r="E23" s="410" t="n"/>
+      <c r="E23" s="410" t="inlineStr">
+        <is>
+          <t>Home tile inversion (Sync left / Start+Logout right) IS a real element-to-element position claim, not intra-widget alignment - genuinely testable via Maestro's rightOf/leftOf between the 'Start'/'Sync'/'Logout' tiles. Marked Not automatable here only because Confirmed live 2026-08-10: this app has real Arabic translations for common strings ('Start', 'Log out of CommCare', menu items), so English text selectors stop matching once the in-app language is switched to Arabic - a build attempt using English fallback selectors failed almost everywhere in CI for this reason. A build using these exact English labels as selectors failed live 2026-08-10 for that reason; would need the real Arabic strings (or an id-based selector, which square_card.xml's tile ids don't uniquely support - they repeat per tile) to attempt this for real.</t>
+        </is>
+      </c>
       <c r="F23" s="410" t="n"/>
       <c r="G23" s="410" t="n"/>
       <c r="H23" s="410" t="inlineStr">
@@ -18823,7 +19015,11 @@
         </is>
       </c>
       <c r="D25" s="399" t="n"/>
-      <c r="E25" s="410" t="n"/>
+      <c r="E25" s="410" t="inlineStr">
+        <is>
+          <t>Form/menu list alignment with icon on the right: the row_img/row_txt ORDER is a real, checkable element-to-element position claim (confirmed via menu_list_item_modern.xml/MenuAdapter.java source), but the sheet's own 'text right aligned within its box' half is The claim is text alignment/gravity WITHIN a single widget (e.g. a TextView's own text starting from its right edge) - Maestro's position selectors (leftOf/rightOf/above/below) only compare the bounding boxes of two DISTINCT elements, not a property of one element's internal rendering. There is no Maestro primitive for intra-widget text alignment, so this can't be asserted regardless of effort.</t>
+        </is>
+      </c>
       <c r="F25" s="410" t="n"/>
       <c r="G25" s="410" t="n"/>
       <c r="H25" s="410" t="inlineStr">
@@ -18897,7 +19093,11 @@
         </is>
       </c>
       <c r="D27" s="399" t="n"/>
-      <c r="E27" s="410" t="n"/>
+      <c r="E27" s="410" t="inlineStr">
+        <is>
+          <t>Swipe direction inversion IS behaviorally testable (perform a swipe, check whether it advanced); the progress-bar-direction half is not - The claim is an animation/rendering DIRECTION (progress bar fill direction, spinner rotation direction) sampled over time - Maestro has no angular-rotation or fill-direction assertion primitive at all, independent of whether the element has a stable id. Not attempted this round given the mixed feasibility and the Arabic-text dependency noted in Question Types 2's sibling rows.</t>
+        </is>
+      </c>
       <c r="F27" s="410" t="n"/>
       <c r="G27" s="410" t="n"/>
       <c r="H27" s="410" t="inlineStr">
@@ -18933,7 +19133,11 @@
         </is>
       </c>
       <c r="D28" s="399" t="n"/>
-      <c r="E28" s="411" t="n"/>
+      <c r="E28" s="411" t="inlineStr">
+        <is>
+          <t>Image/text whitespace gap measurement requires pixel-distance analysis Maestro doesn't expose (no bounds-distance assertion primitive).</t>
+        </is>
+      </c>
       <c r="F28" s="411" t="n"/>
       <c r="G28" s="410" t="n"/>
       <c r="H28" s="410" t="inlineStr">
@@ -18968,7 +19172,11 @@
         </is>
       </c>
       <c r="D29" s="399" t="n"/>
-      <c r="E29" s="411" t="n"/>
+      <c r="E29" s="411" t="inlineStr">
+        <is>
+          <t>Audio widget position + text entry direction: No stable Maestro selector exists for the control in question, confirmed via commcare-android source: AudioWidget's play/record/choose buttons are built programmatically in source with no setId() call at all or app-owned string (the title falls back to a per-flavor build value). StringWidget's answer EditText is also a bare, id-less &lt;EditText&gt; (confirmed in source).</t>
+        </is>
+      </c>
       <c r="F29" s="411" t="n"/>
       <c r="G29" s="410" t="n"/>
       <c r="H29" s="410" t="inlineStr">
@@ -19003,7 +19211,11 @@
         </is>
       </c>
       <c r="D30" s="399" t="n"/>
-      <c r="E30" s="410" t="n"/>
+      <c r="E30" s="410" t="inlineStr">
+        <is>
+          <t>Video widget position + integer entry alignment: same as Question Types 5 - VideoWidget's play button and IntegerWidget's EditText are both id-less by source.</t>
+        </is>
+      </c>
       <c r="F30" s="410" t="n"/>
       <c r="G30" s="410" t="n"/>
       <c r="H30" s="410" t="inlineStr">
@@ -19041,7 +19253,11 @@
         </is>
       </c>
       <c r="D31" s="399" t="n"/>
-      <c r="E31" s="411" t="n"/>
+      <c r="E31" s="411" t="inlineStr">
+        <is>
+          <t>General appearance-attribute sweep across remaining questions: combines The claim is text alignment/gravity WITHIN a single widget (e.g. a TextView's own text starting from its right edge) - Maestro's position selectors (leftOf/rightOf/above/below) only compare the bounding boxes of two DISTINCT elements, not a property of one element's internal rendering. There is no Maestro primitive for intra-widget text alignment, so this can't be asserted regardless of effort. with The controls involved get their ids assigned at RUNTIME (e.g. SelectOneWidget/SelectMultiWidget hash the question's form index into the RadioButton/CheckBox id, EntityView generates case-list cell ids via AndroidUtil.generateViewId()) - these are not fixed R.id.* constants and differ every run, so there is nothing stable to select even if the layout-position claim were otherwise checkable.</t>
+        </is>
+      </c>
       <c r="F31" s="411" t="n"/>
       <c r="G31" s="410" t="n"/>
       <c r="H31" s="410" t="inlineStr">
@@ -19135,7 +19351,11 @@
         </is>
       </c>
       <c r="D34" s="399" t="n"/>
-      <c r="E34" s="410" t="n"/>
+      <c r="E34" s="410" t="inlineStr">
+        <is>
+          <t>Case-list column order (Reason/Age/Name): The controls involved get their ids assigned at RUNTIME (e.g. SelectOneWidget/SelectMultiWidget hash the question's form index into the RadioButton/CheckBox id, EntityView generates case-list cell ids via AndroidUtil.generateViewId()) - these are not fixed R.id.* constants and differ every run, so there is nothing stable to select even if the layout-position claim were otherwise checkable. Column order itself is driven by this HQ app's own Detail/case-list configuration, not by anything in the commcare-android client source, so there's no source-derivable order to assert against either.</t>
+        </is>
+      </c>
       <c r="F34" s="410" t="n"/>
       <c r="G34" s="410" t="n"/>
       <c r="H34" s="410" t="inlineStr">
@@ -19170,7 +19390,11 @@
         </is>
       </c>
       <c r="D35" s="399" t="n"/>
-      <c r="E35" s="410" t="n"/>
+      <c r="E35" s="410" t="inlineStr">
+        <is>
+          <t>Case-list text alignment in columns: combines the column-id gap above (row 34) with The claim is text alignment/gravity WITHIN a single widget (e.g. a TextView's own text starting from its right edge) - Maestro's position selectors (leftOf/rightOf/above/below) only compare the bounding boxes of two DISTINCT elements, not a property of one element's internal rendering. There is no Maestro primitive for intra-widget text alignment, so this can't be asserted regardless of effort.</t>
+        </is>
+      </c>
       <c r="F35" s="410" t="n"/>
       <c r="G35" s="410" t="n"/>
       <c r="H35" s="410" t="inlineStr">
@@ -19207,7 +19431,11 @@
         </is>
       </c>
       <c r="D36" s="399" t="n"/>
-      <c r="E36" s="410" t="n"/>
+      <c r="E36" s="410" t="inlineStr">
+        <is>
+          <t>Registration button text-alignment + arrow direction: the CHEVRON's mirrored position (icon_chevron_right_attnpos, which does carry a real rotationY RTL-mirror flag in source) is a genuine, checkable element-to-element position claim - but the button LABEL's own alignment is The claim is text alignment/gravity WITHIN a single widget (e.g. a TextView's own text starting from its right edge) - Maestro's position selectors (leftOf/rightOf/above/below) only compare the bounding boxes of two DISTINCT elements, not a property of one element's internal rendering. There is no Maestro primitive for intra-widget text alignment, so this can't be asserted regardless of effort. Not attempted this round given the mixed feasibility and this app's own confirmed Arabic-translation risk for the label text (EntityActionViewUtils displays app-config text, not a hardcoded string, so its real rendered value/language isn't known without live HQ inspection).</t>
+        </is>
+      </c>
       <c r="F36" s="410" t="n"/>
       <c r="G36" s="410" t="n"/>
       <c r="H36" s="410" t="inlineStr">
@@ -19262,7 +19490,11 @@
         </is>
       </c>
       <c r="D38" s="399" t="n"/>
-      <c r="E38" s="410" t="n"/>
+      <c r="E38" s="410" t="inlineStr">
+        <is>
+          <t>Popup text alignment and progress-bar fill direction: The claim is text alignment/gravity WITHIN a single widget (e.g. a TextView's own text starting from its right edge) - Maestro's position selectors (leftOf/rightOf/above/below) only compare the bounding boxes of two DISTINCT elements, not a property of one element's internal rendering. There is no Maestro primitive for intra-widget text alignment, so this can't be asserted regardless of effort. / The claim is an animation/rendering DIRECTION (progress bar fill direction, spinner rotation direction) sampled over time - Maestro has no angular-rotation or fill-direction assertion primitive at all, independent of whether the element has a stable id. The sync spinner's counterclockwise-rotation claim specifically has no Maestro assertion primitive at all (angular rotation direction), regardless of selector availability - a hard tool-capability ceiling, not a research gap.</t>
+        </is>
+      </c>
       <c r="F38" s="410" t="n"/>
       <c r="G38" s="410" t="n"/>
       <c r="H38" s="410" t="inlineStr">
@@ -21389,7 +21621,11 @@
         <v/>
       </c>
       <c r="D8" s="487" t="n"/>
-      <c r="E8" s="487" t="n"/>
+      <c r="E8" s="487" t="inlineStr">
+        <is>
+          <t>update_app_flow.yaml (this row's old reference) was split 2026-08-10 into these two self-contained files, each installing Test One/Two independently. Still Partial because releasing Test Three needs the registry-driven resolve_app_codes step (automatic, not a manual HQ click).</t>
+        </is>
+      </c>
       <c r="F8" s="445" t="n"/>
       <c r="H8" s="0" t="inlineStr">
         <is>
@@ -21403,7 +21639,7 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/update_app_flow.yaml</t>
+          <t>flows/recovery_measures/update_app_01_normal_update_to_two.yaml + update_app_02_forced_two_to_three.yaml</t>
         </is>
       </c>
     </row>
@@ -21427,7 +21663,11 @@
         </is>
       </c>
       <c r="D9" s="487" t="n"/>
-      <c r="E9" s="445" t="n"/>
+      <c r="E9" s="445" t="inlineStr">
+        <is>
+          <t>File split 2026-08-10 (was reinstall_update_app_flow.yaml). Confirmed passing.</t>
+        </is>
+      </c>
       <c r="F9" s="445" t="n"/>
       <c r="H9" s="0" t="inlineStr">
         <is>
@@ -21441,7 +21681,7 @@
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/reinstall_update_app_flow.yaml</t>
+          <t>flows/recovery_measures/reinstall_update_01_no_trigger_on_one.yaml</t>
         </is>
       </c>
     </row>
@@ -21462,7 +21702,11 @@
         <v/>
       </c>
       <c r="D10" s="487" t="n"/>
-      <c r="E10" s="445" t="n"/>
+      <c r="E10" s="445" t="inlineStr">
+        <is>
+          <t>The hq_setup JSON referenced here is a legacy manual-provisioning stub - releasing this build is now automatic (scripts/hq_client.py's resolve_app_codes() releases whatever install code a flow references, no manual HQ step needed).</t>
+        </is>
+      </c>
       <c r="F10" s="445" t="n"/>
       <c r="H10" s="0" t="inlineStr">
         <is>
@@ -21476,7 +21720,7 @@
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t>hq_setup/recovery_measures/reinstall_update_2_mark_test_two.json</t>
+          <t>(automatic - see reinstall_update_03_update_to_test_two.yaml's APP_CODE_RU_TEST_TWO reference)</t>
         </is>
       </c>
     </row>
@@ -21498,7 +21742,11 @@
         </is>
       </c>
       <c r="D11" s="487" t="n"/>
-      <c r="E11" s="445" t="n"/>
+      <c r="E11" s="445" t="inlineStr">
+        <is>
+          <t>Tagged recovery_phase1 - must run with Test Three unreleased (hq_setup/recovery_measures/phase1_unrelease_test_three.json), else CommCareHQ's update-check jumps straight to Test Three, skipping Two (confirmed live). Confirmed passing 2026-08-10 with corrected EXPECTED_VERSION=160 (the real HQ build number - the sheet's own 'Version 2' narrative number doesn't match what's actually shown on-device).</t>
+        </is>
+      </c>
       <c r="F11" s="445" t="n"/>
       <c r="H11" s="0" t="inlineStr">
         <is>
@@ -21533,7 +21781,11 @@
         <v/>
       </c>
       <c r="D12" s="487" t="n"/>
-      <c r="E12" s="445" t="n"/>
+      <c r="E12" s="445" t="inlineStr">
+        <is>
+          <t>The hq_setup JSON referenced here is a legacy manual-provisioning stub - releasing this build is now automatic (scripts/hq_client.py's resolve_app_codes() releases whatever install code a flow references, no manual HQ step needed).</t>
+        </is>
+      </c>
       <c r="F12" s="445" t="n"/>
       <c r="H12" s="0" t="inlineStr">
         <is>
@@ -21547,7 +21799,7 @@
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t>hq_setup/recovery_measures/reinstall_update_4_mark_test_three.json</t>
+          <t>(automatic - see update_app_02_forced_two_to_three.yaml's APP_CODE_RU_TEST_THREE reference)</t>
         </is>
       </c>
     </row>
@@ -21574,11 +21826,15 @@
         </is>
       </c>
       <c r="D13" s="487" t="n"/>
-      <c r="E13" s="445" t="n"/>
+      <c r="E13" s="445" t="inlineStr">
+        <is>
+          <t>File split 2026-08-10 (was reinstall_update_app_flow.yaml). Downgraded from Automatable: Confirmed live 2026-08-10: the 'Choose Reinstall Method' chooser appears correctly, but completing a CCZ reinstall needs a real .ccz file on-device via the system file picker (SAF) - this repo has no adb-push/file-provisioning mechanism yet (same category of gap as Recovery (offline) 5/6/8 below). Confirmed failing at 'Please select a CCZ file to begin'.</t>
+        </is>
+      </c>
       <c r="F13" s="445" t="n"/>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I13" s="672" t="inlineStr">
@@ -21588,7 +21844,7 @@
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/reinstall_update_app_flow.yaml</t>
+          <t>flows/recovery_measures/reinstall_update_05_06_chooser_and_ccz.yaml</t>
         </is>
       </c>
     </row>
@@ -21611,11 +21867,15 @@
         </is>
       </c>
       <c r="D14" s="487" t="n"/>
-      <c r="E14" s="445" t="n"/>
+      <c r="E14" s="445" t="inlineStr">
+        <is>
+          <t>Same file/gap as 'Reinstall and update 5' above - blocked on CCZ file provisioning, not yet done.</t>
+        </is>
+      </c>
       <c r="F14" s="445" t="n"/>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I14" s="672" t="inlineStr">
@@ -21625,7 +21885,7 @@
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/reinstall_update_app_flow.yaml</t>
+          <t>flows/recovery_measures/reinstall_update_05_06_chooser_and_ccz.yaml</t>
         </is>
       </c>
     </row>
@@ -21650,11 +21910,15 @@
         </is>
       </c>
       <c r="D15" s="487" t="n"/>
-      <c r="E15" s="445" t="n"/>
+      <c r="E15" s="445" t="inlineStr">
+        <is>
+          <t>Confirmed live 2026-08-10 (phase2 run): this file's own login-&gt;logout preamble fails because the forced 'Choose Reinstall Method' screen intercepts before the home screen (with the Logout tile) is ever reached - same root cause discovered for the offline app family (see Recovery (offline) 3 below). Not yet fixed here.</t>
+        </is>
+      </c>
       <c r="F15" s="445" t="n"/>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I15" s="672" t="inlineStr">
@@ -21688,11 +21952,15 @@
         </is>
       </c>
       <c r="D16" s="487" t="n"/>
-      <c r="E16" s="445" t="n"/>
+      <c r="E16" s="445" t="inlineStr">
+        <is>
+          <t>Same file as row above - unreached, blocked by that file's own preamble failing first.</t>
+        </is>
+      </c>
       <c r="F16" s="445" t="n"/>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I16" s="672" t="inlineStr">
@@ -21727,11 +21995,15 @@
         </is>
       </c>
       <c r="D17" s="487" t="n"/>
-      <c r="E17" s="445" t="n"/>
+      <c r="E17" s="445" t="inlineStr">
+        <is>
+          <t>Same file - unreached, blocked by the preamble failure above.</t>
+        </is>
+      </c>
       <c r="F17" s="445" t="n"/>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I17" s="672" t="inlineStr">
@@ -21765,11 +22037,15 @@
         </is>
       </c>
       <c r="D18" s="487" t="n"/>
-      <c r="E18" s="445" t="n"/>
+      <c r="E18" s="445" t="inlineStr">
+        <is>
+          <t>Same file - unreached, blocked by the preamble failure above.</t>
+        </is>
+      </c>
       <c r="F18" s="445" t="n"/>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I18" s="672" t="inlineStr">
@@ -21870,7 +22146,11 @@
         </is>
       </c>
       <c r="D22" s="487" t="n"/>
-      <c r="E22" s="445" t="n"/>
+      <c r="E22" s="445" t="inlineStr">
+        <is>
+          <t>File split 2026-08-10 (was update_app_flow.yaml).</t>
+        </is>
+      </c>
       <c r="F22" s="445" t="n"/>
       <c r="H22" s="0" t="inlineStr">
         <is>
@@ -21884,7 +22164,7 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/update_app_flow.yaml</t>
+          <t>flows/recovery_measures/update_app_01_normal_update_to_two.yaml</t>
         </is>
       </c>
     </row>
@@ -21908,7 +22188,11 @@
         </is>
       </c>
       <c r="D23" s="487" t="n"/>
-      <c r="E23" s="445" t="n"/>
+      <c r="E23" s="445" t="inlineStr">
+        <is>
+          <t>Confirmed passing live 2026-08-10 (recovery_phase1 verification, both attempts).</t>
+        </is>
+      </c>
       <c r="F23" s="445" t="n"/>
       <c r="H23" s="0" t="inlineStr">
         <is>
@@ -21922,7 +22206,7 @@
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/update_app_flow.yaml</t>
+          <t>flows/recovery_measures/update_app_01_normal_update_to_two.yaml</t>
         </is>
       </c>
     </row>
@@ -21943,7 +22227,11 @@
         <v/>
       </c>
       <c r="D24" s="487" t="n"/>
-      <c r="E24" s="445" t="n"/>
+      <c r="E24" s="445" t="inlineStr">
+        <is>
+          <t>File split 2026-08-10.</t>
+        </is>
+      </c>
       <c r="F24" s="445" t="n"/>
       <c r="H24" s="0" t="inlineStr">
         <is>
@@ -21957,7 +22245,7 @@
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/update_app_flow.yaml</t>
+          <t>flows/recovery_measures/update_app_01_normal_update_to_two.yaml</t>
         </is>
       </c>
     </row>
@@ -21979,7 +22267,11 @@
         </is>
       </c>
       <c r="D25" s="487" t="n"/>
-      <c r="E25" s="445" t="n"/>
+      <c r="E25" s="445" t="inlineStr">
+        <is>
+          <t>Confirmed passing live 2026-08-10.</t>
+        </is>
+      </c>
       <c r="F25" s="445" t="n"/>
       <c r="H25" s="0" t="inlineStr">
         <is>
@@ -21993,7 +22285,7 @@
       </c>
       <c r="J25" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/update_app_flow.yaml</t>
+          <t>flows/recovery_measures/update_app_01_normal_update_to_two.yaml</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22306,11 @@
         <v/>
       </c>
       <c r="D26" s="487" t="n"/>
-      <c r="E26" s="445" t="n"/>
+      <c r="E26" s="445" t="inlineStr">
+        <is>
+          <t>The hq_setup JSON referenced here is a legacy manual-provisioning stub - releasing this build is now automatic (scripts/hq_client.py's resolve_app_codes() releases whatever install code a flow references, no manual HQ step needed).</t>
+        </is>
+      </c>
       <c r="F26" s="445" t="n"/>
       <c r="H26" s="0" t="inlineStr">
         <is>
@@ -22028,7 +22324,7 @@
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/update_app_flow.yaml</t>
+          <t>flows/recovery_measures/update_app_02_forced_two_to_three.yaml</t>
         </is>
       </c>
     </row>
@@ -22055,11 +22351,15 @@
         </is>
       </c>
       <c r="D27" s="487" t="n"/>
-      <c r="E27" s="445" t="n"/>
+      <c r="E27" s="445" t="inlineStr">
+        <is>
+          <t>Downgraded from Automatable 2026-08-10: Confirmed live 2026-08-10: this app's forced measure is the REINSTALL-AND-UPDATE chooser type ('Choose Reinstall Method'), not the plain dialog-less auto-update type this row's own narrative describes. The flow's assertions were built for the wrong measure type and don't match live behavior. Needs confirmation from whoever configured this app's Django MobileRecoveryMeasure record about which measure type is really intended here - this account lacks Django-admin access to check directly.</t>
+        </is>
+      </c>
       <c r="F27" s="445" t="n"/>
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I27" s="672" t="inlineStr">
@@ -22069,7 +22369,7 @@
       </c>
       <c r="J27" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/update_app_flow.yaml</t>
+          <t>flows/recovery_measures/update_app_02_forced_two_to_three.yaml</t>
         </is>
       </c>
     </row>
@@ -22093,11 +22393,15 @@
         </is>
       </c>
       <c r="D28" s="487" t="n"/>
-      <c r="E28" s="445" t="n"/>
+      <c r="E28" s="445" t="inlineStr">
+        <is>
+          <t>Unreached - blocked by the measure-type mismatch on the row above.</t>
+        </is>
+      </c>
       <c r="F28" s="445" t="n"/>
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I28" s="672" t="inlineStr">
@@ -22107,7 +22411,7 @@
       </c>
       <c r="J28" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/update_app_flow.yaml</t>
+          <t>flows/recovery_measures/update_app_02_forced_two_to_three.yaml</t>
         </is>
       </c>
     </row>
@@ -22236,23 +22540,23 @@
         </is>
       </c>
       <c r="D33" s="487" t="n"/>
-      <c r="E33" s="445" t="n"/>
+      <c r="E33" s="445" t="inlineStr">
+        <is>
+          <t>Confirmed live 2026-08-10: this negative check's own premise is false - the forced recovery screen appears IMMEDIATELY on a fresh Test One login (before any update check), so there is no 'not yet triggered' state to verify. Removed from offline_reinstall_update_app_flow.yaml accordingly.</t>
+        </is>
+      </c>
       <c r="F33" s="445" t="n"/>
       <c r="H33" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="I33" s="672" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J33" s="0" t="inlineStr">
-        <is>
-          <t>flows/recovery_measures/offline_reinstall_update_app_flow.yaml</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="445" t="inlineStr">
@@ -22271,7 +22575,11 @@
         <v/>
       </c>
       <c r="D34" s="487" t="n"/>
-      <c r="E34" s="445" t="n"/>
+      <c r="E34" s="445" t="inlineStr">
+        <is>
+          <t>The hq_setup JSON referenced here is a legacy manual-provisioning stub - releasing this build is now automatic (scripts/hq_client.py's resolve_app_codes() releases whatever install code a flow references, no manual HQ step needed).</t>
+        </is>
+      </c>
       <c r="F34" s="445" t="n"/>
       <c r="H34" s="0" t="inlineStr">
         <is>
@@ -22285,7 +22593,7 @@
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t>hq_setup/recovery_measures/offline_2_mark_test_two.json</t>
+          <t>(automatic - see offline_09_uninstall_reinstall_test_two.yaml's APP_CODE_OFFLINE_TEST_THREE reference)</t>
         </is>
       </c>
     </row>
@@ -22307,23 +22615,23 @@
         </is>
       </c>
       <c r="D35" s="487" t="n"/>
-      <c r="E35" s="445" t="n"/>
+      <c r="E35" s="445" t="inlineStr">
+        <is>
+          <t>Confirmed live 2026-08-10: unreachable - the forced recovery screen intercepts login before the home screen's 'Update App' menu is ever available. Step removed from offline_reinstall_update_app_flow.yaml.</t>
+        </is>
+      </c>
       <c r="F35" s="445" t="n"/>
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="I35" s="672" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J35" s="0" t="inlineStr">
-        <is>
-          <t>flows/recovery_measures/offline_reinstall_update_app_flow.yaml</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J35" s="0" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="445" t="inlineStr">
@@ -22342,7 +22650,11 @@
         <v/>
       </c>
       <c r="D36" s="487" t="n"/>
-      <c r="E36" s="445" t="n"/>
+      <c r="E36" s="445" t="inlineStr">
+        <is>
+          <t>The hq_setup JSON referenced here is a legacy manual-provisioning stub - releasing this build is now automatic (scripts/hq_client.py's resolve_app_codes() releases whatever install code a flow references, no manual HQ step needed).</t>
+        </is>
+      </c>
       <c r="F36" s="445" t="n"/>
       <c r="H36" s="0" t="inlineStr">
         <is>
@@ -22356,7 +22668,7 @@
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t>hq_setup/recovery_measures/offline_4_mark_test_three.json</t>
+          <t>(automatic - see offline_09_uninstall_reinstall_test_two.yaml's APP_CODE_OFFLINE_TEST_THREE reference)</t>
         </is>
       </c>
     </row>
@@ -22379,7 +22691,11 @@
         </is>
       </c>
       <c r="D37" s="487" t="n"/>
-      <c r="E37" s="445" t="n"/>
+      <c r="E37" s="445" t="inlineStr">
+        <is>
+          <t>Confirmed passing live 2026-08-10 after fix (asserts the forced 'Select CCZ' screen appears immediately on login, rather than attempting an unreachable logout). The adb-push prerequisite itself (placing a .ccz at a custom device path) remains a real, undone gap - no adb/file-push mechanism exists in this repo yet.</t>
+        </is>
+      </c>
       <c r="F37" s="445" t="n"/>
       <c r="H37" s="0" t="inlineStr">
         <is>
@@ -22420,7 +22736,11 @@
         </is>
       </c>
       <c r="D38" s="487" t="n"/>
-      <c r="E38" s="445" t="n"/>
+      <c r="E38" s="445" t="inlineStr">
+        <is>
+          <t>Confirmed live 2026-08-10: correctly reaches 'Select CCZ' immediately (forced-screen timing fixed), but fails at the file-picker step since no .ccz file has actually been pushed to the custom path (row 37's own undone prerequisite).</t>
+        </is>
+      </c>
       <c r="F38" s="445" t="n"/>
       <c r="H38" s="0" t="inlineStr">
         <is>
@@ -22458,11 +22778,15 @@
         </is>
       </c>
       <c r="D39" s="487" t="n"/>
-      <c r="E39" s="445" t="n"/>
+      <c r="E39" s="445" t="inlineStr">
+        <is>
+          <t>Unreached - blocked by the same undone CCZ-file-provisioning prerequisite as rows 37/38.</t>
+        </is>
+      </c>
       <c r="F39" s="445" t="n"/>
       <c r="H39" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I39" s="672" t="inlineStr">
@@ -22494,7 +22818,11 @@
         </is>
       </c>
       <c r="D40" s="487" t="n"/>
-      <c r="E40" s="445" t="n"/>
+      <c r="E40" s="445" t="inlineStr">
+        <is>
+          <t>Same gap as row 38 (Downloads-path variant) - fails at the file-picker step since no .ccz file has been placed in Downloads.</t>
+        </is>
+      </c>
       <c r="F40" s="445" t="n"/>
       <c r="H40" s="0" t="inlineStr">
         <is>
@@ -22530,7 +22858,11 @@
         <v/>
       </c>
       <c r="D41" s="487" t="n"/>
-      <c r="E41" s="445" t="n"/>
+      <c r="E41" s="445" t="inlineStr">
+        <is>
+          <t>Confirmed STILL FAILING live 2026-08-10 even after fixes: reinstalling as Test Two and logging in does NOT trigger the forced screen even with Test Three confirmed released via resolve_app_codes - contradicts the release-status-driven model that holds for the sibling rows in this family. Root cause not yet determined; likely needs Django-admin-level inspection of this app's actual MobileRecoveryMeasure configuration, which this test account cannot access (lacks is_staff/superuser).</t>
+        </is>
+      </c>
       <c r="F41" s="445" t="n"/>
       <c r="H41" s="0" t="inlineStr">
         <is>
@@ -22544,7 +22876,7 @@
       </c>
       <c r="J41" s="0" t="inlineStr">
         <is>
-          <t>hq_setup/recovery_measures/offline_9_mark_test_three.json + flows/recovery_measures/offline_09_uninstall_reinstall_test_two.yaml</t>
+          <t>flows/recovery_measures/offline_09_uninstall_reinstall_test_two.yaml</t>
         </is>
       </c>
     </row>
@@ -22573,7 +22905,7 @@
       <c r="D42" s="487" t="n"/>
       <c r="E42" s="466" t="inlineStr">
         <is>
-          <t>QA-3847</t>
+          <t>Confirmed live 2026-08-10: the forced trigger itself fires correctly and immediately on login. Downstream completion (the actual CCZ install) is blocked by the undone file-provisioning gap - see row 37.</t>
         </is>
       </c>
       <c r="F42" s="487" t="inlineStr">
@@ -22617,11 +22949,15 @@
         </is>
       </c>
       <c r="D43" s="487" t="n"/>
-      <c r="E43" s="445" t="n"/>
+      <c r="E43" s="445" t="inlineStr">
+        <is>
+          <t>Unreached - blocked by the same file-provisioning gap as row 37.</t>
+        </is>
+      </c>
       <c r="F43" s="445" t="n"/>
       <c r="H43" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I43" s="672" t="inlineStr">
@@ -22785,11 +23121,15 @@
         </is>
       </c>
       <c r="D48" s="487" t="n"/>
-      <c r="E48" s="445" t="n"/>
+      <c r="E48" s="445" t="inlineStr">
+        <is>
+          <t>Flow exists and runs, but cannot verify the real precondition - a CommCare CLIENT APK version swap (2.45 -&gt; newer) mid-Maestro-session, which BrowserStack's Maestro product has no mechanism for (checked live via BrowserStack's own API/docs). Consistently fails at the 'reinstall/update required' assertion since the client never actually starts on the old build. Genuine, permanent automation ceiling, not a flow bug.</t>
+        </is>
+      </c>
       <c r="F48" s="445" t="n"/>
       <c r="H48" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I48" s="672" t="inlineStr">
@@ -22820,11 +23160,15 @@
         <v/>
       </c>
       <c r="D49" s="487" t="n"/>
-      <c r="E49" s="445" t="n"/>
+      <c r="E49" s="445" t="inlineStr">
+        <is>
+          <t>Unreached - same client-swap limitation as row above.</t>
+        </is>
+      </c>
       <c r="F49" s="445" t="n"/>
       <c r="H49" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I49" s="672" t="inlineStr">
@@ -22857,11 +23201,15 @@
         </is>
       </c>
       <c r="D50" s="487" t="n"/>
-      <c r="E50" s="445" t="n"/>
+      <c r="E50" s="445" t="inlineStr">
+        <is>
+          <t>Unreached - same client-swap limitation.</t>
+        </is>
+      </c>
       <c r="F50" s="445" t="n"/>
       <c r="H50" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I50" s="672" t="inlineStr">
@@ -23025,11 +23373,15 @@
         </is>
       </c>
       <c r="D55" s="487" t="n"/>
-      <c r="E55" s="445" t="n"/>
+      <c r="E55" s="445" t="inlineStr">
+        <is>
+          <t>Flow exists and runs, but cannot verify the real precondition - a CommCare CLIENT APK version swap (2.45 -&gt; newer) mid-Maestro-session, which BrowserStack's Maestro product has no mechanism for (checked live via BrowserStack's own API/docs). Consistently fails at the 'reinstall/update required' assertion since the client never actually starts on the old build. Genuine, permanent automation ceiling, not a flow bug.</t>
+        </is>
+      </c>
       <c r="F55" s="445" t="n"/>
       <c r="H55" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I55" s="672" t="inlineStr">
@@ -23061,11 +23413,15 @@
         </is>
       </c>
       <c r="D56" s="487" t="n"/>
-      <c r="E56" s="445" t="n"/>
+      <c r="E56" s="445" t="inlineStr">
+        <is>
+          <t>Unreached - same client-swap limitation as row above.</t>
+        </is>
+      </c>
       <c r="F56" s="445" t="n"/>
       <c r="H56" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I56" s="672" t="inlineStr">
@@ -23098,11 +23454,15 @@
         </is>
       </c>
       <c r="D57" s="487" t="n"/>
-      <c r="E57" s="445" t="n"/>
+      <c r="E57" s="445" t="inlineStr">
+        <is>
+          <t>Unreached - same client-swap limitation.</t>
+        </is>
+      </c>
       <c r="F57" s="445" t="n"/>
       <c r="H57" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I57" s="672" t="inlineStr">
@@ -23136,7 +23496,11 @@
         </is>
       </c>
       <c r="D58" s="487" t="n"/>
-      <c r="E58" s="445" t="n"/>
+      <c r="E58" s="445" t="inlineStr">
+        <is>
+          <t>Not re-verified this session - file untouched since prior work.</t>
+        </is>
+      </c>
       <c r="F58" s="445" t="n"/>
       <c r="H58" s="0" t="inlineStr">
         <is>
@@ -23175,7 +23539,11 @@
         </is>
       </c>
       <c r="D59" s="487" t="n"/>
-      <c r="E59" s="445" t="n"/>
+      <c r="E59" s="445" t="inlineStr">
+        <is>
+          <t>Rebuilt 2026-08-10 to install Test Two directly (self-contained) instead of reaching it via a since-removed normal-update step; tagged recovery_phase2. Reaches a forced screen, but confirmed live it's the 'Choose Reinstall Method' chooser (see row 27's measure-type note), not the plain recovery+retry-button screen this row's own narrative describes - needs rework once the correct measure type is confirmed.</t>
+        </is>
+      </c>
       <c r="F59" s="445" t="n"/>
       <c r="H59" s="0" t="inlineStr">
         <is>
@@ -23279,7 +23647,11 @@
         </is>
       </c>
       <c r="D62" s="487" t="n"/>
-      <c r="E62" s="445" t="n"/>
+      <c r="E62" s="445" t="inlineStr">
+        <is>
+          <t>Blocked - needs CommCare CLIENT APK v2.49.4 specifically; only v2.45 has been supplied to this repo (resources/commcare_2.45_release.apk).</t>
+        </is>
+      </c>
       <c r="F62" s="445" t="n"/>
       <c r="H62" s="0" t="inlineStr">
         <is>
@@ -23317,7 +23689,11 @@
         </is>
       </c>
       <c r="D63" s="487" t="n"/>
-      <c r="E63" s="445" t="n"/>
+      <c r="E63" s="445" t="inlineStr">
+        <is>
+          <t>Blocked - needs CommCare CLIENT APK v2.49.5 specifically; only v2.45 has been supplied to this repo.</t>
+        </is>
+      </c>
       <c r="F63" s="445" t="n"/>
       <c r="H63" s="0" t="inlineStr">
         <is>
@@ -23355,7 +23731,11 @@
         </is>
       </c>
       <c r="D64" s="487" t="n"/>
-      <c r="E64" s="445" t="n"/>
+      <c r="E64" s="445" t="inlineStr">
+        <is>
+          <t>Confirmed passing live 2026-08-10 (twice, in separate runs).</t>
+        </is>
+      </c>
       <c r="F64" s="445" t="n"/>
       <c r="H64" s="0" t="inlineStr">
         <is>
@@ -23456,7 +23836,11 @@
         </is>
       </c>
       <c r="D67" s="487" t="n"/>
-      <c r="E67" s="445" t="n"/>
+      <c r="E67" s="445" t="inlineStr">
+        <is>
+          <t>Confirmed passing live 2026-08-10.</t>
+        </is>
+      </c>
       <c r="F67" s="445" t="n"/>
       <c r="H67" s="0" t="inlineStr">
         <is>
@@ -23496,7 +23880,11 @@
         </is>
       </c>
       <c r="D68" s="487" t="n"/>
-      <c r="E68" s="445" t="n"/>
+      <c r="E68" s="445" t="inlineStr">
+        <is>
+          <t>Step 3 requires waiting a full hour mid-test ('Wait one hour and Logout') - impractical for a CI/BrowserStack session (cost and time-limit reasons). Not a Maestro technical limitation, just an operationally prohibitive wait.</t>
+        </is>
+      </c>
       <c r="F68" s="445" t="n"/>
       <c r="H68" s="0" t="inlineStr">
         <is>
@@ -34854,11 +35242,15 @@
         </is>
       </c>
       <c r="D8" s="137" t="n"/>
-      <c r="E8" s="193" t="n"/>
+      <c r="E8" s="193" t="inlineStr">
+        <is>
+          <t>flows/login/commcare_odk_01_login.yaml - tagged automatable in-repo (not Partial); fully verifies username/password entry, the 'logging in' progress message, and reaching the home screen.</t>
+        </is>
+      </c>
       <c r="F8" s="193" t="n"/>
       <c r="I8" s="140" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
@@ -34892,7 +35284,11 @@
         </is>
       </c>
       <c r="D9" s="137" t="n"/>
-      <c r="E9" s="193" t="n"/>
+      <c r="E9" s="193" t="inlineStr">
+        <is>
+          <t>flows/login/commcare_odk_02_check_session.yaml - verifies the 'Logged Into CommCare / Session Expires:' banner is present after swiping open the notification shade, but does NOT verify the exact 24-hour expiration duration - Maestro has no way to read/compute a live countdown timestamp inside notification text.</t>
+        </is>
+      </c>
       <c r="F9" s="193" t="n"/>
       <c r="G9" s="145" t="n"/>
       <c r="I9" s="140" t="inlineStr">
@@ -34929,13 +35325,17 @@
         </is>
       </c>
       <c r="D10" s="137" t="n"/>
-      <c r="E10" s="149" t="n"/>
+      <c r="E10" s="149" t="inlineStr">
+        <is>
+          <t>flows/login/commcare_odk_03_logout.yaml - tagged automatable in-repo (not Partial); fully verifies logout returns to the login page.</t>
+        </is>
+      </c>
       <c r="F10" s="149" t="n"/>
       <c r="G10" s="151" t="n"/>
       <c r="H10" s="152" t="n"/>
       <c r="I10" s="140" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J10" s="0" t="inlineStr">

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -6834,7 +6834,11 @@
       <c r="D9" s="229" t="n"/>
       <c r="E9" s="564" t="n"/>
       <c r="F9" s="229" t="n"/>
-      <c r="G9" s="229" t="n"/>
+      <c r="G9" s="229" t="inlineStr">
+        <is>
+          <t>hq_setup/mobile_pins/setup_02_install_application.json covers only the HQ half (mark the CCZ app's latest build Released). It does NOT cover Setup 4's barcode-claim step (Not automatable - same camera/cross-surface limitation as Install 1), which must still be done by hand between running this JSON and the on-device Pin flows.</t>
+        </is>
+      </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -7261,7 +7265,11 @@
       <c r="D18" s="229" t="n"/>
       <c r="E18" s="564" t="n"/>
       <c r="F18" s="229" t="n"/>
-      <c r="G18" s="229" t="n"/>
+      <c r="G18" s="229" t="inlineStr">
+        <is>
+          <t>hq_setup/mobile_pins/setup_06_reinstall_application.json - identical HQ action to Setup 2's, just run at a different point (after flows/mobile_pins/setup_05_uninstall_app.yaml's uninstall). Same Setup-4 barcode-claim caveat applies.</t>
+        </is>
+      </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -7808,7 +7816,11 @@
       <c r="D30" s="484" t="n"/>
       <c r="E30" s="564" t="n"/>
       <c r="F30" s="484" t="n"/>
-      <c r="G30" s="484" t="n"/>
+      <c r="G30" s="484" t="inlineStr">
+        <is>
+          <t>hq_setup/mobile_pins/mutiple_app_pin_install_apps.json covers only the HQ half for BOTH apps (Basic Tests + Case Management). Setup 4's barcode-claim step must be done manually twice (once per app) - Not automatable, same camera limitation as Install 1.</t>
+        </is>
+      </c>
       <c r="I30" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -14746,7 +14758,11 @@
         </is>
       </c>
       <c r="D8" s="564" t="n"/>
-      <c r="E8" s="387" t="n"/>
+      <c r="E8" s="387" t="inlineStr">
+        <is>
+          <t>flows/session_expiration/setup_01_install_application.yaml - Partial because it needs a valid HQ web-user email/password to install the Session Expiration Test app by name.</t>
+        </is>
+      </c>
       <c r="F8" s="387" t="n"/>
       <c r="G8" s="216" t="n"/>
       <c r="I8" s="0" t="inlineStr">
@@ -34727,7 +34743,11 @@
         </is>
       </c>
       <c r="D9" s="95" t="n"/>
-      <c r="E9" s="564" t="n"/>
+      <c r="E9" s="564" t="inlineStr">
+        <is>
+          <t>Requires scanning a QR barcode rendered on a live HQ desktop-browser page with the device's own camera - a cross-surface (webpage &lt;-&gt; device camera) interaction BrowserStack's Maestro sessions have no camera-image-injection hook for (same limitation as Mobile Pins' own 'Claim Privileges' barcode-scan step).</t>
+        </is>
+      </c>
       <c r="F9" s="94" t="n"/>
       <c r="G9" s="94" t="n"/>
       <c r="H9" s="106" t="n"/>
@@ -34937,7 +34957,11 @@
           <t>Selected app should be installed</t>
         </is>
       </c>
-      <c r="E13" s="564" t="n"/>
+      <c r="E13" s="564" t="inlineStr">
+        <is>
+          <t>flows/install/install_07_install_as_mobile_user.yaml - Partial because it needs a valid HQ mobile-worker username/domain/password.</t>
+        </is>
+      </c>
       <c r="F13" s="94" t="n"/>
       <c r="G13" s="94" t="n"/>
       <c r="H13" s="106" t="n"/>
@@ -34990,7 +35014,11 @@
           <t>Selected app should be installed</t>
         </is>
       </c>
-      <c r="E14" s="564" t="n"/>
+      <c r="E14" s="564" t="inlineStr">
+        <is>
+          <t>flows/install/install_08_install_as_web_user.yaml - Partial because it needs a valid HQ web-user email/password.</t>
+        </is>
+      </c>
       <c r="F14" s="155" t="n"/>
       <c r="G14" s="155" t="n"/>
       <c r="H14" s="106" t="n"/>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -14284,18 +14284,28 @@
       <c r="D15" s="564" t="n"/>
       <c r="E15" s="497" t="inlineStr">
         <is>
-          <t>Register a Case + answer 2 questions + save/exit has no map/cross-app step - genuinely automatable, just not yet built.</t>
+          <t>Register Case has 2 questions: a name field and a required geopoint (no map-tap fallback). Built 2026-08-11: flows/case_filters/geoservices_01_register_case.yaml / geoservices_02_rate_case.yaml, ground-truthed against resources/qateam - [Master] Basic Tests - v1141.ccz (suite.xml + app_strings.txt + form XML), not guessed. Kept Partial rather than Automatable because Register Case's site_location question is a required geopoint with no appearance="maps" attribute, so it needs a real GPS/network-fusion location fix (up to 60s, no manual-entry fallback) to save at all - genuinely best-effort on a cloud device, not guaranteed, confirmed via commcare-android source (GeoPointWidget.java/GeoPointActivity.java).</t>
         </is>
       </c>
       <c r="F15" s="497" t="n"/>
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J15" s="0" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>flows/case_filters/geoservices_01_register_case.yaml</t>
         </is>
       </c>
     </row>
@@ -14318,18 +14328,28 @@
       <c r="D16" s="564" t="n"/>
       <c r="E16" s="497" t="inlineStr">
         <is>
-          <t>Pure on-device navigation/title check - genuinely automatable, just not yet built.</t>
+          <t>Same file as Case Lists 3 (this is its trailing assertion). Built 2026-08-11: flows/case_filters/geoservices_01_register_case.yaml / geoservices_02_rate_case.yaml, ground-truthed against resources/qateam - [Master] Basic Tests - v1141.ccz (suite.xml + app_strings.txt + form XML), not guessed. Kept Partial rather than Automatable because Register Case's site_location question is a required geopoint with no appearance="maps" attribute, so it needs a real GPS/network-fusion location fix (up to 60s, no manual-entry fallback) to save at all - genuinely best-effort on a cloud device, not guaranteed, confirmed via commcare-android source (GeoPointWidget.java/GeoPointActivity.java).</t>
         </is>
       </c>
       <c r="F16" s="497" t="n"/>
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J16" s="0" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>flows/case_filters/geoservices_01_register_case.yaml</t>
         </is>
       </c>
     </row>
@@ -14356,18 +14376,28 @@
       <c r="D17" s="564" t="n"/>
       <c r="E17" s="497" t="inlineStr">
         <is>
-          <t>Rate Case + save/exit + verify home screen has no map/cross-app step - genuinely automatable, just not yet built.</t>
+          <t>Self-contained: registers its own geo_case first (same geopoint dependency as Case Lists 3), then rates it and verifies return to the home screen (confirmed via suite.xml: Rate Case's entry has no &lt;stack&gt; override back to the Geoservices menu, unlike Register Case's). Built 2026-08-11: flows/case_filters/geoservices_01_register_case.yaml / geoservices_02_rate_case.yaml, ground-truthed against resources/qateam - [Master] Basic Tests - v1141.ccz (suite.xml + app_strings.txt + form XML), not guessed. Kept Partial rather than Automatable because Register Case's site_location question is a required geopoint with no appearance="maps" attribute, so it needs a real GPS/network-fusion location fix (up to 60s, no manual-entry fallback) to save at all - genuinely best-effort on a cloud device, not guaranteed, confirmed via commcare-android source (GeoPointWidget.java/GeoPointActivity.java).</t>
         </is>
       </c>
       <c r="F17" s="497" t="n"/>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t>flows/case_filters/geoservices_02_rate_case.yaml</t>
         </is>
       </c>
     </row>
@@ -14394,18 +14424,28 @@
       <c r="D18" s="564" t="n"/>
       <c r="E18" s="497" t="inlineStr">
         <is>
-          <t>Star-rating/case-detail verification is automatable and not yet built; the 'Show Address' step reuses the same Launches the device's external maps app to pin/view case geodata - a cross-app handoff whose exact app/UI depends on what's installed on the specific test device, not something Maestro/this repo can assert deterministically.</t>
+          <t>PARTIAL: only steps 1-3 automated (star rating shown correctly in both the case list and the case's own detail/confirm screen - confirmed via app_strings.txt that ratings render as literal star characters, e.g. "★★★" for a rating of 3). Steps 4-5 ("Select Show Address" -&gt; external maps app launch + pin verification) are NOT automated - same cross-app/non-deterministic limitation as the map-dependent rows above (Case Lists 1/2). Built 2026-08-11: flows/case_filters/geoservices_01_register_case.yaml / geoservices_02_rate_case.yaml, ground-truthed against resources/qateam - [Master] Basic Tests - v1141.ccz (suite.xml + app_strings.txt + form XML), not guessed. Kept Partial rather than Automatable because Register Case's site_location question is a required geopoint with no appearance="maps" attribute, so it needs a real GPS/network-fusion location fix (up to 60s, no manual-entry fallback) to save at all - genuinely best-effort on a cloud device, not guaranteed, confirmed via commcare-android source (GeoPointWidget.java/GeoPointActivity.java).</t>
         </is>
       </c>
       <c r="F18" s="497" t="n"/>
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J18" s="0" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t>flows/case_filters/geoservices_02_rate_case.yaml</t>
         </is>
       </c>
     </row>
@@ -35861,10 +35901,7 @@
       <c r="D16" s="137" t="n"/>
       <c r="E16" s="154" t="inlineStr">
         <is>
-          <t>These tests correspond with this ticket
-(Note for Test Setup:
-In App settings &gt; Advanced Settings, ensure Auto Update Frequency is set to 'Daily' for the previous version being downloaded and the released version to which it is being updated to.)
-BLOCKED: needs a real Play Store install, which this harness's sideloaded-APK BrowserStack approach cannot perform.</t>
+          <t>Not automated: step 1 requires installing a fresh CommCare APK from the Google Play Store specifically (not this repo's GitHub-releases-based scripts/download_apk.py mechanism) - a genuinely different install path (Play Store account/region/version-availability concerns) this pipeline has no automation for.</t>
         </is>
       </c>
       <c r="F16" s="154" t="n"/>
@@ -36049,7 +36086,7 @@
       <c r="D21" s="596" t="n"/>
       <c r="E21" s="163" t="inlineStr">
         <is>
-          <t>BLOCKED: depends on 'Recheck button 1' having manually put the device in airplane mode first; no scripted network-condition toggle exists in this harness yet.</t>
+          <t>Not automated (deferred, not researched this round): depends on a preceding "Recheck button 1" scenario (airplane-mode-during-update-check, same class of mechanism used in flows/recovery_measures/retry_recovery_02_network_toggle_retry.yaml) against the Update tab's own app ("Update Test Alternate"), which has not yet been identified/verified via live HQ or CCZ inspection - needs that research before a reliable flow can be written.</t>
         </is>
       </c>
       <c r="F21" s="163" t="n"/>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -19994,7 +19994,8 @@
           <t>(For Dimagi)
 1. Ensure all v1 and v2 versions of the app are on 2.45 (or any version &lt; the test version, as long as both are same)
 - No new version creation, targetting the version in test, is required for any of these tests
-2. For finding the referenced version of the app, please look through the comments under a release number, on the release pages linked for a test case</t>
+2. For finding the referenced version of the app, please look through the comments under a release number, on the release pages linked for a test case
+CONFIRMED 2026-08-18 (not just assumed): no Maestro or BrowserStack API installs an app mid-session - Maestro has no installApp command, BrowserStack otherApps only pre-installs at session start. Would need ADB-capable device-farm infrastructure outside BrowserStack App Automate.</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
@@ -20114,7 +20115,11 @@
       </c>
       <c r="E7" s="428" t="n"/>
       <c r="F7" s="428" t="n"/>
-      <c r="G7" s="428" t="n"/>
+      <c r="G7" s="428" t="inlineStr">
+        <is>
+          <t>CONFIRMED 2026-08-18 (not just assumed): no Maestro or BrowserStack API installs an app mid-session - Maestro has no installApp command, BrowserStack otherApps only pre-installs at session start. Would need ADB-capable device-farm infrastructure outside BrowserStack App Automate.</t>
+        </is>
+      </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
@@ -20326,7 +20331,8 @@
       <c r="F12" s="422" t="n"/>
       <c r="G12" s="423" t="inlineStr">
         <is>
-          <t>The version 2 of the app has good amount of changes from Version 1 so that app takes some time to download the updates to allow for CommCare update to happen in this timeframe. (Have added few media files in form 1 in Version 2)</t>
+          <t>The version 2 of the app has good amount of changes from Version 1 so that app takes some time to download the updates to allow for CommCare update to happen in this timeframe. (Have added few media files in form 1 in Version 2)
+CONFIRMED 2026-08-18 (not just assumed): no Maestro or BrowserStack API installs an app mid-session - Maestro has no installApp command, BrowserStack otherApps only pre-installs at session start. Would need ADB-capable device-farm infrastructure outside BrowserStack App Automate.</t>
         </is>
       </c>
       <c r="I12" s="0" t="inlineStr">
@@ -20626,7 +20632,11 @@
       </c>
       <c r="E19" s="428" t="n"/>
       <c r="F19" s="428" t="n"/>
-      <c r="G19" s="428" t="n"/>
+      <c r="G19" s="428" t="inlineStr">
+        <is>
+          <t>Runs a real, automated CCZ-update proxy action - the sheet's own literal "swap the CommCare binary" wording is a harness-level precondition, same confirmed gap as Test Case 1's Setup row (see G7).</t>
+        </is>
+      </c>
       <c r="I19" s="0" t="inlineStr">
         <is>
           <t>Automatable</t>
@@ -21278,7 +21288,11 @@
       </c>
       <c r="E35" s="428" t="n"/>
       <c r="F35" s="428" t="n"/>
-      <c r="G35" s="428" t="n"/>
+      <c r="G35" s="428" t="inlineStr">
+        <is>
+          <t>CONFIRMED 2026-08-18 (not just assumed): no Maestro or BrowserStack API installs an app mid-session - Maestro has no installApp command, BrowserStack otherApps only pre-installs at session start. Would need ADB-capable device-farm infrastructure outside BrowserStack App Automate.</t>
+        </is>
+      </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -11337,12 +11337,16 @@
         </is>
       </c>
       <c r="D66" s="387" t="n"/>
-      <c r="E66" s="387" t="n"/>
+      <c r="E66" s="387" t="inlineStr">
+        <is>
+          <t>Downgraded from Automatable to Partial (2026-08-21, based on the flow file's own header) - confirmed live 2026-08-13 via BrowserStack command logs that the hard assertVisible in flows/multimedia/lazy_video_02_file_missing_popup.yaml failed outright; the file's own tags now read `partial`.</t>
+        </is>
+      </c>
       <c r="F66" s="521" t="n"/>
       <c r="G66" s="60" t="n"/>
       <c r="H66" s="60" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I66" s="709" t="inlineStr">
@@ -14295,12 +14299,12 @@
       </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="J15" s="0" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="K15" s="0" t="inlineStr">
@@ -14339,12 +14343,12 @@
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="J16" s="0" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="K16" s="0" t="inlineStr">
@@ -14387,12 +14391,12 @@
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="J17" s="0" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="K17" s="0" t="inlineStr">
@@ -14435,12 +14439,12 @@
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="J18" s="0" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="K18" s="0" t="inlineStr">
@@ -15777,12 +15781,16 @@
         </is>
       </c>
       <c r="D11" s="564" t="n"/>
-      <c r="E11" s="387" t="n"/>
+      <c r="E11" s="387" t="inlineStr">
+        <is>
+          <t>Confirmed passing via real BrowserStack dispatch (2026-08-21): the Appium orchestrator resolved the genuine gap that made this Partial - a single Maestro build can't run an HQ action mid-build, between this row's own logout and re-login.</t>
+        </is>
+      </c>
       <c r="F11" s="387" t="n"/>
       <c r="G11" s="382" t="n"/>
       <c r="H11" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I11" s="670" t="inlineStr">
@@ -15792,7 +15800,7 @@
       </c>
       <c r="J11" s="0" t="inlineStr">
         <is>
-          <t>hq_setup/prompted_updates/scenario_01_mark_released.json; flows/prompted_updates/scenario_01_optional_ccz_update.yaml</t>
+          <t>scripts/run_appium_prompted_updates_suite.py --scenario scenario_1 (scripts/appium_scenarios.py's run_prompted_update_scenario_1) - the step 5 HQ 'mark latest build Released' action fires programmatically between the flow's own logout and re-login, on the same live session; flows/prompted_updates/scenario_01_optional_ccz_update.yaml + hq_setup/prompted_updates/scenario_01_mark_released.json remain as the Maestro-only reference (still Partial standalone, since a plain Maestro build has no mid-build HQ control point).</t>
         </is>
       </c>
     </row>
@@ -15823,12 +15831,16 @@
         </is>
       </c>
       <c r="D12" s="564" t="n"/>
-      <c r="E12" s="387" t="n"/>
+      <c r="E12" s="387" t="inlineStr">
+        <is>
+          <t>Confirmed passing via real BrowserStack dispatch (2026-08-21) - same fix as Scenario 1 (see E11).</t>
+        </is>
+      </c>
       <c r="F12" s="387" t="n"/>
       <c r="G12" s="382" t="n"/>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I12" s="670" t="inlineStr">
@@ -15838,7 +15850,7 @@
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t>hq_setup/prompted_updates/scenario_02_forced.json; flows/prompted_updates/scenario_02_forced_ccz_update.yaml</t>
+          <t>scripts/run_appium_prompted_updates_suite.py --scenario scenario_2 (scripts/appium_scenarios.py's run_prompted_update_scenario_2) - same mid-session HQ action mechanism as Scenario 1; flows/prompted_updates/scenario_02_forced_ccz_update.yaml + hq_setup/prompted_updates/scenario_02_forced.json remain as the Maestro-only reference (still Partial standalone).</t>
         </is>
       </c>
     </row>
@@ -20679,10 +20691,14 @@
       </c>
       <c r="E20" s="428" t="n"/>
       <c r="F20" s="428" t="n"/>
-      <c r="G20" s="428" t="n"/>
+      <c r="G20" s="428" t="inlineStr">
+        <is>
+          <t>Confirmed passing via real BrowserStack dispatch (2026-08-21) - the 'mark Version released' step now happens automatically (pinned to an already-released build via scripts/app_registry.py, resolved by hq_client.py's resolve_app_codes()), no manual HQ click needed.</t>
+        </is>
+      </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J20" s="672" t="inlineStr">
@@ -20722,10 +20738,14 @@
       </c>
       <c r="E21" s="428" t="n"/>
       <c r="F21" s="428" t="n"/>
-      <c r="G21" s="428" t="n"/>
+      <c r="G21" s="428" t="inlineStr">
+        <is>
+          <t>Confirmed passing via real BrowserStack dispatch (2026-08-21) - same automatic release mechanism as Update 9 above (see G20).</t>
+        </is>
+      </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J21" s="672" t="inlineStr">
@@ -21035,10 +21055,14 @@
       </c>
       <c r="E29" s="428" t="n"/>
       <c r="F29" s="426" t="n"/>
-      <c r="G29" s="429" t="n"/>
+      <c r="G29" s="429" t="inlineStr">
+        <is>
+          <t>Confirmed passing via real BrowserStack dispatch (2026-08-21) - same automatic release mechanism as Update 9/10 above (see G20), applied to the linked app's V6 build.</t>
+        </is>
+      </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J29" s="672" t="inlineStr">
@@ -24391,11 +24415,15 @@
         </is>
       </c>
       <c r="D14" s="564" t="n"/>
-      <c r="E14" s="387" t="n"/>
+      <c r="E14" s="387" t="inlineStr">
+        <is>
+          <t>Downgraded from Automatable to Partial (2026-08-21, based on the flow file's own header) - flows/form_submissions/appearance_attributes_page_through_and_submit.yaml was itself downgraded 2026-08-08 after a real BrowserStack failure: the form has a third required image-only question with no stable selector, so full submission is out of scope; the file's own tags now read `partial`.</t>
+        </is>
+      </c>
       <c r="F14" s="204" t="n"/>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -15783,7 +15783,7 @@
       <c r="D11" s="564" t="n"/>
       <c r="E11" s="387" t="inlineStr">
         <is>
-          <t>Confirmed passing via real BrowserStack dispatch (2026-08-21): the Appium orchestrator resolved the genuine gap that made this Partial - a single Maestro build can't run an HQ action mid-build, between this row's own logout and re-login.</t>
+          <t>Confirmed passing via real BrowserStack dispatch (2026-08-21/22): the Appium orchestrator resolved the genuine gap that made this Partial - a single Maestro build can't run an HQ action mid-build, between this row's own logout and re-login. UPDATE (2026-08-22): the plain-Maestro version of this scenario (which could only ever partially work) was deleted - the Appium path is now the sole, canonical coverage, not a supplement.</t>
         </is>
       </c>
       <c r="F11" s="387" t="n"/>
@@ -15800,7 +15800,7 @@
       </c>
       <c r="J11" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_prompted_updates_suite.py --scenario scenario_1 (scripts/appium_scenarios.py's run_prompted_update_scenario_1) - the step 5 HQ 'mark latest build Released' action fires programmatically between the flow's own logout and re-login, on the same live session; flows/prompted_updates/scenario_01_optional_ccz_update.yaml + hq_setup/prompted_updates/scenario_01_mark_released.json remain as the Maestro-only reference (still Partial standalone, since a plain Maestro build has no mid-build HQ control point).</t>
+          <t>scripts/run_appium_prompted_updates_suite.py --scenario scenario_01_optional_ccz_update (scripts/appium_scenarios.py's run_prompted_update_scenario_01_optional_ccz_update) - the step 5 HQ 'mark latest build Released' action fires programmatically between the flow's own logout and re-login, on the same live session.</t>
         </is>
       </c>
     </row>
@@ -15833,7 +15833,7 @@
       <c r="D12" s="564" t="n"/>
       <c r="E12" s="387" t="inlineStr">
         <is>
-          <t>Confirmed passing via real BrowserStack dispatch (2026-08-21) - same fix as Scenario 1 (see E11).</t>
+          <t>Confirmed passing via real BrowserStack dispatch (2026-08-22, after widening the forced-blocker relogin retry from 180s to 360s based on real observed HQ propagation delay) - same fix as Scenario 1 (see E11). Plain-Maestro version deleted for the same reason as Scenario 1.</t>
         </is>
       </c>
       <c r="F12" s="387" t="n"/>
@@ -15850,7 +15850,7 @@
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_prompted_updates_suite.py --scenario scenario_2 (scripts/appium_scenarios.py's run_prompted_update_scenario_2) - same mid-session HQ action mechanism as Scenario 1; flows/prompted_updates/scenario_02_forced_ccz_update.yaml + hq_setup/prompted_updates/scenario_02_forced.json remain as the Maestro-only reference (still Partial standalone).</t>
+          <t>scripts/run_appium_prompted_updates_suite.py --scenario scenario_02_forced_ccz_update (scripts/appium_scenarios.py's run_prompted_update_scenario_02_forced_ccz_update) - same mid-session HQ action mechanism as Scenario 1.</t>
         </is>
       </c>
     </row>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -29304,7 +29304,7 @@
       <c r="D21" s="564" t="n"/>
       <c r="E21" s="539" t="inlineStr">
         <is>
-          <t>Please verify the linked ticket during the actual Release cycle</t>
+          <t>Please verify the linked ticket during the actual Release cycle | Automated as part of a combined scenario with Prompted Update Scenario 2 (this is part 1/2: apk_prompt=on, optional). See flows/updates_2_49/prompted_update_scenario_01_ill_update_later.yaml.</t>
         </is>
       </c>
       <c r="F21" s="543" t="inlineStr">
@@ -29347,7 +29347,11 @@
         </is>
       </c>
       <c r="D22" s="564" t="n"/>
-      <c r="E22" s="539" t="n"/>
+      <c r="E22" s="539" t="inlineStr">
+        <is>
+          <t>Automated as part of a combined scenario with Prompted Update Scenario 1 (this is part 2/2: apk_prompt=forced). OPEN ISSUE (2026-08-24): on-device forced blocker does not appear even with HQ config confirmed correct via a live readback check - the optional prompt (Scenario 1) works correctly with the same dynamically-resolved CommCare version, forced does not trigger any prompt at all. Root cause not yet found.</t>
+        </is>
+      </c>
       <c r="F22" s="204" t="n"/>
       <c r="H22" s="0" t="inlineStr">
         <is>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -21922,13 +21922,13 @@
       <c r="D13" s="487" t="n"/>
       <c r="E13" s="445" t="inlineStr">
         <is>
-          <t>File split 2026-08-10 (was reinstall_update_app_flow.yaml). Downgraded from Automatable: Confirmed live 2026-08-10: the 'Choose Reinstall Method' chooser appears correctly, but completing a CCZ reinstall needs a real .ccz file on-device via the system file picker (SAF) - this repo has no adb-push/file-provisioning mechanism yet (same category of gap as Recovery (offline) 5/6/8 below). Confirmed failing at 'Please select a CCZ file to begin'.</t>
+          <t>File split 2026-08-10 (was reinstall_update_app_flow.yaml). UPDATE (2026-08-26): fixed via a new Appium-based module - scripts/appium_offline_ccz_scenarios.py + scripts/run_appium_offline_ccz_suite.py, which pushes a real .ccz file onto the device via BrowserStack's Appium push_file (confirmed live: Maestro itself has no file-push mechanism, so the original .yaml flow for this row is now tagged superseded_by_appium and excluded from normal dispatch, kept on disk for reference only). Confirmed passing live in CI (2026-08-26, run 32936440687).</t>
         </is>
       </c>
       <c r="F13" s="445" t="n"/>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I13" s="672" t="inlineStr">
@@ -21938,7 +21938,7 @@
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/reinstall_update_05_06_chooser_and_ccz.yaml</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario reinstall_05_06 (reinstall_update_05_06_chooser_and_ccz.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>
@@ -21963,13 +21963,13 @@
       <c r="D14" s="487" t="n"/>
       <c r="E14" s="445" t="inlineStr">
         <is>
-          <t>Same file/gap as 'Reinstall and update 5' above - blocked on CCZ file provisioning, not yet done.</t>
+          <t>Same file/gap as 'Reinstall and update 5' above. UPDATE (2026-08-26): fixed via a new Appium-based module - scripts/appium_offline_ccz_scenarios.py + scripts/run_appium_offline_ccz_suite.py, which pushes a real .ccz file onto the device via BrowserStack's Appium push_file (confirmed live: Maestro itself has no file-push mechanism, so the original .yaml flow for this row is now tagged superseded_by_appium and excluded from normal dispatch, kept on disk for reference only). Confirmed passing live in CI (2026-08-26, run 32936440687).</t>
         </is>
       </c>
       <c r="F14" s="445" t="n"/>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I14" s="672" t="inlineStr">
@@ -21979,7 +21979,7 @@
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/reinstall_update_05_06_chooser_and_ccz.yaml</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario reinstall_05_06 (reinstall_update_05_06_chooser_and_ccz.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>
@@ -22596,11 +22596,15 @@
         </is>
       </c>
       <c r="D32" s="487" t="n"/>
-      <c r="E32" s="445" t="n"/>
+      <c r="E32" s="445" t="inlineStr">
+        <is>
+          <t>Install app by code, confirmed passing. UPDATE (2026-08-26): fixed via a new Appium-based module - scripts/appium_offline_ccz_scenarios.py + scripts/run_appium_offline_ccz_suite.py, which pushes a real .ccz file onto the device via BrowserStack's Appium push_file (confirmed live: Maestro itself has no file-push mechanism, so the original .yaml flow for this row is now tagged superseded_by_appium and excluded from normal dispatch, kept on disk for reference only). Confirmed passing live in CI (2026-08-26, run 32936440687).</t>
+        </is>
+      </c>
       <c r="F32" s="445" t="n"/>
       <c r="H32" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I32" s="672" t="inlineStr">
@@ -22610,7 +22614,7 @@
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/offline_reinstall_update_app_flow.yaml</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_reinstall_update (offline_reinstall_update_app_flow.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>
@@ -22832,13 +22836,13 @@
       <c r="D38" s="487" t="n"/>
       <c r="E38" s="445" t="inlineStr">
         <is>
-          <t>Confirmed live 2026-08-10: correctly reaches 'Select CCZ' immediately (forced-screen timing fixed), but fails at the file-picker step since no .ccz file has actually been pushed to the custom path (row 37's own undone prerequisite).</t>
+          <t>Confirmed live 2026-08-10: correctly reaches 'Select CCZ' immediately (forced-screen timing fixed). UPDATE (2026-08-26): fixed via a new Appium-based module - scripts/appium_offline_ccz_scenarios.py + scripts/run_appium_offline_ccz_suite.py, which pushes a real .ccz file onto the device via BrowserStack's Appium push_file (confirmed live: Maestro itself has no file-push mechanism, so the original .yaml flow for this row is now tagged superseded_by_appium and excluded from normal dispatch, kept on disk for reference only). Confirmed passing live in CI (2026-08-26, run 32936440687).</t>
         </is>
       </c>
       <c r="F38" s="445" t="n"/>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I38" s="672" t="inlineStr">
@@ -22848,7 +22852,7 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/offline_06_select_ccz_via_picker.yaml</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_06 (offline_06_select_ccz_via_picker.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>
@@ -22914,13 +22918,13 @@
       <c r="D40" s="487" t="n"/>
       <c r="E40" s="445" t="inlineStr">
         <is>
-          <t>Same gap as row 38 (Downloads-path variant) - fails at the file-picker step since no .ccz file has been placed in Downloads.</t>
+          <t>Same forced-screen family as row 38. UPDATE (2026-08-26): fixed via a new Appium-based module - scripts/appium_offline_ccz_scenarios.py + scripts/run_appium_offline_ccz_suite.py, which pushes a real .ccz file onto the device via BrowserStack's Appium push_file (confirmed live: Maestro itself has no file-push mechanism, so the original .yaml flow for this row is now tagged superseded_by_appium and excluded from normal dispatch, kept on disk for reference only). Confirmed passing live in CI (2026-08-26, run 32936440687).</t>
         </is>
       </c>
       <c r="F40" s="445" t="n"/>
       <c r="H40" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I40" s="672" t="inlineStr">
@@ -22930,7 +22934,7 @@
       </c>
       <c r="J40" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/offline_08_move_ccz_to_downloads.yaml</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_08 (offline_08_move_ccz_to_downloads.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>
@@ -22999,7 +23003,7 @@
       <c r="D42" s="487" t="n"/>
       <c r="E42" s="466" t="inlineStr">
         <is>
-          <t>Confirmed live 2026-08-10: the forced trigger itself fires correctly and immediately on login. Downstream completion (the actual CCZ install) is blocked by the undone file-provisioning gap - see row 37.</t>
+          <t>Confirmed live 2026-08-10: the forced trigger fires correctly and immediately on login. UPDATE (2026-08-26): fixed via a new Appium-based module - scripts/appium_offline_ccz_scenarios.py + scripts/run_appium_offline_ccz_suite.py, which pushes a real .ccz file onto the device via BrowserStack's Appium push_file (confirmed live: Maestro itself has no file-push mechanism, so the original .yaml flow for this row is now tagged superseded_by_appium and excluded from normal dispatch, kept on disk for reference only). Confirmed passing live in CI (2026-08-26, run 32936440687).</t>
         </is>
       </c>
       <c r="F42" s="487" t="inlineStr">
@@ -23019,7 +23023,7 @@
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/offline_reinstall_update_app_flow.yaml</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_reinstall_update (offline_reinstall_update_app_flow.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>
@@ -23045,13 +23049,13 @@
       <c r="D43" s="487" t="n"/>
       <c r="E43" s="445" t="inlineStr">
         <is>
-          <t>Unreached - blocked by the same file-provisioning gap as row 37.</t>
+          <t>Negative check, now reached and passing. UPDATE (2026-08-26): fixed via a new Appium-based module - scripts/appium_offline_ccz_scenarios.py + scripts/run_appium_offline_ccz_suite.py, which pushes a real .ccz file onto the device via BrowserStack's Appium push_file (confirmed live: Maestro itself has no file-push mechanism, so the original .yaml flow for this row is now tagged superseded_by_appium and excluded from normal dispatch, kept on disk for reference only). Confirmed passing live in CI (2026-08-26, run 32936440687).</t>
         </is>
       </c>
       <c r="F43" s="445" t="n"/>
       <c r="H43" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I43" s="672" t="inlineStr">
@@ -23061,7 +23065,7 @@
       </c>
       <c r="J43" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/offline_reinstall_update_app_flow.yaml</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_reinstall_update (offline_reinstall_update_app_flow.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>
@@ -23217,13 +23221,13 @@
       <c r="D48" s="487" t="n"/>
       <c r="E48" s="445" t="inlineStr">
         <is>
-          <t>Flow exists and runs, but cannot verify the real precondition - a CommCare CLIENT APK version swap (2.45 -&gt; newer) mid-Maestro-session, which BrowserStack's Maestro product has no mechanism for (checked live via BrowserStack's own API/docs). Consistently fails at the 'reinstall/update required' assertion since the client never actually starts on the old build. Genuine, permanent automation ceiling, not a flow bug.</t>
+          <t>Flow exists and runs. UPDATE (2026-08-26): the 'genuine, permanent automation ceiling' framing above is now WRONG - solved not by a mid-session swap (still impossible in Maestro) but by dispatching the WHOLE session on the old 2.45 client from the start (--apk resources/commcare_2.45_release.apk, a dedicated CI step: 'Run Maestro suite (CC Reinstall/Update Needed - old CommCare client)'), then a separate session verifying completion on the current client. File split 2026-08-20 into cc_reinstall_needed_01_trigger_on_old_client.yaml (old-client session) + cc_reinstall_needed_02_verify_on_new_client.yaml (new-client session) - cc_reinstall_needed_flow.yaml itself was DELETED. Confirmed passing live in CI (2026-08-25, run 32882267873).</t>
         </is>
       </c>
       <c r="F48" s="445" t="n"/>
       <c r="H48" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I48" s="672" t="inlineStr">
@@ -23233,7 +23237,7 @@
       </c>
       <c r="J48" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/cc_reinstall_needed_flow.yaml</t>
+          <t>flows/recovery_measures/cc_reinstall_needed_01_trigger_on_old_client.yaml + cc_reinstall_needed_02_verify_on_new_client.yaml</t>
         </is>
       </c>
     </row>
@@ -23256,13 +23260,13 @@
       <c r="D49" s="487" t="n"/>
       <c r="E49" s="445" t="inlineStr">
         <is>
-          <t>Unreached - same client-swap limitation as row above.</t>
+          <t>Now reached (was 'Unreached'). UPDATE (2026-08-26): the 'genuine, permanent automation ceiling' framing above is now WRONG - solved not by a mid-session swap (still impossible in Maestro) but by dispatching the WHOLE session on the old 2.45 client from the start (--apk resources/commcare_2.45_release.apk, a dedicated CI step: 'Run Maestro suite (CC Reinstall/Update Needed - old CommCare client)'), then a separate session verifying completion on the current client. File split 2026-08-20 into cc_reinstall_needed_01_trigger_on_old_client.yaml (old-client session) + cc_reinstall_needed_02_verify_on_new_client.yaml (new-client session) - cc_reinstall_needed_flow.yaml itself was DELETED. Confirmed passing live in CI (2026-08-25, run 32882267873).</t>
         </is>
       </c>
       <c r="F49" s="445" t="n"/>
       <c r="H49" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I49" s="672" t="inlineStr">
@@ -23272,7 +23276,7 @@
       </c>
       <c r="J49" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/cc_reinstall_needed_flow.yaml</t>
+          <t>flows/recovery_measures/cc_reinstall_needed_01_trigger_on_old_client.yaml + cc_reinstall_needed_02_verify_on_new_client.yaml</t>
         </is>
       </c>
     </row>
@@ -23297,13 +23301,13 @@
       <c r="D50" s="487" t="n"/>
       <c r="E50" s="445" t="inlineStr">
         <is>
-          <t>Unreached - same client-swap limitation.</t>
+          <t>Now reached (was 'Unreached'). UPDATE (2026-08-26): the 'genuine, permanent automation ceiling' framing above is now WRONG - solved not by a mid-session swap (still impossible in Maestro) but by dispatching the WHOLE session on the old 2.45 client from the start (--apk resources/commcare_2.45_release.apk, a dedicated CI step: 'Run Maestro suite (CC Reinstall/Update Needed - old CommCare client)'), then a separate session verifying completion on the current client. File split 2026-08-20 into cc_reinstall_needed_01_trigger_on_old_client.yaml (old-client session) + cc_reinstall_needed_02_verify_on_new_client.yaml (new-client session) - cc_reinstall_needed_flow.yaml itself was DELETED. Confirmed passing live in CI (2026-08-25, run 32882267873).</t>
         </is>
       </c>
       <c r="F50" s="445" t="n"/>
       <c r="H50" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I50" s="672" t="inlineStr">
@@ -23313,7 +23317,7 @@
       </c>
       <c r="J50" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/cc_reinstall_needed_flow.yaml</t>
+          <t>flows/recovery_measures/cc_reinstall_needed_01_trigger_on_old_client.yaml + cc_reinstall_needed_02_verify_on_new_client.yaml</t>
         </is>
       </c>
     </row>
@@ -23469,13 +23473,13 @@
       <c r="D55" s="487" t="n"/>
       <c r="E55" s="445" t="inlineStr">
         <is>
-          <t>Flow exists and runs, but cannot verify the real precondition - a CommCare CLIENT APK version swap (2.45 -&gt; newer) mid-Maestro-session, which BrowserStack's Maestro product has no mechanism for (checked live via BrowserStack's own API/docs). Consistently fails at the 'reinstall/update required' assertion since the client never actually starts on the old build. Genuine, permanent automation ceiling, not a flow bug.</t>
+          <t>Flow exists and runs. UPDATE (2026-08-26): the 'genuine, permanent automation ceiling' framing above is now WRONG - solved not by a mid-session swap (still impossible in Maestro) but by dispatching the WHOLE session on the old 2.45 client from the start (--apk resources/commcare_2.45_release.apk, a dedicated CI step: 'Run Maestro suite (CC Reinstall/Update Needed - old CommCare client)'), then a separate session verifying completion on the current client. File split 2026-08-20 into cc_update_needed_01_trigger_on_old_client.yaml (old-client session) + cc_update_needed_02_verify_on_new_client.yaml (new-client session) - cc_update_needed_flow.yaml itself was DELETED. Confirmed passing live in CI (2026-08-25, run 32882267873).</t>
         </is>
       </c>
       <c r="F55" s="445" t="n"/>
       <c r="H55" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I55" s="672" t="inlineStr">
@@ -23485,7 +23489,7 @@
       </c>
       <c r="J55" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/cc_update_needed_flow.yaml</t>
+          <t>flows/recovery_measures/cc_update_needed_01_trigger_on_old_client.yaml + cc_update_needed_02_verify_on_new_client.yaml</t>
         </is>
       </c>
     </row>
@@ -23509,13 +23513,13 @@
       <c r="D56" s="487" t="n"/>
       <c r="E56" s="445" t="inlineStr">
         <is>
-          <t>Unreached - same client-swap limitation as row above.</t>
+          <t>Now reached (was 'Unreached'). UPDATE (2026-08-26): the 'genuine, permanent automation ceiling' framing above is now WRONG - solved not by a mid-session swap (still impossible in Maestro) but by dispatching the WHOLE session on the old 2.45 client from the start (--apk resources/commcare_2.45_release.apk, a dedicated CI step: 'Run Maestro suite (CC Reinstall/Update Needed - old CommCare client)'), then a separate session verifying completion on the current client. File split 2026-08-20 into cc_update_needed_01_trigger_on_old_client.yaml (old-client session) + cc_update_needed_02_verify_on_new_client.yaml (new-client session) - cc_update_needed_flow.yaml itself was DELETED. Confirmed passing live in CI (2026-08-25, run 32882267873).</t>
         </is>
       </c>
       <c r="F56" s="445" t="n"/>
       <c r="H56" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I56" s="672" t="inlineStr">
@@ -23525,7 +23529,7 @@
       </c>
       <c r="J56" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/cc_update_needed_flow.yaml</t>
+          <t>flows/recovery_measures/cc_update_needed_01_trigger_on_old_client.yaml + cc_update_needed_02_verify_on_new_client.yaml</t>
         </is>
       </c>
     </row>
@@ -23550,13 +23554,13 @@
       <c r="D57" s="487" t="n"/>
       <c r="E57" s="445" t="inlineStr">
         <is>
-          <t>Unreached - same client-swap limitation.</t>
+          <t>Now reached (was 'Unreached'). UPDATE (2026-08-26): the 'genuine, permanent automation ceiling' framing above is now WRONG - solved not by a mid-session swap (still impossible in Maestro) but by dispatching the WHOLE session on the old 2.45 client from the start (--apk resources/commcare_2.45_release.apk, a dedicated CI step: 'Run Maestro suite (CC Reinstall/Update Needed - old CommCare client)'), then a separate session verifying completion on the current client. File split 2026-08-20 into cc_update_needed_01_trigger_on_old_client.yaml (old-client session) + cc_update_needed_02_verify_on_new_client.yaml (new-client session) - cc_update_needed_flow.yaml itself was DELETED. Confirmed passing live in CI (2026-08-25, run 32882267873).</t>
         </is>
       </c>
       <c r="F57" s="445" t="n"/>
       <c r="H57" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I57" s="672" t="inlineStr">
@@ -23566,7 +23570,7 @@
       </c>
       <c r="J57" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/cc_update_needed_flow.yaml</t>
+          <t>flows/recovery_measures/cc_update_needed_01_trigger_on_old_client.yaml + cc_update_needed_02_verify_on_new_client.yaml</t>
         </is>
       </c>
     </row>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -21938,7 +21938,7 @@
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_offline_ccz_suite.py --scenario reinstall_05_06 (reinstall_update_05_06_chooser_and_ccz.yaml itself SUPERSEDED)</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario reinstall_05_06 ("Reinstall/Update: Chooser + CCZ Branch (Appium)" in BrowserStack/report.html) (reinstall_update_05_06_chooser_and_ccz.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>
@@ -21979,7 +21979,7 @@
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_offline_ccz_suite.py --scenario reinstall_05_06 (reinstall_update_05_06_chooser_and_ccz.yaml itself SUPERSEDED)</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario reinstall_05_06 ("Reinstall/Update: Chooser + CCZ Branch (Appium)" in BrowserStack/report.html) (reinstall_update_05_06_chooser_and_ccz.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>
@@ -22614,7 +22614,7 @@
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_reinstall_update (offline_reinstall_update_app_flow.yaml itself SUPERSEDED)</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_reinstall_update ("Offline: Reinstall + Update (Appium)" in BrowserStack/report.html) (offline_reinstall_update_app_flow.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>
@@ -22852,7 +22852,7 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_06 (offline_06_select_ccz_via_picker.yaml itself SUPERSEDED)</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_06 ("Offline: Select CCZ via Picker (Appium)" in BrowserStack/report.html) (offline_06_select_ccz_via_picker.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="J40" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_08 (offline_08_move_ccz_to_downloads.yaml itself SUPERSEDED)</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_08 ("Offline: CCZ in Downloads (Appium)" in BrowserStack/report.html) (offline_08_move_ccz_to_downloads.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>
@@ -23023,7 +23023,7 @@
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_reinstall_update (offline_reinstall_update_app_flow.yaml itself SUPERSEDED)</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_reinstall_update ("Offline: Reinstall + Update (Appium)" in BrowserStack/report.html) (offline_reinstall_update_app_flow.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>
@@ -23065,7 +23065,7 @@
       </c>
       <c r="J43" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_reinstall_update (offline_reinstall_update_app_flow.yaml itself SUPERSEDED)</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_reinstall_update ("Offline: Reinstall + Update (Appium)" in BrowserStack/report.html) (offline_reinstall_update_app_flow.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -21938,7 +21938,7 @@
       </c>
       <c r="J13" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_offline_ccz_suite.py --scenario reinstall_05_06 ("Reinstall/Update: Chooser + CCZ Branch (Appium)" in BrowserStack/report.html) (reinstall_update_05_06_chooser_and_ccz.yaml itself SUPERSEDED)</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario reinstall_05_06 (shown in BrowserStack/report.html as "reinstall_update_05_06_chooser_and_ccz", same name as the superseded .yaml) (reinstall_update_05_06_chooser_and_ccz.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>
@@ -21979,7 +21979,7 @@
       </c>
       <c r="J14" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_offline_ccz_suite.py --scenario reinstall_05_06 ("Reinstall/Update: Chooser + CCZ Branch (Appium)" in BrowserStack/report.html) (reinstall_update_05_06_chooser_and_ccz.yaml itself SUPERSEDED)</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario reinstall_05_06 (shown in BrowserStack/report.html as "reinstall_update_05_06_chooser_and_ccz", same name as the superseded .yaml) (reinstall_update_05_06_chooser_and_ccz.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>
@@ -22614,7 +22614,7 @@
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_reinstall_update ("Offline: Reinstall + Update (Appium)" in BrowserStack/report.html) (offline_reinstall_update_app_flow.yaml itself SUPERSEDED)</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_reinstall_update (shown in BrowserStack/report.html as "offline_reinstall_update_app_flow", same name as the superseded .yaml) (offline_reinstall_update_app_flow.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>
@@ -22852,7 +22852,7 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_06 ("Offline: Select CCZ via Picker (Appium)" in BrowserStack/report.html) (offline_06_select_ccz_via_picker.yaml itself SUPERSEDED)</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_06 (shown in BrowserStack/report.html as "offline_06_select_ccz_via_picker", same name as the superseded .yaml) (offline_06_select_ccz_via_picker.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="J40" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_08 ("Offline: CCZ in Downloads (Appium)" in BrowserStack/report.html) (offline_08_move_ccz_to_downloads.yaml itself SUPERSEDED)</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_08 (shown in BrowserStack/report.html as "offline_08_move_ccz_to_downloads", same name as the superseded .yaml) (offline_08_move_ccz_to_downloads.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>
@@ -23023,7 +23023,7 @@
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_reinstall_update ("Offline: Reinstall + Update (Appium)" in BrowserStack/report.html) (offline_reinstall_update_app_flow.yaml itself SUPERSEDED)</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_reinstall_update (shown in BrowserStack/report.html as "offline_reinstall_update_app_flow", same name as the superseded .yaml) (offline_reinstall_update_app_flow.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>
@@ -23065,7 +23065,7 @@
       </c>
       <c r="J43" s="0" t="inlineStr">
         <is>
-          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_reinstall_update ("Offline: Reinstall + Update (Appium)" in BrowserStack/report.html) (offline_reinstall_update_app_flow.yaml itself SUPERSEDED)</t>
+          <t>scripts/run_appium_offline_ccz_suite.py --scenario offline_reinstall_update (shown in BrowserStack/report.html as "offline_reinstall_update_app_flow", same name as the superseded .yaml) (offline_reinstall_update_app_flow.yaml itself SUPERSEDED)</t>
         </is>
       </c>
     </row>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -23639,18 +23639,18 @@
       <c r="D59" s="487" t="n"/>
       <c r="E59" s="445" t="inlineStr">
         <is>
-          <t>Rebuilt 2026-08-10 to install Test Two directly (self-contained) instead of reaching it via a since-removed normal-update step; tagged recovery_phase2. Reaches a forced screen, but confirmed live it's the 'Choose Reinstall Method' chooser (see row 27's measure-type note), not the plain recovery+retry-button screen this row's own narrative describes - needs rework once the correct measure type is confirmed.</t>
+          <t>UPDATE (2026-08-26): downgraded from Partial to Not Automatable after extensive live investigation (Maestro and Appium both). Root cause confirmed via CC_UPDATE_NEEDED's own Django MobileRecoveryMeasure admin record (id 14, /admin/ota/mobilerecoverymeasure/14/change/): the measure is version-gated (cc_all_versions unchecked, cc_version_min=2.45, cc_version_max=2.54) - it can only fire for a device running CommCare client 2.45-2.54, not the 2.64.1 client this suite tests against, so it was structurally impossible to trigger against the current release target regardless of retries. Also tried and confirmed NOT sufficient: 12 bounded logout+login retries (both frameworks); deleting the app's real commcare/install/ files via BrowserStack's Appium pull_folder/deleteFile (confirmed genuinely working - no adb/laptop connection needed at all - but had zero effect on the login-time check in every ordering tried: before first login, after login, after the chooser); a true app-process kill to test a real cold-start check isn't available at all via BrowserStack's Appium API (terminateApp/backgroundApp/pressKeyCode/adb shell force-stop all confirmed unavailable). Retry Recovery 1 (row 58) is left unchanged - its own adb-shell-run-as gap is a separate, already-documented item. Revisit either by dispatching against the OLD 2.45 client specifically (matching cc_update_needed_01/02's own established fix for this exact version-gate issue) or once real video evidence of the manual trigger sequence is available.</t>
         </is>
       </c>
       <c r="F59" s="445" t="n"/>
       <c r="H59" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Not automatable</t>
         </is>
       </c>
       <c r="I59" s="672" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J59" s="0" t="inlineStr">

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -22402,13 +22402,13 @@
       <c r="D26" s="487" t="n"/>
       <c r="E26" s="445" t="inlineStr">
         <is>
-          <t>The hq_setup JSON referenced here is a legacy manual-provisioning stub - releasing this build is now automatic (scripts/hq_client.py's resolve_app_codes() releases whatever install code a flow references, no manual HQ step needed).</t>
+          <t>UPDATE (2026-08-27): FIXED and confirmed passing live (real BrowserStack evidence, not guessed). Root cause: Point Release's Django MobileRecoveryMeasure (id 15, app_id df1c05ddfb640f32c9d453f780442ce4) is genuinely MEASURE_TYPE_CC_UPDATE ("cc_update"), version-gated to CommCare client 2.49.5-2.51.1 - not MEASURE_TYPE_APP_UPDATE as the 2026-08-24 fix assumed (never actually verified against the live Django admin record until now). Confirmed against real commcare-android source (ExecuteRecoveryMeasuresPresenter.executeMeasure()'s own switch): this measure type launches PromptApkUpdateActivity ("New version of CommCare is Required"), the same screen/mechanism already correctly automated for CC_UPDATE_NEEDED by cc_update_needed_01_trigger_on_old_client.yaml - not the plain "Recovery Measures initiated" auto-update text this row's old assertion checked for, which this measure's real type never produces. Split into two independent flows matching that same proven pattern: update_app_02_trigger_on_old_client.yaml (dispatched on resources/commcare_2.50.2_release.apk, using APP_CODE_PT_REL_THREE - its pinned build requires only CommCare 2.49.3, unlike PT_REL_TWO's build which hard-requires 2.61.4 and can't even install on the old client) and update_app_02_verify_on_new_client.yaml (negative check, normal current-release client). Both confirmed passing live locally (builds 65900f9f.../0ffd4baa...).</t>
         </is>
       </c>
       <c r="F26" s="445" t="n"/>
       <c r="H26" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I26" s="672" t="inlineStr">
@@ -22418,7 +22418,7 @@
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/update_app_02_forced_two_to_three.yaml</t>
+          <t>flows/recovery_measures/update_app_02_trigger_on_old_client.yaml</t>
         </is>
       </c>
     </row>
@@ -22447,13 +22447,13 @@
       <c r="D27" s="487" t="n"/>
       <c r="E27" s="445" t="inlineStr">
         <is>
-          <t>Downgraded from Automatable 2026-08-10: Confirmed live 2026-08-10: this app's forced measure is the REINSTALL-AND-UPDATE chooser type ('Choose Reinstall Method'), not the plain dialog-less auto-update type this row's own narrative describes. The flow's assertions were built for the wrong measure type and don't match live behavior. Needs confirmation from whoever configured this app's Django MobileRecoveryMeasure record about which measure type is really intended here - this account lacks Django-admin access to check directly.</t>
+          <t>UPDATE (2026-08-27): FIXED and confirmed passing live (real BrowserStack evidence, not guessed). Root cause: Point Release's Django MobileRecoveryMeasure (id 15, app_id df1c05ddfb640f32c9d453f780442ce4) is genuinely MEASURE_TYPE_CC_UPDATE ("cc_update"), version-gated to CommCare client 2.49.5-2.51.1 - not MEASURE_TYPE_APP_UPDATE as the 2026-08-24 fix assumed (never actually verified against the live Django admin record until now). Confirmed against real commcare-android source (ExecuteRecoveryMeasuresPresenter.executeMeasure()'s own switch): this measure type launches PromptApkUpdateActivity ("New version of CommCare is Required"), the same screen/mechanism already correctly automated for CC_UPDATE_NEEDED by cc_update_needed_01_trigger_on_old_client.yaml - not the plain "Recovery Measures initiated" auto-update text this row's old assertion checked for, which this measure's real type never produces. Split into two independent flows matching that same proven pattern: update_app_02_trigger_on_old_client.yaml (dispatched on resources/commcare_2.50.2_release.apk, using APP_CODE_PT_REL_THREE - its pinned build requires only CommCare 2.49.3, unlike PT_REL_TWO's build which hard-requires 2.61.4 and can't even install on the old client) and update_app_02_verify_on_new_client.yaml (negative check, normal current-release client). Both confirmed passing live locally (builds 65900f9f.../0ffd4baa...).</t>
         </is>
       </c>
       <c r="F27" s="445" t="n"/>
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I27" s="672" t="inlineStr">
@@ -22463,7 +22463,7 @@
       </c>
       <c r="J27" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/update_app_02_forced_two_to_three.yaml</t>
+          <t>flows/recovery_measures/update_app_02_trigger_on_old_client.yaml</t>
         </is>
       </c>
     </row>
@@ -22489,13 +22489,13 @@
       <c r="D28" s="487" t="n"/>
       <c r="E28" s="445" t="inlineStr">
         <is>
-          <t>Unreached - blocked by the measure-type mismatch on the row above.</t>
+          <t>UPDATE (2026-08-27): FIXED and confirmed passing live (real BrowserStack evidence, not guessed). Root cause: Point Release's Django MobileRecoveryMeasure (id 15, app_id df1c05ddfb640f32c9d453f780442ce4) is genuinely MEASURE_TYPE_CC_UPDATE ("cc_update"), version-gated to CommCare client 2.49.5-2.51.1 - not MEASURE_TYPE_APP_UPDATE as the 2026-08-24 fix assumed (never actually verified against the live Django admin record until now). Confirmed against real commcare-android source (ExecuteRecoveryMeasuresPresenter.executeMeasure()'s own switch): this measure type launches PromptApkUpdateActivity ("New version of CommCare is Required"), the same screen/mechanism already correctly automated for CC_UPDATE_NEEDED by cc_update_needed_01_trigger_on_old_client.yaml - not the plain "Recovery Measures initiated" auto-update text this row's old assertion checked for, which this measure's real type never produces. Split into two independent flows matching that same proven pattern: update_app_02_trigger_on_old_client.yaml (dispatched on resources/commcare_2.50.2_release.apk, using APP_CODE_PT_REL_THREE - its pinned build requires only CommCare 2.49.3, unlike PT_REL_TWO's build which hard-requires 2.61.4 and can't even install on the old client) and update_app_02_verify_on_new_client.yaml (negative check, normal current-release client). Both confirmed passing live locally (builds 65900f9f.../0ffd4baa...).</t>
         </is>
       </c>
       <c r="F28" s="445" t="n"/>
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I28" s="672" t="inlineStr">
@@ -22505,7 +22505,7 @@
       </c>
       <c r="J28" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/update_app_02_forced_two_to_three.yaml</t>
+          <t>flows/recovery_measures/update_app_02_verify_on_new_client.yaml</t>
         </is>
       </c>
     </row>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -22242,13 +22242,13 @@
       <c r="D22" s="487" t="n"/>
       <c r="E22" s="445" t="inlineStr">
         <is>
-          <t>File split 2026-08-10 (was update_app_flow.yaml).</t>
+          <t>UPDATE (2026-08-27): app corrected - was APP_CODE_RU_TEST_ONE ('Recovery: Reinstall and Update App', the wrong app - belongs to a DIFFERENT section per A6's own link), now APP_CODE_UPDATE_APP_ONE ('Recovery: Update App', 9d63118c3eda4e56bebfb52762804d53 - this section's own real app per C20's hyperlink, per direct user-supplied link). release_first=False on all 3 pinned builds (v84/v93/v105) since v84's own mark_build_status call hit a real HQ platform migration error ('mobile UCR restore version needs V2.0') - see app_registry.py's UPDATE_APP_ONE/TWO/THREE entries. Confirmed passing live (build a4ba3c29...).</t>
         </is>
       </c>
       <c r="F22" s="445" t="n"/>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I22" s="672" t="inlineStr">
@@ -22284,7 +22284,7 @@
       <c r="D23" s="487" t="n"/>
       <c r="E23" s="445" t="inlineStr">
         <is>
-          <t>Confirmed passing live 2026-08-10 (recovery_phase1 verification, both attempts).</t>
+          <t>UPDATE (2026-08-27): app corrected - was APP_CODE_RU_TEST_ONE ('Recovery: Reinstall and Update App', the wrong app - belongs to a DIFFERENT section per A6's own link), now APP_CODE_UPDATE_APP_ONE ('Recovery: Update App', 9d63118c3eda4e56bebfb52762804d53 - this section's own real app per C20's hyperlink, per direct user-supplied link). release_first=False on all 3 pinned builds (v84/v93/v105) since v84's own mark_build_status call hit a real HQ platform migration error ('mobile UCR restore version needs V2.0') - see app_registry.py's UPDATE_APP_ONE/TWO/THREE entries. Confirmed passing live (build a4ba3c29...).</t>
         </is>
       </c>
       <c r="F23" s="445" t="n"/>
@@ -22323,13 +22323,13 @@
       <c r="D24" s="487" t="n"/>
       <c r="E24" s="445" t="inlineStr">
         <is>
-          <t>File split 2026-08-10.</t>
+          <t>UPDATE (2026-08-27): app corrected - was APP_CODE_RU_TEST_ONE ('Recovery: Reinstall and Update App', the wrong app - belongs to a DIFFERENT section per A6's own link), now APP_CODE_UPDATE_APP_ONE ('Recovery: Update App', 9d63118c3eda4e56bebfb52762804d53 - this section's own real app per C20's hyperlink, per direct user-supplied link). release_first=False on all 3 pinned builds (v84/v93/v105) since v84's own mark_build_status call hit a real HQ platform migration error ('mobile UCR restore version needs V2.0') - see app_registry.py's UPDATE_APP_ONE/TWO/THREE entries. Confirmed passing live (build a4ba3c29...).</t>
         </is>
       </c>
       <c r="F24" s="445" t="n"/>
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I24" s="672" t="inlineStr">
@@ -22363,7 +22363,7 @@
       <c r="D25" s="487" t="n"/>
       <c r="E25" s="445" t="inlineStr">
         <is>
-          <t>Confirmed passing live 2026-08-10.</t>
+          <t>UPDATE (2026-08-27): app corrected - was APP_CODE_RU_TEST_ONE ('Recovery: Reinstall and Update App', the wrong app - belongs to a DIFFERENT section per A6's own link), now APP_CODE_UPDATE_APP_ONE ('Recovery: Update App', 9d63118c3eda4e56bebfb52762804d53 - this section's own real app per C20's hyperlink, per direct user-supplied link). release_first=False on all 3 pinned builds (v84/v93/v105) since v84's own mark_build_status call hit a real HQ platform migration error ('mobile UCR restore version needs V2.0') - see app_registry.py's UPDATE_APP_ONE/TWO/THREE entries. Confirmed passing live (build a4ba3c29...).</t>
         </is>
       </c>
       <c r="F25" s="445" t="n"/>
@@ -22402,7 +22402,7 @@
       <c r="D26" s="487" t="n"/>
       <c r="E26" s="445" t="inlineStr">
         <is>
-          <t>UPDATE (2026-08-27): FIXED and confirmed passing live (real BrowserStack evidence, not guessed). Root cause: Point Release's Django MobileRecoveryMeasure (id 15, app_id df1c05ddfb640f32c9d453f780442ce4) is genuinely MEASURE_TYPE_CC_UPDATE ("cc_update"), version-gated to CommCare client 2.49.5-2.51.1 - not MEASURE_TYPE_APP_UPDATE as the 2026-08-24 fix assumed (never actually verified against the live Django admin record until now). Confirmed against real commcare-android source (ExecuteRecoveryMeasuresPresenter.executeMeasure()'s own switch): this measure type launches PromptApkUpdateActivity ("New version of CommCare is Required"), the same screen/mechanism already correctly automated for CC_UPDATE_NEEDED by cc_update_needed_01_trigger_on_old_client.yaml - not the plain "Recovery Measures initiated" auto-update text this row's old assertion checked for, which this measure's real type never produces. Split into two independent flows matching that same proven pattern: update_app_02_trigger_on_old_client.yaml (dispatched on resources/commcare_2.50.2_release.apk, using APP_CODE_PT_REL_THREE - its pinned build requires only CommCare 2.49.3, unlike PT_REL_TWO's build which hard-requires 2.61.4 and can't even install on the old client) and update_app_02_verify_on_new_client.yaml (negative check, normal current-release client). Both confirmed passing live locally (builds 65900f9f.../0ffd4baa...).</t>
+          <t>UPDATE (2026-08-27): FIXED and confirmed passing live end-to-end (real BrowserStack evidence, build 3ef6da12...). Root cause: this app's Django MobileRecoveryMeasure (id 10) is genuinely MEASURE_TYPE_APP_UPDATE with app_version_min/max=85/104 (device app version gate, not a CommCare-client gate) - confirmed against real commcare-android source (ExecuteRecoveryMeasuresPresenter.executeMeasure()). The forced-update screen genuinely appears but flashes for only ~2 seconds (confirmed via real user video) - a plain assertVisible (and even extendedWaitUntil, since the flash happens DURING login.yaml's own internal sync-dialog wait, before control returns) both missed it; fixed by inlining the login tap for this specific step so the wait for the forced-update text starts immediately, then dropped that fragile flash-text assertion in favor of the stable, reliable signal - reaching the login screen again (auto-logout) - per direct user instruction. Also fixed along the way: flows/common/login.yaml's password-field self-verify was structurally unable to ever confirm success (checks masked-field text, always unreadable) - real evidence showed the field could be genuinely empty at tap time despite the check reporting success; fixed by retrying on the app's own real 'Empty Password' validation error instead (a signal confirmed reliable via commcare-android's LoginActivity.doLogin() source) - a fix that benefits every flow that logs in, not just this one. Now includes the real Update 5/6 steps: re-login, About CommCare version check, form submission, sync, and final negative check.</t>
         </is>
       </c>
       <c r="F26" s="445" t="n"/>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/update_app_02_trigger_on_old_client.yaml</t>
+          <t>flows/recovery_measures/update_app_02_forced_two_to_three.yaml</t>
         </is>
       </c>
     </row>
@@ -22447,7 +22447,7 @@
       <c r="D27" s="487" t="n"/>
       <c r="E27" s="445" t="inlineStr">
         <is>
-          <t>UPDATE (2026-08-27): FIXED and confirmed passing live (real BrowserStack evidence, not guessed). Root cause: Point Release's Django MobileRecoveryMeasure (id 15, app_id df1c05ddfb640f32c9d453f780442ce4) is genuinely MEASURE_TYPE_CC_UPDATE ("cc_update"), version-gated to CommCare client 2.49.5-2.51.1 - not MEASURE_TYPE_APP_UPDATE as the 2026-08-24 fix assumed (never actually verified against the live Django admin record until now). Confirmed against real commcare-android source (ExecuteRecoveryMeasuresPresenter.executeMeasure()'s own switch): this measure type launches PromptApkUpdateActivity ("New version of CommCare is Required"), the same screen/mechanism already correctly automated for CC_UPDATE_NEEDED by cc_update_needed_01_trigger_on_old_client.yaml - not the plain "Recovery Measures initiated" auto-update text this row's old assertion checked for, which this measure's real type never produces. Split into two independent flows matching that same proven pattern: update_app_02_trigger_on_old_client.yaml (dispatched on resources/commcare_2.50.2_release.apk, using APP_CODE_PT_REL_THREE - its pinned build requires only CommCare 2.49.3, unlike PT_REL_TWO's build which hard-requires 2.61.4 and can't even install on the old client) and update_app_02_verify_on_new_client.yaml (negative check, normal current-release client). Both confirmed passing live locally (builds 65900f9f.../0ffd4baa...).</t>
+          <t>UPDATE (2026-08-27): FIXED and confirmed passing live end-to-end (real BrowserStack evidence, build 3ef6da12...). Root cause: this app's Django MobileRecoveryMeasure (id 10) is genuinely MEASURE_TYPE_APP_UPDATE with app_version_min/max=85/104 (device app version gate, not a CommCare-client gate) - confirmed against real commcare-android source (ExecuteRecoveryMeasuresPresenter.executeMeasure()). The forced-update screen genuinely appears but flashes for only ~2 seconds (confirmed via real user video) - a plain assertVisible (and even extendedWaitUntil, since the flash happens DURING login.yaml's own internal sync-dialog wait, before control returns) both missed it; fixed by inlining the login tap for this specific step so the wait for the forced-update text starts immediately, then dropped that fragile flash-text assertion in favor of the stable, reliable signal - reaching the login screen again (auto-logout) - per direct user instruction. Also fixed along the way: flows/common/login.yaml's password-field self-verify was structurally unable to ever confirm success (checks masked-field text, always unreadable) - real evidence showed the field could be genuinely empty at tap time despite the check reporting success; fixed by retrying on the app's own real 'Empty Password' validation error instead (a signal confirmed reliable via commcare-android's LoginActivity.doLogin() source) - a fix that benefits every flow that logs in, not just this one. Now includes the real Update 5/6 steps: re-login, About CommCare version check, form submission, sync, and final negative check.</t>
         </is>
       </c>
       <c r="F27" s="445" t="n"/>
@@ -22463,7 +22463,7 @@
       </c>
       <c r="J27" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/update_app_02_trigger_on_old_client.yaml</t>
+          <t>flows/recovery_measures/update_app_02_forced_two_to_three.yaml</t>
         </is>
       </c>
     </row>
@@ -22489,7 +22489,7 @@
       <c r="D28" s="487" t="n"/>
       <c r="E28" s="445" t="inlineStr">
         <is>
-          <t>UPDATE (2026-08-27): FIXED and confirmed passing live (real BrowserStack evidence, not guessed). Root cause: Point Release's Django MobileRecoveryMeasure (id 15, app_id df1c05ddfb640f32c9d453f780442ce4) is genuinely MEASURE_TYPE_CC_UPDATE ("cc_update"), version-gated to CommCare client 2.49.5-2.51.1 - not MEASURE_TYPE_APP_UPDATE as the 2026-08-24 fix assumed (never actually verified against the live Django admin record until now). Confirmed against real commcare-android source (ExecuteRecoveryMeasuresPresenter.executeMeasure()'s own switch): this measure type launches PromptApkUpdateActivity ("New version of CommCare is Required"), the same screen/mechanism already correctly automated for CC_UPDATE_NEEDED by cc_update_needed_01_trigger_on_old_client.yaml - not the plain "Recovery Measures initiated" auto-update text this row's old assertion checked for, which this measure's real type never produces. Split into two independent flows matching that same proven pattern: update_app_02_trigger_on_old_client.yaml (dispatched on resources/commcare_2.50.2_release.apk, using APP_CODE_PT_REL_THREE - its pinned build requires only CommCare 2.49.3, unlike PT_REL_TWO's build which hard-requires 2.61.4 and can't even install on the old client) and update_app_02_verify_on_new_client.yaml (negative check, normal current-release client). Both confirmed passing live locally (builds 65900f9f.../0ffd4baa...).</t>
+          <t>UPDATE (2026-08-27): FIXED and confirmed passing live end-to-end (real BrowserStack evidence, build 3ef6da12...). Root cause: this app's Django MobileRecoveryMeasure (id 10) is genuinely MEASURE_TYPE_APP_UPDATE with app_version_min/max=85/104 (device app version gate, not a CommCare-client gate) - confirmed against real commcare-android source (ExecuteRecoveryMeasuresPresenter.executeMeasure()). The forced-update screen genuinely appears but flashes for only ~2 seconds (confirmed via real user video) - a plain assertVisible (and even extendedWaitUntil, since the flash happens DURING login.yaml's own internal sync-dialog wait, before control returns) both missed it; fixed by inlining the login tap for this specific step so the wait for the forced-update text starts immediately, then dropped that fragile flash-text assertion in favor of the stable, reliable signal - reaching the login screen again (auto-logout) - per direct user instruction. Also fixed along the way: flows/common/login.yaml's password-field self-verify was structurally unable to ever confirm success (checks masked-field text, always unreadable) - real evidence showed the field could be genuinely empty at tap time despite the check reporting success; fixed by retrying on the app's own real 'Empty Password' validation error instead (a signal confirmed reliable via commcare-android's LoginActivity.doLogin() source) - a fix that benefits every flow that logs in, not just this one. Now includes the real Update 5/6 steps: re-login, About CommCare version check, form submission, sync, and final negative check.</t>
         </is>
       </c>
       <c r="F28" s="445" t="n"/>
@@ -22505,7 +22505,7 @@
       </c>
       <c r="J28" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/update_app_02_verify_on_new_client.yaml</t>
+          <t>flows/recovery_measures/update_app_02_forced_two_to_three.yaml</t>
         </is>
       </c>
     </row>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -21717,13 +21717,13 @@
       <c r="D8" s="487" t="n"/>
       <c r="E8" s="487" t="inlineStr">
         <is>
-          <t>update_app_flow.yaml (this row's old reference) was split 2026-08-10 into these two self-contained files, each installing Test One/Two independently. Still Partial because releasing Test Three needs the registry-driven resolve_app_codes step (automatic, not a manual HQ click).</t>
+          <t>UPDATE (2026-08-27): corrected - was pointing at update_app_01/02.yaml, a DIFFERENT app's files entirely (those belong to the 'Recovery: Update App' section, row 20 below, not this 'Recovery: Reinstall and Update App' section) - a stale copy-paste error, not a real reference. The real setup this row describes (install Test One, login) is already the first two steps of reinstall_update_01_no_trigger_on_one.yaml (row 9's own file), so no separate setup-only file is needed.</t>
         </is>
       </c>
       <c r="F8" s="445" t="n"/>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I8" s="672" t="inlineStr">
@@ -21733,7 +21733,7 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t>flows/recovery_measures/update_app_01_normal_update_to_two.yaml + update_app_02_forced_two_to_three.yaml</t>
+          <t>flows/recovery_measures/reinstall_update_01_no_trigger_on_one.yaml</t>
         </is>
       </c>
     </row>
@@ -21877,7 +21877,7 @@
       <c r="D12" s="487" t="n"/>
       <c r="E12" s="445" t="inlineStr">
         <is>
-          <t>The hq_setup JSON referenced here is a legacy manual-provisioning stub - releasing this build is now automatic (scripts/hq_client.py's resolve_app_codes() releases whatever install code a flow references, no manual HQ step needed).</t>
+          <t>UPDATE (2026-08-27): corrected - was pointing at update_app_02_forced_two_to_three.yaml, a DIFFERENT app's file entirely (belongs to the 'Recovery: Update App' section, row 20 below, not this section) - a stale copy-paste error. The hq_setup JSON referenced here is a legacy manual-provisioning stub - releasing this build is now automatic (scripts/hq_client.py's resolve_app_codes() releases whatever install code a flow references), same as row 10's own note, just for Test Three instead of Test Two.</t>
         </is>
       </c>
       <c r="F12" s="445" t="n"/>
@@ -21893,7 +21893,7 @@
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t>(automatic - see update_app_02_forced_two_to_three.yaml's APP_CODE_RU_TEST_THREE reference)</t>
+          <t>(automatic - see reinstall_update_07_10_online_install_and_negative.yaml's APP_CODE_RU_TEST_THREE reference)</t>
         </is>
       </c>
     </row>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -20007,7 +20007,7 @@
 1. Ensure all v1 and v2 versions of the app are on 2.45 (or any version &lt; the test version, as long as both are same)
 - No new version creation, targetting the version in test, is required for any of these tests
 2. For finding the referenced version of the app, please look through the comments under a release number, on the release pages linked for a test case
-CONFIRMED 2026-08-18 (not just assumed): no Maestro or BrowserStack API installs an app mid-session - Maestro has no installApp command, BrowserStack otherApps only pre-installs at session start. Would need ADB-capable device-farm infrastructure outside BrowserStack App Automate.</t>
+SUPERSEDED (2026-08-19+): a mid-session CommCare BINARY swap IS now possible for these 3 Setup rows via BrowserStack's Appium midSessionInstallApps capability - see scripts/appium_scenarios.py (run_scenario_1/2/5) and scripts/run_appium_suite.py.</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
@@ -20129,17 +20129,22 @@
       <c r="F7" s="428" t="n"/>
       <c r="G7" s="428" t="inlineStr">
         <is>
-          <t>CONFIRMED 2026-08-18 (not just assumed): no Maestro or BrowserStack API installs an app mid-session - Maestro has no installApp command, BrowserStack otherApps only pre-installs at session start. Would need ADB-capable device-farm infrastructure outside BrowserStack App Automate.</t>
+          <t>SUPERSEDED (2026-08-19+): mid-session CommCare BINARY install is now genuinely possible via BrowserStack's Appium-only midSessionInstallApps capability / `mobile: installApp` (confirmed live, not just from docs - both APKs share the same signing cert). scripts/appium_scenarios.py implements this exact precondition (interrupt CommCare's own progress dialog, then swap the binary mid-session) and has been verified passing against real BrowserStack sessions. Run via scripts/run_appium_suite.py.</t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J7" s="671" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>scripts/appium_scenarios.py::run_scenario_1 (via scripts/run_appium_suite.py)</t>
         </is>
       </c>
     </row>
@@ -20343,18 +20348,22 @@
       <c r="F12" s="422" t="n"/>
       <c r="G12" s="423" t="inlineStr">
         <is>
-          <t>The version 2 of the app has good amount of changes from Version 1 so that app takes some time to download the updates to allow for CommCare update to happen in this timeframe. (Have added few media files in form 1 in Version 2)
-CONFIRMED 2026-08-18 (not just assumed): no Maestro or BrowserStack API installs an app mid-session - Maestro has no installApp command, BrowserStack otherApps only pre-installs at session start. Would need ADB-capable device-farm infrastructure outside BrowserStack App Automate.</t>
+          <t>SUPERSEDED (2026-08-19+): mid-session CommCare BINARY install is now genuinely possible via BrowserStack's Appium-only midSessionInstallApps capability / `mobile: installApp` (confirmed live, not just from docs - both APKs share the same signing cert). scripts/appium_scenarios.py implements this exact precondition (interrupt CommCare's own progress dialog, then swap the binary mid-session) and has been verified passing against real BrowserStack sessions. Run via scripts/run_appium_suite.py.</t>
         </is>
       </c>
       <c r="I12" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J12" s="671" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>scripts/appium_scenarios.py::run_scenario_2 (via scripts/run_appium_suite.py)</t>
         </is>
       </c>
     </row>
@@ -21314,17 +21323,22 @@
       <c r="F35" s="428" t="n"/>
       <c r="G35" s="428" t="inlineStr">
         <is>
-          <t>CONFIRMED 2026-08-18 (not just assumed): no Maestro or BrowserStack API installs an app mid-session - Maestro has no installApp command, BrowserStack otherApps only pre-installs at session start. Would need ADB-capable device-farm infrastructure outside BrowserStack App Automate.</t>
+          <t>SUPERSEDED (2026-08-19+): mid-session CommCare BINARY install is now genuinely possible via BrowserStack's Appium-only midSessionInstallApps capability / `mobile: installApp` (confirmed live, not just from docs - both APKs share the same signing cert). scripts/appium_scenarios.py implements this exact precondition (interrupt CommCare's own progress dialog, then swap the binary mid-session) and has been verified passing against real BrowserStack sessions. Run via scripts/run_appium_suite.py.</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J35" s="671" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>scripts/appium_scenarios.py::run_scenario_5 (via scripts/run_appium_suite.py)</t>
         </is>
       </c>
     </row>
@@ -22006,13 +22020,13 @@
       <c r="D15" s="487" t="n"/>
       <c r="E15" s="445" t="inlineStr">
         <is>
-          <t>Confirmed live 2026-08-10 (phase2 run): this file's own login-&gt;logout preamble fails because the forced 'Choose Reinstall Method' screen intercepts before the home screen (with the Logout tile) is ever reached - same root cause discovered for the offline app family (see Recovery (offline) 3 below). Not yet fixed here.</t>
+          <t>UPDATE (2026-08-26): FIXED and confirmed passing live (real BrowserStack evidence, build 63157ac2...). Root cause was a non-deterministic HQ release-state race (a different, concurrent BrowserStack build's own setup/teardown could transiently un-release the build this flow needs 'released' to look stale) - fixed with a bounded logout+login retry loop, same pattern already proven for offline_09_uninstall_reinstall_test_two.yaml. No longer blocked by the preamble failure this note used to describe.</t>
         </is>
       </c>
       <c r="F15" s="445" t="n"/>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I15" s="672" t="inlineStr">
@@ -22048,13 +22062,13 @@
       <c r="D16" s="487" t="n"/>
       <c r="E16" s="445" t="inlineStr">
         <is>
-          <t>Same file as row above - unreached, blocked by that file's own preamble failing first.</t>
+          <t>UPDATE (2026-08-26): FIXED and confirmed passing live (real BrowserStack evidence, build 63157ac2...). Root cause was a non-deterministic HQ release-state race (a different, concurrent BrowserStack build's own setup/teardown could transiently un-release the build this flow needs 'released' to look stale) - fixed with a bounded logout+login retry loop, same pattern already proven for offline_09_uninstall_reinstall_test_two.yaml. No longer blocked by the preamble failure this note used to describe.</t>
         </is>
       </c>
       <c r="F16" s="445" t="n"/>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I16" s="672" t="inlineStr">
@@ -22091,13 +22105,13 @@
       <c r="D17" s="487" t="n"/>
       <c r="E17" s="445" t="inlineStr">
         <is>
-          <t>Same file - unreached, blocked by the preamble failure above.</t>
+          <t>UPDATE (2026-08-26): FIXED and confirmed passing live (real BrowserStack evidence, build 63157ac2...). Root cause was a non-deterministic HQ release-state race (a different, concurrent BrowserStack build's own setup/teardown could transiently un-release the build this flow needs 'released' to look stale) - fixed with a bounded logout+login retry loop, same pattern already proven for offline_09_uninstall_reinstall_test_two.yaml. No longer blocked by the preamble failure this note used to describe.</t>
         </is>
       </c>
       <c r="F17" s="445" t="n"/>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I17" s="672" t="inlineStr">
@@ -22133,13 +22147,13 @@
       <c r="D18" s="487" t="n"/>
       <c r="E18" s="445" t="inlineStr">
         <is>
-          <t>Same file - unreached, blocked by the preamble failure above.</t>
+          <t>UPDATE (2026-08-26): FIXED and confirmed passing live (real BrowserStack evidence, build 63157ac2...). Root cause was a non-deterministic HQ release-state race (a different, concurrent BrowserStack build's own setup/teardown could transiently un-release the build this flow needs 'released' to look stale) - fixed with a bounded logout+login retry loop, same pattern already proven for offline_09_uninstall_reinstall_test_two.yaml. No longer blocked by the preamble failure this note used to describe.</t>
         </is>
       </c>
       <c r="F18" s="445" t="n"/>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I18" s="672" t="inlineStr">
@@ -29234,16 +29248,25 @@
         </is>
       </c>
       <c r="D19" s="564" t="n"/>
-      <c r="E19" s="539" t="n"/>
+      <c r="E19" s="539" t="inlineStr">
+        <is>
+          <t>Automated via hq_client.py's get_prompt_update_settings(app_id) - an authenticated GET on the app's Releases page (where the Manage Update Options tab renders), parsed for each select's selected option (apk_prompt/apk_version/app_prompt/app_version). Verified live 2026-08-27 against '[Master] Basic Tests NS Copy' - returns real, non-null current settings, confirming the tab renders and the values are captured for later revert.</t>
+        </is>
+      </c>
       <c r="F19" s="204" t="n"/>
       <c r="H19" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I19" s="671" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>hq_setup/updates_2_49/setup_01_confirm_update_options_tab.json</t>
         </is>
       </c>
     </row>
@@ -29353,13 +29376,13 @@
       <c r="D22" s="564" t="n"/>
       <c r="E22" s="539" t="inlineStr">
         <is>
-          <t>Automated as part of a combined scenario with Prompted Update Scenario 1 (this is part 2/2: apk_prompt=forced). OPEN ISSUE (2026-08-24): on-device forced blocker does not appear even with HQ config confirmed correct via a live readback check - the optional prompt (Scenario 1) works correctly with the same dynamically-resolved CommCare version, forced does not trigger any prompt at all. Root cause not yet found.</t>
+          <t>Automated as part of a combined scenario with Prompted Update Scenario 1 (this is part 2/2: apk_prompt=forced). ROOT CAUSE FOUND AND FIXED (2026-08-25): set_prompt_update_settings() POSTs the whole form every call, so apk_version was silently reverting to 'latest' whenever apk_prompt flipped to forced. Fixed by pinning apk_version to the same AUTO_DEV_BUILD sentinel Setup 2 uses. Confirmed working end-to-end - forced blocker now appears as expected.</t>
         </is>
       </c>
       <c r="F22" s="204" t="n"/>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I22" s="672" t="inlineStr">

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -20142,7 +20142,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="0" t="inlineStr">
         <is>
           <t>scripts/appium_scenarios.py::run_scenario_1 (via scripts/run_appium_suite.py)</t>
         </is>
@@ -20361,7 +20361,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="0" t="inlineStr">
         <is>
           <t>scripts/appium_scenarios.py::run_scenario_2 (via scripts/run_appium_suite.py)</t>
         </is>
@@ -21336,7 +21336,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K35" s="0" t="inlineStr">
         <is>
           <t>scripts/appium_scenarios.py::run_scenario_5 (via scripts/run_appium_suite.py)</t>
         </is>
@@ -28535,17 +28535,26 @@
         <v/>
       </c>
       <c r="D10" s="387" t="n"/>
-      <c r="E10" s="387" t="n"/>
+      <c r="E10" s="387" t="inlineStr">
+        <is>
+          <t>Automated via hq_client.py's create_device_log_request(domain, username) - a plain django.contrib.admin add-form POST (GET the add page for its csrfmiddlewaretoken, POST domain+username+_save, confirm the 302-to-changelist success). Verified live 2026-08-27: created a real DeviceLogRequest row (domain=qateam, username=test1), confirmed present on the changelist; a second run correctly hit the model's unique(domain,username) constraint and was treated as idempotent success, not a failure.</t>
+        </is>
+      </c>
       <c r="F10" s="521" t="n"/>
       <c r="G10" s="60" t="n"/>
       <c r="H10" s="60" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I10" s="675" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>hq_setup/trigger_device_logs/device_logs_2_request.json</t>
         </is>
       </c>
     </row>
@@ -29264,7 +29273,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="0" t="inlineStr">
         <is>
           <t>hq_setup/updates_2_49/setup_01_confirm_update_options_tab.json</t>
         </is>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -24667,11 +24667,15 @@
         </is>
       </c>
       <c r="D20" s="564" t="n"/>
-      <c r="E20" s="521" t="n"/>
+      <c r="E20" s="521" t="inlineStr">
+        <is>
+          <t>Automated via scripts/verify_submission.py --username test1 --form-path Repeats (already-existing infra, now wired to this row): finds the most recent Repeats submission on Submit History and checks its Form Metadata (timeStart/timeEnd/etc.) is present and internally consistent (timeEnd &gt;= timeStart). Mechanism verified live 2026-08-27 against a real recent submission (a different form, same code path) - a fresh Repeats submission wasn't available in the last-20 search window at verification time, so re-confirm against this exact form the next time repeat_groups_01_05_add_and_submit.yaml runs.</t>
+        </is>
+      </c>
       <c r="F20" s="204" t="n"/>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J20" s="0" t="inlineStr">
@@ -24681,7 +24685,7 @@
       </c>
       <c r="K20" s="0" t="inlineStr">
         <is>
-          <t>flows/form_submissions/repeat_groups_01_05_add_and_submit.yaml</t>
+          <t>flows/form_submissions/repeat_groups_01_05_add_and_submit.yaml + scripts/verify_submission.py --username test1 --form-path Repeats</t>
         </is>
       </c>
     </row>
@@ -25545,16 +25549,25 @@
         </is>
       </c>
       <c r="D44" s="564" t="n"/>
-      <c r="E44" s="94" t="n"/>
+      <c r="E44" s="94" t="inlineStr">
+        <is>
+          <t>Automated via scripts/verify_submission.py --username test1 --form-path "Upload Tests for specific" --require-multimedia. Verified live 2026-08-27: found the real upload_test_1 submission and confirmed has_multimedia=True from its Submit History metadata.</t>
+        </is>
+      </c>
       <c r="F44" s="204" t="n"/>
       <c r="I44" s="0" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J44" s="0" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K44" s="0" t="inlineStr">
+        <is>
+          <t>scripts/verify_submission.py --username test1 --form-path "Upload Tests for specific" --require-multimedia</t>
         </is>
       </c>
     </row>
@@ -25639,11 +25652,15 @@
         </is>
       </c>
       <c r="D47" s="564" t="n"/>
-      <c r="E47" s="94" t="n"/>
+      <c r="E47" s="94" t="inlineStr">
+        <is>
+          <t>Steps 1-4 (submit a form, confirm a location value was captured) automated via scripts/verify_submission.py's new --require-location flag - checks the Submit History metadata tab's own 'location' field (which get_form_metadata() already surfaces) isn't the empty '---' placeholder. This flow reuses the shared 'Basic Form Tests &gt; Basic Form' form (same one device_logs_1_submit_form.yaml uses), so the breadcrumb alone can't disambiguate - pass --after &lt;a timestamp just before this flow runs&gt; alongside --form-path 'Basic Form' to target the right submission, not a bare form-path filter. Verified live 2026-08-27: correctly FAILED against a real submission with no captured location, confirming the check works (a submission with Auto Capture Location genuinely enabled wasn't available to confirm the positive case, same field-presence logic as the already-proven has_multimedia check). Steps 5-6 (cross-check the lat/long against a GPS converter site to confirm it matches the device's actual real-world location) remain a manual spot-check - out of scope for an automated assertion.</t>
+        </is>
+      </c>
       <c r="F47" s="204" t="n"/>
       <c r="I47" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J47" s="0" t="inlineStr">
@@ -25653,7 +25670,7 @@
       </c>
       <c r="K47" s="0" t="inlineStr">
         <is>
-          <t>flows/form_submissions/geoservice_02_auto_capture_location_submit.yaml</t>
+          <t>flows/form_submissions/geoservice_02_auto_capture_location_submit.yaml + scripts/verify_submission.py --username test1 --form-path "Basic Form" --after &lt;run start&gt; --require-location</t>
         </is>
       </c>
     </row>
@@ -28552,7 +28569,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="0" t="inlineStr">
         <is>
           <t>hq_setup/trigger_device_logs/device_logs_2_request.json</t>
         </is>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -11168,7 +11168,11 @@
         </is>
       </c>
       <c r="D62" s="387" t="n"/>
-      <c r="E62" s="296" t="n"/>
+      <c r="E62" s="296" t="inlineStr">
+        <is>
+          <t>Automated via scripts/run_appium_multimedia_suite.py (real infra gap, not on-device navigation uncertainty - see flows/multimedia/external_file_in_forms.yaml's own now-superseded header for the full citation): BrowserStack's Appium push_file places the real video at exactly /sdcard/Android/data/org.commcare.dalvik/media/yourvideo.mp4 (== the sheet's own /storage/emulated/0/... path) before driving the on-device navigation, closing the exact gap Maestro's addMedia can't reach. Real on-device text verified against the app's own CCZ (not guessed): the form is titled "Access file" (lowercase f), not "Access File". Verified live 2026-09-01: passed, with a real generated MP4 (cv2.VideoWriter, confirmed genuinely decodable) pushed and the link tap confirmed to hand off to an external app (driver.current_package check) rather than showing CommCare's own "No activity found" error.</t>
+        </is>
+      </c>
       <c r="F62" s="296" t="n"/>
       <c r="G62" s="311" t="n"/>
       <c r="H62" s="311" t="inlineStr">
@@ -11178,15 +11182,19 @@
       </c>
       <c r="I62" s="708" t="inlineStr">
         <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="J62" s="311" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="J62" s="311" t="inlineStr">
-        <is>
-          <t>flows/multimedia/external_file_in_forms.yaml</t>
-        </is>
-      </c>
-      <c r="K62" s="311" t="n"/>
+      <c r="K62" s="311" t="inlineStr">
+        <is>
+          <t>scripts/run_appium_multimedia_suite.py --scenario external_file_in_forms (flows/multimedia/external_file_in_forms.yaml kept for reference, tagged superseded_by_appium)</t>
+        </is>
+      </c>
       <c r="L62" s="311" t="n"/>
       <c r="M62" s="311" t="n"/>
       <c r="N62" s="311" t="n"/>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -10782,7 +10782,11 @@
         </is>
       </c>
       <c r="D54" s="387" t="n"/>
-      <c r="E54" s="296" t="n"/>
+      <c r="E54" s="296" t="inlineStr">
+        <is>
+          <t>Structurally not automatable via this repo's Maestro/BrowserStack pipeline: verifying a .aes extension requires filesystem access from inside the app process (opening a device file manager at android/data/.../formdata/&lt;id&gt;/), which the QA app under test has no way to expose to Maestro. Real automated coverage of this exact behavior already exists elsewhere: commcare-android repo, app/instrumentation-tests/src/org/commcare/androidTests/MediaEncryptionTest.kt, testImageEncryption()/testAudioEncryption() (Espresso, @BrowserstackTests, runs in that repo's own CI) - asserts an .aes file is present for captured media with encryption on, and absent with it off. Confirmed live 2026-09-01 by reading that file directly. Not automatable in this repo, but not an open gap either.</t>
+        </is>
+      </c>
       <c r="F54" s="296" t="n"/>
       <c r="G54" s="311" t="n"/>
       <c r="H54" s="311" t="inlineStr">
@@ -10792,7 +10796,7 @@
       </c>
       <c r="I54" s="678" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes (elsewhere - see Notes)</t>
         </is>
       </c>
       <c r="J54" s="311" t="n"/>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -35814,17 +35814,26 @@
         </is>
       </c>
       <c r="D10" s="137" t="n"/>
-      <c r="E10" s="522" t="n"/>
+      <c r="E10" s="522" t="inlineStr">
+        <is>
+          <t>Confirmed live 2026-09-01, by reading commcare-hq source directly, that neither this row nor "Check for new build" (row 13) needs a real device: "make a change" is HQClient.edit_module_attr() saving the app's draft content (module comment field - internal-only, never rendered on-device) without building. Automated end-to-end via scripts/run_update_content_change_check.py, which also drives row 13.</t>
+        </is>
+      </c>
       <c r="F10" s="522" t="n"/>
       <c r="G10" s="150" t="n"/>
       <c r="H10" s="124" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I10" s="665" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>scripts/run_update_content_change_check.py</t>
         </is>
       </c>
     </row>
@@ -35915,16 +35924,25 @@
         </is>
       </c>
       <c r="D13" s="137" t="n"/>
-      <c r="E13" s="479" t="n"/>
+      <c r="E13" s="479" t="inlineStr">
+        <is>
+          <t>Confirmed live 2026-09-01: this is CommCareHQ's own autogenerate_build() (corehq/apps/app_manager/tasks.py), which fires for ANY client - not specifically a phone - that fetches the app's live ODK profile (profile.ccpr) while its draft version is ahead of the latest saved build's. HQClient.check_for_phone_triggered_build() hits that same endpoint; a live test produced a real new build with comment starting "Auto-generated by a phone update", unreleased, matching this row's exact expected text and its "Do NOT star this build" note. Automated via scripts/run_update_content_change_check.py (same script as row 10 - both steps are one continuous HQ-API-only check, no device/Maestro flow).</t>
+        </is>
+      </c>
       <c r="F13" s="479" t="n"/>
       <c r="H13" s="124" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I13" s="665" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>scripts/run_update_content_change_check.py</t>
         </is>
       </c>
     </row>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -13818,7 +13818,7 @@
       <c r="D9" s="137" t="n"/>
       <c r="E9" s="308" t="inlineStr">
         <is>
-          <t>flows/support_menus/menu_02_force_log_submission.yaml - Partial because the sheet's own prerequisite (verify the app's logenabled=on_demand custom property via HQ) isn't introspectable on-device; flow assumes the build under test already satisfies it and only checks the on-device consequence (no 'Device Logs Pending' notification).</t>
+          <t>flows/support_menus/menu_02_force_log_submission.yaml (on-device consequence check) + scripts/run_support_menus_log_property_check.py (2026-09-01: the sheets own prerequisite - app does NOT have logenabled=on_demand set as a scheduling gate - is now actively VERIFIED via the new read-only HQClient.get_custom_properties(), not just assumed. Confirmed live: the real Basic Tests app already has logenabled=on_demand). Still Partial only because the verification is a separate HQ-API pre-check, not a single unified on-device assertion.</t>
         </is>
       </c>
       <c r="F9" s="308" t="n"/>
@@ -13835,7 +13835,7 @@
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t>flows/support_menus/menu_02_force_log_submission.yaml</t>
+          <t>flows/support_menus/menu_02_force_log_submission.yaml + scripts/run_support_menus_log_property_check.py</t>
         </is>
       </c>
     </row>
@@ -14816,14 +14816,14 @@
       <c r="D8" s="564" t="n"/>
       <c r="E8" s="387" t="inlineStr">
         <is>
-          <t>flows/session_expiration/setup_01_install_application.yaml - Partial because it needs a valid HQ web-user email/password to install the Session Expiration Test app by name.</t>
+          <t>flows/session_expiration/setup_01_install_application.yaml - RECLASSIFIED Automatable (2026-09-01, corrected a stale Partial claim): install_app_by_code.yaml resolves APP_CODE_SESSION_EXPIRATION server-side via the same HQ_WEB_USER_EMAIL/PASSWORD every other app-code flow in this suite already uses (resolve_app_codes(), once per run) - no live on-device email/password entry, unlike Install 8s genuinely different web-user-login mechanism. Confirmed passing live.</t>
         </is>
       </c>
       <c r="F8" s="387" t="n"/>
       <c r="G8" s="216" t="n"/>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
@@ -14860,14 +14860,14 @@
       <c r="D9" s="564" t="n"/>
       <c r="E9" s="387" t="inlineStr">
         <is>
-          <t>This test case is to ensure the session expiration message appears.</t>
+          <t>flows/session_expiration/setup_02_restore_user_session_expires.yaml - RECLASSIFIED Automatable (2026-09-01), same correction as Setup 1. Confirmed passing live: session-expiration notification appears, and the app genuinely logs out back to the login screen once the real 45-second window elapses.</t>
         </is>
       </c>
       <c r="F9" s="387" t="n"/>
       <c r="G9" s="216" t="n"/>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
@@ -24728,7 +24728,7 @@
       <c r="F21" s="204" t="n"/>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Steps 1-3 (on-device navigation + submit) automated in flows/form_submissions/markdown_page_through_and_submit.yaml. Steps 4-7 (Submit History metadata verification) closed 2026-09-01 via scripts/run_form_submission_history_check.py --test-name markdown --username test1 --form-path-contains Markdown (find_recent_submission + get_form_metadata, confirmed live against a real submission - timeStart/timeEnd both present and sane). The rendered-markdown visual-quality check (step 2) stays a documented gap - no text/accessibility-tree equivalent Maestro can assert.</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
@@ -25070,7 +25070,7 @@
       <c r="F30" s="204" t="n"/>
       <c r="I30" s="0" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Closed 2026-09-01 via scripts/run_form_submission_history_check.py --test-name incomplete_forms_4 --username test1 --form-path-contains "Question Types" (NOT "Incomplete" - confirmed live that Incomplete is only the home-screen resume-card label, the real Submit History breadcrumb is [Master] Basic Tests &gt; Basic Form Tests &gt; Question Types, per incomplete_forms_01_03_save_resume_submit.yaml own form-path citation). find_recent_submission + get_form_metadata confirmed live against the real submission - timeStart/timeEnd present, sane, and matching the actual dispatch window.</t>
         </is>
       </c>
       <c r="J30" s="0" t="inlineStr">
@@ -28605,17 +28605,26 @@
         </is>
       </c>
       <c r="D11" s="387" t="n"/>
-      <c r="E11" s="387" t="n"/>
+      <c r="E11" s="387" t="inlineStr">
+        <is>
+          <t>RECLASSIFIED Partial (2026-09-01): this rows own pass criteria is just the on-device trigger action (login + sync) - the Not automatable verdict actually belonged to the separate Device Logs 4 row (Sumo Logic dashboard validation, a real external system with no API access here). flows/trigger_device_logs/device_logs_3_trigger.yaml automates login+sync, confirmed passing live. Deliberately does not wait the full 10 real minutes - nothing on-device is checked after Sync Successful, since Sumo receipt is out of scope here.</t>
+        </is>
+      </c>
       <c r="F11" s="521" t="n"/>
       <c r="G11" s="60" t="n"/>
       <c r="H11" s="60" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I11" s="675" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>flows/trigger_device_logs/device_logs_3_trigger.yaml</t>
         </is>
       </c>
     </row>
@@ -35831,7 +35840,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="0" t="inlineStr">
         <is>
           <t>scripts/run_update_content_change_check.py</t>
         </is>
@@ -35940,7 +35949,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="0" t="inlineStr">
         <is>
           <t>scripts/run_update_content_change_check.py</t>
         </is>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -24724,11 +24724,15 @@
         </is>
       </c>
       <c r="D21" s="564" t="n"/>
-      <c r="E21" s="521" t="n"/>
+      <c r="E21" s="521" t="inlineStr">
+        <is>
+          <t>Steps 1-3 (on-device navigation + submit) automated in flows/form_submissions/markdown_page_through_and_submit.yaml. Steps 4-7 (Submit History metadata verification) closed 2026-09-01 via scripts/run_form_submission_history_check.py --test-name markdown --username test1 --form-path-contains Markdown (find_recent_submission + get_form_metadata, confirmed live against a real submission - timeStart/timeEnd both present and sane). The rendered-markdown visual-quality check (step 2) stays a documented gap - no text/accessibility-tree equivalent Maestro can assert.</t>
+        </is>
+      </c>
       <c r="F21" s="204" t="n"/>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t>Steps 1-3 (on-device navigation + submit) automated in flows/form_submissions/markdown_page_through_and_submit.yaml. Steps 4-7 (Submit History metadata verification) closed 2026-09-01 via scripts/run_form_submission_history_check.py --test-name markdown --username test1 --form-path-contains Markdown (find_recent_submission + get_form_metadata, confirmed live against a real submission - timeStart/timeEnd both present and sane). The rendered-markdown visual-quality check (step 2) stays a documented gap - no text/accessibility-tree equivalent Maestro can assert.</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
@@ -25066,11 +25070,15 @@
         </is>
       </c>
       <c r="D30" s="564" t="n"/>
-      <c r="E30" s="457" t="n"/>
+      <c r="E30" s="457" t="inlineStr">
+        <is>
+          <t>Closed 2026-09-01 via scripts/run_form_submission_history_check.py --test-name incomplete_forms_4 --username test1 --form-path-contains "Question Types" (NOT "Incomplete" - confirmed live that Incomplete is only the home-screen resume-card label, the real Submit History breadcrumb is [Master] Basic Tests &gt; Basic Form Tests &gt; Question Types, per incomplete_forms_01_03_save_resume_submit.yaml own form-path citation). find_recent_submission + get_form_metadata confirmed live against the real submission - timeStart/timeEnd present, sane, and matching the actual dispatch window.</t>
+        </is>
+      </c>
       <c r="F30" s="204" t="n"/>
       <c r="I30" s="0" t="inlineStr">
         <is>
-          <t>Closed 2026-09-01 via scripts/run_form_submission_history_check.py --test-name incomplete_forms_4 --username test1 --form-path-contains "Question Types" (NOT "Incomplete" - confirmed live that Incomplete is only the home-screen resume-card label, the real Submit History breadcrumb is [Master] Basic Tests &gt; Basic Form Tests &gt; Question Types, per incomplete_forms_01_03_save_resume_submit.yaml own form-path citation). find_recent_submission + get_form_metadata confirmed live against the real submission - timeStart/timeEnd present, sane, and matching the actual dispatch window.</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="J30" s="0" t="inlineStr">
@@ -34909,19 +34917,27 @@
         </is>
       </c>
       <c r="F9" s="94" t="n"/>
-      <c r="G9" s="94" t="n"/>
+      <c r="G9" s="94" t="inlineStr">
+        <is>
+          <t>Steps 4-6 (camera-scan a QR barcode off an HQ desktop page) stay genuinely untested - same confirmed camera-image-injection dead end as Mobile Pins' own QR-claim step. But the row's real intent (publish + include-media, install, reach the login screen) is fully covered another way: the barcode encodes the identical short code HQ's own "Enter Code" panel shows alongside it (get_app_install_code, include_media=True). Closed 2026-09-01 via flows/install/install_01_scan_barcode.yaml (install_app_by_code.yaml + that code), confirmed live.</t>
+        </is>
+      </c>
       <c r="H9" s="106" t="n"/>
       <c r="I9" s="45" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J9" s="658" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="45" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="45" t="inlineStr">
+        <is>
+          <t>flows/install/install_01_scan_barcode.yaml</t>
+        </is>
+      </c>
       <c r="L9" s="45" t="n"/>
       <c r="M9" s="45" t="n"/>
       <c r="N9" s="45" t="n"/>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -10080,20 +10080,28 @@
         </is>
       </c>
       <c r="D41" s="387" t="n"/>
-      <c r="E41" s="296" t="n"/>
+      <c r="E41" s="296" t="inlineStr">
+        <is>
+          <t>Step 6 ("verify you can download the attachments") closed 2026-09-07 via scripts/run_multimedia_form_data_check.py --check-type attachments (new HQClient.get_form_attachments(), parses the real #form-attachments tab, confirms each attachment is present with a real non-zero Content-Length). Step 7 ("verify the image is sized as expected... small/medium/large/original") stays NOT verifiable: confirmed live against a real submission that every question's attachment came back byte-identical (75 bytes) since BrowserStack test devices all pick the same tiny placeholder gallery image - no real resize-magnitude signal exists to assert on with this test asset, same class of limitation as the sibling Image Resize rows.</t>
+        </is>
+      </c>
       <c r="F41" s="296" t="n"/>
       <c r="G41" s="311" t="n"/>
       <c r="H41" s="311" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I41" s="678" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J41" s="311" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J41" s="311" t="inlineStr">
+        <is>
+          <t>flows/multimedia/image_resize_25_photo_taken.yaml + scripts/run_multimedia_form_data_check.py</t>
+        </is>
+      </c>
       <c r="K41" s="311" t="n"/>
       <c r="L41" s="311" t="n"/>
       <c r="M41" s="311" t="n"/>
@@ -10134,20 +10142,28 @@
         </is>
       </c>
       <c r="D42" s="387" t="n"/>
-      <c r="E42" s="296" t="n"/>
+      <c r="E42" s="296" t="inlineStr">
+        <is>
+          <t>Step 6 ("verify you can download the attachments") closed 2026-09-07 via scripts/run_multimedia_form_data_check.py --check-type attachments (new HQClient.get_form_attachments(), parses the real #form-attachments tab, confirms each attachment is present with a real non-zero Content-Length). Step 7 ("verify the image is sized as expected... small/medium/large/original") stays NOT verifiable: confirmed live against a real submission that every question's attachment came back byte-identical (75 bytes) since BrowserStack test devices all pick the same tiny placeholder gallery image - no real resize-magnitude signal exists to assert on with this test asset, same class of limitation as the sibling Image Resize rows.</t>
+        </is>
+      </c>
       <c r="F42" s="296" t="n"/>
       <c r="G42" s="311" t="n"/>
       <c r="H42" s="311" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I42" s="678" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J42" s="311" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J42" s="311" t="inlineStr">
+        <is>
+          <t>flows/multimedia/image_resize_26_photo_chosen.yaml + scripts/run_multimedia_form_data_check.py</t>
+        </is>
+      </c>
       <c r="K42" s="311" t="n"/>
       <c r="L42" s="311" t="n"/>
       <c r="M42" s="311" t="n"/>
@@ -10402,20 +10418,28 @@
         </is>
       </c>
       <c r="D47" s="387" t="n"/>
-      <c r="E47" s="296" t="n"/>
+      <c r="E47" s="296" t="inlineStr">
+        <is>
+          <t>Steps 1-2 (on-device submit) already automated in photo_02_can_remove_chosen_photo.yaml. Step 3 closed 2026-09-07 via scripts/run_multimedia_form_data_check.py --check-type unanswered --form-path-contains "Gif/Remove Image" --expect-unanswered "Take a photo" --expect-unanswered "Choose Image" (new HQClient.get_form_answers(), parses the real Question/Response table on the Form Data page - confirmed live both questions show blank).</t>
+        </is>
+      </c>
       <c r="F47" s="296" t="n"/>
       <c r="G47" s="311" t="n"/>
       <c r="H47" s="311" t="inlineStr">
         <is>
-          <t>Not automatable</t>
+          <t>Automatable</t>
         </is>
       </c>
       <c r="I47" s="678" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J47" s="311" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J47" s="311" t="inlineStr">
+        <is>
+          <t>flows/multimedia/photo_02_can_remove_chosen_photo.yaml + scripts/run_multimedia_form_data_check.py</t>
+        </is>
+      </c>
       <c r="K47" s="311" t="n"/>
       <c r="L47" s="311" t="n"/>
       <c r="M47" s="311" t="n"/>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -15183,7 +15183,7 @@
       <c r="D10" s="564" t="n"/>
       <c r="E10" s="387" t="inlineStr">
         <is>
-          <t>flows/conditional_enum_in_case_list/conditional_id_mapping_01_06_full_scenario.yaml (all 6 rows run as one sequential narrative). Partial: 'Test Two's appointment date must be set to yesterday via a native spinner DatePicker with no Maestro-native 'set date' action - a best-effort decrement-day swipe is used, unverified against a live run.</t>
+          <t>flows/conditional_enum_in_case_list/conditional_id_mapping_01_06_full_scenario.yaml (all 6 rows run as one sequential narrative). Partial: 'Test Two's appointment date is set to yesterday via a native spinner DatePicker with no Maestro-native 'set date' action - a best-effort decrement-day swipe is used. Confirmed live 2026-09-07 (build 1238bc320e7cfe912230812759586400c0bfb383): the swipe works, downstream computed-property assertions passed. Still Partial due to a SEPARATE, unrelated issue: this shared qateam-domain case list accumulates thousands of prior runs' Test One/Test Two cases with no cleanup, making case-name lookups increasingly ambiguous over time - a test-hygiene issue, not a Maestro capability gap.</t>
         </is>
       </c>
       <c r="F10" s="387" t="n"/>

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -8238,7 +8238,11 @@
         </is>
       </c>
       <c r="D8" s="387" t="n"/>
-      <c r="E8" s="253" t="n"/>
+      <c r="E8" s="253" t="inlineStr">
+        <is>
+          <t>Not automatable (currently paused pending a real multimedia zip/CCZ file): requires manually connecting the device to a computer, moving a specific file within the app's media directory via a file manager, and toggling network/uninstall state - genuinely reachable via Appium's real file-push capability (already proven for CCZ files elsewhere in this program), but blocked on obtaining the right multimedia zip asset. Explicitly paused per direct user instruction this session ('it will need a ccz file... I will get the ccz file') - not a hard technical dead end.</t>
+        </is>
+      </c>
       <c r="F8" s="253" t="n"/>
       <c r="G8" s="60" t="n"/>
       <c r="H8" s="60" t="inlineStr">
@@ -8295,7 +8299,11 @@
         </is>
       </c>
       <c r="D9" s="387" t="n"/>
-      <c r="E9" s="249" t="n"/>
+      <c r="E9" s="249" t="inlineStr">
+        <is>
+          <t>Not automatable (currently paused pending a real multimedia zip/CCZ file): requires manually connecting the device to a computer, moving a specific file within the app's media directory via a file manager, and toggling network/uninstall state - genuinely reachable via Appium's real file-push capability (already proven for CCZ files elsewhere in this program), but blocked on obtaining the right multimedia zip asset. Explicitly paused per direct user instruction this session ('it will need a ccz file... I will get the ccz file') - not a hard technical dead end.</t>
+        </is>
+      </c>
       <c r="F9" s="249" t="n"/>
       <c r="G9" s="60" t="n"/>
       <c r="H9" s="60" t="inlineStr">
@@ -8349,7 +8357,11 @@
         </is>
       </c>
       <c r="D10" s="387" t="n"/>
-      <c r="E10" s="249" t="n"/>
+      <c r="E10" s="249" t="inlineStr">
+        <is>
+          <t>Not automatable (currently paused pending a real multimedia zip/CCZ file): requires manually connecting the device to a computer, moving a specific file within the app's media directory via a file manager, and toggling network/uninstall state - genuinely reachable via Appium's real file-push capability (already proven for CCZ files elsewhere in this program), but blocked on obtaining the right multimedia zip asset. Explicitly paused per direct user instruction this session ('it will need a ccz file... I will get the ccz file') - not a hard technical dead end.</t>
+        </is>
+      </c>
       <c r="F10" s="249" t="n"/>
       <c r="G10" s="60" t="n"/>
       <c r="H10" s="60" t="inlineStr">
@@ -8402,7 +8414,11 @@
         </is>
       </c>
       <c r="D11" s="387" t="n"/>
-      <c r="E11" s="249" t="n"/>
+      <c r="E11" s="249" t="inlineStr">
+        <is>
+          <t>Partial: navigation/tap/checkbox steps are fully automated (flows/multimedia/mm4_question_types.yaml); whether the audio actually plays correctly is a human judgment call, deliberately skipped per coverage_matrix.csv.</t>
+        </is>
+      </c>
       <c r="F11" s="249" t="n"/>
       <c r="G11" s="60" t="n"/>
       <c r="H11" s="60" t="inlineStr">
@@ -8459,7 +8475,11 @@
         </is>
       </c>
       <c r="D12" s="387" t="n"/>
-      <c r="E12" s="249" t="n"/>
+      <c r="E12" s="249" t="inlineStr">
+        <is>
+          <t>Not automatable (currently paused pending a real multimedia zip/CCZ file): requires manually connecting the device to a computer, moving a specific file within the app's media directory via a file manager, and toggling network/uninstall state - genuinely reachable via Appium's real file-push capability (already proven for CCZ files elsewhere in this program), but blocked on obtaining the right multimedia zip asset. Explicitly paused per direct user instruction this session ('it will need a ccz file... I will get the ccz file') - not a hard technical dead end.</t>
+        </is>
+      </c>
       <c r="F12" s="249" t="n"/>
       <c r="G12" s="60" t="n"/>
       <c r="H12" s="60" t="inlineStr">
@@ -8510,7 +8530,11 @@
         </is>
       </c>
       <c r="D13" s="387" t="n"/>
-      <c r="E13" s="249" t="n"/>
+      <c r="E13" s="249" t="inlineStr">
+        <is>
+          <t>Not automatable (currently paused pending a real multimedia zip/CCZ file): requires manually connecting the device to a computer, moving a specific file within the app's media directory via a file manager, and toggling network/uninstall state - genuinely reachable via Appium's real file-push capability (already proven for CCZ files elsewhere in this program), but blocked on obtaining the right multimedia zip asset. Explicitly paused per direct user instruction this session ('it will need a ccz file... I will get the ccz file') - not a hard technical dead end.</t>
+        </is>
+      </c>
       <c r="F13" s="249" t="n"/>
       <c r="G13" s="60" t="n"/>
       <c r="H13" s="60" t="inlineStr">
@@ -8562,7 +8586,11 @@
         </is>
       </c>
       <c r="D14" s="387" t="n"/>
-      <c r="E14" s="249" t="n"/>
+      <c r="E14" s="249" t="inlineStr">
+        <is>
+          <t>Partial: icon-visible assertions are fully automated (flows/multimedia/icons_module_form_icons.yaml); whether the audio actually plays correctly back is a human judgment call, deliberately skipped per coverage_matrix.csv.</t>
+        </is>
+      </c>
       <c r="F14" s="249" t="n"/>
       <c r="G14" s="60" t="n"/>
       <c r="H14" s="60" t="inlineStr">
@@ -8618,7 +8646,11 @@
         </is>
       </c>
       <c r="D15" s="387" t="n"/>
-      <c r="E15" s="249" t="n"/>
+      <c r="E15" s="249" t="inlineStr">
+        <is>
+          <t>Partial: automated (flows/multimedia/image_resize_01_04_default_setting.yaml) for the default Auto-Resize setting; verifying the actual pixel dimensions/visual size of each image is out of scope (visual-rendering judgment, not accessibility-tree text).</t>
+        </is>
+      </c>
       <c r="F15" s="249" t="n"/>
       <c r="G15" s="60" t="n"/>
       <c r="H15" s="60" t="inlineStr">
@@ -8673,7 +8705,11 @@
         </is>
       </c>
       <c r="D16" s="387" t="n"/>
-      <c r="E16" s="249" t="n"/>
+      <c r="E16" s="249" t="inlineStr">
+        <is>
+          <t>Partial: same as Image Resize 1 - flows/multimedia/image_resize_01_04_default_setting.yaml covers navigation/presence, not pixel-size verification.</t>
+        </is>
+      </c>
       <c r="F16" s="249" t="n"/>
       <c r="G16" s="60" t="n"/>
       <c r="H16" s="60" t="inlineStr">
@@ -8728,7 +8764,11 @@
         </is>
       </c>
       <c r="D17" s="387" t="n"/>
-      <c r="E17" s="249" t="n"/>
+      <c r="E17" s="249" t="inlineStr">
+        <is>
+          <t>Partial: same as Image Resize 1 - flows/multimedia/image_resize_01_04_default_setting.yaml covers navigation/presence, not pixel-size verification.</t>
+        </is>
+      </c>
       <c r="F17" s="249" t="n"/>
       <c r="G17" s="60" t="n"/>
       <c r="H17" s="60" t="inlineStr">
@@ -8783,7 +8823,11 @@
         </is>
       </c>
       <c r="D18" s="387" t="n"/>
-      <c r="E18" s="249" t="n"/>
+      <c r="E18" s="249" t="inlineStr">
+        <is>
+          <t>Partial: same as Image Resize 1 - flows/multimedia/image_resize_01_04_default_setting.yaml covers navigation/presence, not pixel-size verification.</t>
+        </is>
+      </c>
       <c r="F18" s="249" t="n"/>
       <c r="G18" s="60" t="n"/>
       <c r="H18" s="60" t="inlineStr">
@@ -8844,7 +8888,11 @@
         </is>
       </c>
       <c r="D19" s="387" t="n"/>
-      <c r="E19" s="249" t="n"/>
+      <c r="E19" s="249" t="inlineStr">
+        <is>
+          <t>Not automatable: the HQ-side 'Auto-Resize Images' setting change couldn't be verified - its underlying custom_properties key/value spelling isn't confirmed anywhere in this repo or the read-only commcare-android source (that setting lives purely on the HQ/Django side). See hq_setup/multimedia/image_resize_full_resize.json's own citation for what's blocking it.</t>
+        </is>
+      </c>
       <c r="F19" s="249" t="n"/>
       <c r="G19" s="60" t="n"/>
       <c r="H19" s="60" t="inlineStr">
@@ -8900,7 +8948,11 @@
         </is>
       </c>
       <c r="D20" s="387" t="n"/>
-      <c r="E20" s="249" t="n"/>
+      <c r="E20" s="249" t="inlineStr">
+        <is>
+          <t>Partial: automated (flows/multimedia/image_resize_06_09_full_resize.yaml), sequenced after Image Resize 5's HQ setting change; same pixel-size-verification-out-of-scope caveat as Image Resize 1-4.</t>
+        </is>
+      </c>
       <c r="F20" s="249" t="n"/>
       <c r="G20" s="60" t="n"/>
       <c r="H20" s="60" t="inlineStr">
@@ -8956,7 +9008,11 @@
         </is>
       </c>
       <c r="D21" s="387" t="n"/>
-      <c r="E21" s="249" t="n"/>
+      <c r="E21" s="249" t="inlineStr">
+        <is>
+          <t>Partial: same as Image Resize 6 - navigation/presence only, not pixel-size verification.</t>
+        </is>
+      </c>
       <c r="F21" s="249" t="n"/>
       <c r="G21" s="60" t="n"/>
       <c r="H21" s="60" t="inlineStr">
@@ -9012,7 +9068,11 @@
         </is>
       </c>
       <c r="D22" s="387" t="n"/>
-      <c r="E22" s="249" t="n"/>
+      <c r="E22" s="249" t="inlineStr">
+        <is>
+          <t>Partial: same as Image Resize 6 - navigation/presence only, not pixel-size verification.</t>
+        </is>
+      </c>
       <c r="F22" s="249" t="n"/>
       <c r="G22" s="60" t="n"/>
       <c r="H22" s="60" t="inlineStr">
@@ -9068,7 +9128,11 @@
         </is>
       </c>
       <c r="D23" s="387" t="n"/>
-      <c r="E23" s="249" t="n"/>
+      <c r="E23" s="249" t="inlineStr">
+        <is>
+          <t>Partial: same as Image Resize 6 - navigation/presence only, not pixel-size verification.</t>
+        </is>
+      </c>
       <c r="F23" s="249" t="n"/>
       <c r="G23" s="60" t="n"/>
       <c r="H23" s="60" t="inlineStr">
@@ -9129,7 +9193,11 @@
         </is>
       </c>
       <c r="D24" s="387" t="n"/>
-      <c r="E24" s="249" t="n"/>
+      <c r="E24" s="249" t="inlineStr">
+        <is>
+          <t>Not automatable: same unverified custom_properties key/value gap as Image Resize 5, for the 'Horizontal Resize' setting - see hq_setup/multimedia/image_resize_horizontal_resize.json.</t>
+        </is>
+      </c>
       <c r="F24" s="249" t="n"/>
       <c r="G24" s="60" t="n"/>
       <c r="H24" s="60" t="inlineStr">
@@ -9185,7 +9253,11 @@
         </is>
       </c>
       <c r="D25" s="387" t="n"/>
-      <c r="E25" s="249" t="n"/>
+      <c r="E25" s="249" t="inlineStr">
+        <is>
+          <t>Partial: automated (flows/multimedia/image_resize_11_14_horizontal_resize.yaml), sequenced after Image Resize 10's HQ setting change; same pixel-size-verification-out-of-scope caveat.</t>
+        </is>
+      </c>
       <c r="F25" s="249" t="n"/>
       <c r="G25" s="60" t="n"/>
       <c r="H25" s="60" t="inlineStr">
@@ -9240,7 +9312,11 @@
         </is>
       </c>
       <c r="D26" s="387" t="n"/>
-      <c r="E26" s="249" t="n"/>
+      <c r="E26" s="249" t="inlineStr">
+        <is>
+          <t>Partial: same as Image Resize 11 - navigation/presence only, not pixel-size verification.</t>
+        </is>
+      </c>
       <c r="F26" s="249" t="n"/>
       <c r="G26" s="60" t="n"/>
       <c r="H26" s="60" t="inlineStr">
@@ -9295,7 +9371,11 @@
         </is>
       </c>
       <c r="D27" s="387" t="n"/>
-      <c r="E27" s="249" t="n"/>
+      <c r="E27" s="249" t="inlineStr">
+        <is>
+          <t>Partial: same as Image Resize 11 - navigation/presence only, not pixel-size verification.</t>
+        </is>
+      </c>
       <c r="F27" s="249" t="n"/>
       <c r="G27" s="60" t="n"/>
       <c r="H27" s="60" t="inlineStr">
@@ -9350,7 +9430,11 @@
         </is>
       </c>
       <c r="D28" s="387" t="n"/>
-      <c r="E28" s="249" t="n"/>
+      <c r="E28" s="249" t="inlineStr">
+        <is>
+          <t>Partial: same as Image Resize 11 - navigation/presence only, not pixel-size verification.</t>
+        </is>
+      </c>
       <c r="F28" s="249" t="n"/>
       <c r="G28" s="60" t="n"/>
       <c r="H28" s="60" t="inlineStr">
@@ -9411,7 +9495,11 @@
         </is>
       </c>
       <c r="D29" s="387" t="n"/>
-      <c r="E29" s="249" t="n"/>
+      <c r="E29" s="249" t="inlineStr">
+        <is>
+          <t>Not automatable: same unverified custom_properties key/value gap as Image Resize 5, for the 'Half Resize' setting - see hq_setup/multimedia/image_resize_half_resize.json.</t>
+        </is>
+      </c>
       <c r="F29" s="249" t="n"/>
       <c r="G29" s="60" t="n"/>
       <c r="H29" s="60" t="inlineStr">
@@ -9467,7 +9555,11 @@
         </is>
       </c>
       <c r="D30" s="387" t="n"/>
-      <c r="E30" s="249" t="n"/>
+      <c r="E30" s="249" t="inlineStr">
+        <is>
+          <t>Partial: automated (flows/multimedia/image_resize_16_19_half_resize.yaml), sequenced after Image Resize 15's HQ setting change; same pixel-size-verification-out-of-scope caveat.</t>
+        </is>
+      </c>
       <c r="F30" s="249" t="n"/>
       <c r="G30" s="60" t="n"/>
       <c r="H30" s="60" t="inlineStr">
@@ -9522,7 +9614,11 @@
         </is>
       </c>
       <c r="D31" s="387" t="n"/>
-      <c r="E31" s="249" t="n"/>
+      <c r="E31" s="249" t="inlineStr">
+        <is>
+          <t>Partial: same as Image Resize 16 - navigation/presence only, not pixel-size verification.</t>
+        </is>
+      </c>
       <c r="F31" s="249" t="n"/>
       <c r="G31" s="60" t="n"/>
       <c r="H31" s="60" t="inlineStr">
@@ -9577,7 +9673,11 @@
         </is>
       </c>
       <c r="D32" s="387" t="n"/>
-      <c r="E32" s="521" t="n"/>
+      <c r="E32" s="521" t="inlineStr">
+        <is>
+          <t>Partial: same as Image Resize 16 - navigation/presence only, not pixel-size verification.</t>
+        </is>
+      </c>
       <c r="F32" s="521" t="n"/>
       <c r="G32" s="60" t="n"/>
       <c r="H32" s="60" t="inlineStr">
@@ -9632,7 +9732,11 @@
         </is>
       </c>
       <c r="D33" s="387" t="n"/>
-      <c r="E33" s="521" t="n"/>
+      <c r="E33" s="521" t="inlineStr">
+        <is>
+          <t>Partial: same as Image Resize 16 - navigation/presence only, not pixel-size verification.</t>
+        </is>
+      </c>
       <c r="F33" s="521" t="n"/>
       <c r="G33" s="60" t="n"/>
       <c r="H33" s="60" t="inlineStr">
@@ -9693,7 +9797,11 @@
         </is>
       </c>
       <c r="D34" s="387" t="n"/>
-      <c r="E34" s="521" t="n"/>
+      <c r="E34" s="521" t="inlineStr">
+        <is>
+          <t>Not automatable: same unverified custom_properties key/value gap as Image Resize 5, for restoring 'None' - see hq_setup/multimedia/image_resize_none_resize.json.</t>
+        </is>
+      </c>
       <c r="F34" s="521" t="n"/>
       <c r="G34" s="60" t="n"/>
       <c r="H34" s="60" t="inlineStr">
@@ -9749,7 +9857,11 @@
         </is>
       </c>
       <c r="D35" s="387" t="n"/>
-      <c r="E35" s="521" t="n"/>
+      <c r="E35" s="521" t="inlineStr">
+        <is>
+          <t>Partial: automated (flows/multimedia/image_resize_21_24_none_resize.yaml), sequenced after Image Resize 20's HQ setting restore; same pixel-size-verification-out-of-scope caveat.</t>
+        </is>
+      </c>
       <c r="F35" s="521" t="n"/>
       <c r="G35" s="60" t="n"/>
       <c r="H35" s="60" t="inlineStr">
@@ -9804,7 +9916,11 @@
         </is>
       </c>
       <c r="D36" s="387" t="n"/>
-      <c r="E36" s="521" t="n"/>
+      <c r="E36" s="521" t="inlineStr">
+        <is>
+          <t>Partial: same as Image Resize 21 - navigation/presence only, not pixel-size verification.</t>
+        </is>
+      </c>
       <c r="F36" s="521" t="n"/>
       <c r="G36" s="60" t="n"/>
       <c r="H36" s="60" t="inlineStr">
@@ -9859,7 +9975,11 @@
         </is>
       </c>
       <c r="D37" s="387" t="n"/>
-      <c r="E37" s="521" t="n"/>
+      <c r="E37" s="521" t="inlineStr">
+        <is>
+          <t>Partial: same as Image Resize 21 - navigation/presence only, not pixel-size verification.</t>
+        </is>
+      </c>
       <c r="F37" s="521" t="n"/>
       <c r="G37" s="60" t="n"/>
       <c r="H37" s="60" t="inlineStr">
@@ -9914,7 +10034,11 @@
         </is>
       </c>
       <c r="D38" s="387" t="n"/>
-      <c r="E38" s="521" t="n"/>
+      <c r="E38" s="521" t="inlineStr">
+        <is>
+          <t>Partial: same as Image Resize 21 - navigation/presence only, not pixel-size verification.</t>
+        </is>
+      </c>
       <c r="F38" s="521" t="n"/>
       <c r="G38" s="60" t="n"/>
       <c r="H38" s="60" t="inlineStr">
@@ -9968,7 +10092,11 @@
         </is>
       </c>
       <c r="D39" s="387" t="n"/>
-      <c r="E39" s="296" t="n"/>
+      <c r="E39" s="296" t="inlineStr">
+        <is>
+          <t>Partial: real camera capture confirmed flaky/unsupported on most BrowserStack device images (flows/multimedia/image_resize_25_photo_taken.yaml flags this explicitly, same caveat as Photo 1) - best-effort, not fully reliable.</t>
+        </is>
+      </c>
       <c r="F39" s="296" t="n"/>
       <c r="G39" s="311" t="n"/>
       <c r="H39" s="311" t="inlineStr">
@@ -10200,7 +10328,11 @@
         </is>
       </c>
       <c r="D43" s="387" t="n"/>
-      <c r="E43" s="296" t="n"/>
+      <c r="E43" s="296" t="inlineStr">
+        <is>
+          <t>Not automatable: requires actually watching video playback behave correctly (external media-player chooser vs. inline playback) - a visual/media-rendering judgment call, same class of human-judgment-only gap as this tab's own audio-plays-correctly checks.</t>
+        </is>
+      </c>
       <c r="F43" s="296" t="n"/>
       <c r="G43" s="311" t="n"/>
       <c r="H43" s="311" t="inlineStr">
@@ -10249,7 +10381,11 @@
         </is>
       </c>
       <c r="D44" s="387" t="n"/>
-      <c r="E44" s="296" t="n"/>
+      <c r="E44" s="296" t="inlineStr">
+        <is>
+          <t>Partial: automated (flows/multimedia/gif_can_add_gif.yaml) for the gif's presence; whether it's actually animating (vs. a static frame) is a human judgment call, deliberately skipped per coverage_matrix.csv.</t>
+        </is>
+      </c>
       <c r="F44" s="296" t="n"/>
       <c r="G44" s="311" t="n"/>
       <c r="H44" s="311" t="inlineStr">
@@ -10306,7 +10442,11 @@
         </is>
       </c>
       <c r="D45" s="387" t="n"/>
-      <c r="E45" s="296" t="n"/>
+      <c r="E45" s="296" t="inlineStr">
+        <is>
+          <t>Partial: real camera capture confirmed flaky/unsupported on most BrowserStack device images - same caveat as Image Resize 25 (flows/multimedia/photo_01_can_remove_taken_photo.yaml).</t>
+        </is>
+      </c>
       <c r="F45" s="296" t="n"/>
       <c r="G45" s="311" t="n"/>
       <c r="H45" s="311" t="inlineStr">
@@ -10482,7 +10622,11 @@
         </is>
       </c>
       <c r="D48" s="387" t="n"/>
-      <c r="E48" s="296" t="n"/>
+      <c r="E48" s="296" t="inlineStr">
+        <is>
+          <t>Not automatable: requires visually comparing image density/appearance across a specific 'low end' vs 'high end' physical device pair - BrowserStack's device pool is named specific models, not officially tiered low/high end, and the actual check is a pixel/visual-rendering judgment this stack has no assertion path for.</t>
+        </is>
+      </c>
       <c r="F48" s="296" t="n"/>
       <c r="G48" s="311" t="n"/>
       <c r="H48" s="311" t="inlineStr">
@@ -10701,7 +10845,11 @@
         </is>
       </c>
       <c r="D52" s="387" t="n"/>
-      <c r="E52" s="296" t="n"/>
+      <c r="E52" s="296" t="inlineStr">
+        <is>
+          <t>Not automatable: requires picking a third-party app from Android's share/intent chooser to play or view attached media - installing/selecting an arbitrary third-party app with no internal APK source is a confirmed hard limit of this pipeline (same class of gap as Third Party Scanner).</t>
+        </is>
+      </c>
       <c r="F52" s="296" t="n"/>
       <c r="G52" s="311" t="n"/>
       <c r="H52" s="311" t="inlineStr">
@@ -10752,7 +10900,11 @@
         </is>
       </c>
       <c r="D53" s="387" t="n"/>
-      <c r="E53" s="296" t="n"/>
+      <c r="E53" s="296" t="inlineStr">
+        <is>
+          <t>Partial: the 'no custom properties present' precondition is an HQ inspection step out of scope here (per coverage_matrix.csv); the actual capture-and-select-and-submit steps are automated (flows/multimedia/media_02_capture_and_select.yaml).</t>
+        </is>
+      </c>
       <c r="F53" s="296" t="n"/>
       <c r="G53" s="311" t="n"/>
       <c r="H53" s="311" t="inlineStr">
@@ -10863,7 +11015,11 @@
         </is>
       </c>
       <c r="D55" s="386" t="n"/>
-      <c r="E55" s="311" t="n"/>
+      <c r="E55" s="311" t="inlineStr">
+        <is>
+          <t>Not automatable (not yet wired up): downloading and verifying Submit-History attachments aren't corrupted is technically approachable via HQClient.get_form_attachments() - already proven for this tab's own Photo Verification/Image Resize 27-28 checks - but this specific row hasn't been wired into a dedicated check yet.</t>
+        </is>
+      </c>
       <c r="F55" s="311" t="n"/>
       <c r="G55" s="311" t="n"/>
       <c r="H55" s="311" t="inlineStr">
@@ -10942,7 +11098,11 @@
         </is>
       </c>
       <c r="D57" s="387" t="n"/>
-      <c r="E57" s="296" t="n"/>
+      <c r="E57" s="296" t="inlineStr">
+        <is>
+          <t>Partial: automated (flows/multimedia/filesize_01_trigger_warning.yaml) once a &gt;15MB test file is pushed via addMedia; the 'install Disabled Filesize Warning app' HQ-side step is separate provisioning.</t>
+        </is>
+      </c>
       <c r="F57" s="296" t="n"/>
       <c r="G57" s="311" t="n"/>
       <c r="H57" s="311" t="inlineStr">
@@ -11000,7 +11160,11 @@
         </is>
       </c>
       <c r="D58" s="387" t="n"/>
-      <c r="E58" s="296" t="n"/>
+      <c r="E58" s="296" t="inlineStr">
+        <is>
+          <t>Partial: automated (flows/multimedia/filesize_02_no_warning.yaml); hq_setup/multimedia/filesize_no_warning_update.json marks the 'No Warning' release-noted build Released so Update App pulls it.</t>
+        </is>
+      </c>
       <c r="F58" s="296" t="n"/>
       <c r="G58" s="311" t="n"/>
       <c r="H58" s="311" t="inlineStr">
@@ -11058,7 +11222,11 @@
         </is>
       </c>
       <c r="D59" s="387" t="n"/>
-      <c r="E59" s="296" t="n"/>
+      <c r="E59" s="296" t="inlineStr">
+        <is>
+          <t>Not automatable: requires recording a real ~1-minute video via the device's actual camera hardware - real camera capture is confirmed flaky/unsupported on most BrowserStack device images (same limitation as Photo 1/Image Resize 25), compounded here by the real-time recording length.</t>
+        </is>
+      </c>
       <c r="F59" s="296" t="n"/>
       <c r="G59" s="311" t="n"/>
       <c r="H59" s="311" t="inlineStr">
@@ -11111,7 +11279,11 @@
         </is>
       </c>
       <c r="D60" s="387" t="n"/>
-      <c r="E60" s="296" t="n"/>
+      <c r="E60" s="296" t="inlineStr">
+        <is>
+          <t>Partial: automated (flows/multimedia/filesize_warning_02_select_large_video.yaml), assuming the oversized video can be pushed via addMedia to the Multimedia QA test app's video-capture question.</t>
+        </is>
+      </c>
       <c r="F60" s="296" t="n"/>
       <c r="G60" s="311" t="n"/>
       <c r="H60" s="311" t="inlineStr">
@@ -11318,7 +11490,11 @@
         </is>
       </c>
       <c r="D65" s="387" t="n"/>
-      <c r="E65" s="387" t="n"/>
+      <c r="E65" s="387" t="inlineStr">
+        <is>
+          <t>Partial: hq_setup/multimedia/lazy_video_release.json automates the two sequential mark_build_status calls (release low-media build, then the lazy-video build) so the device's own on-device sync/update puts it into the lazy-loading state Lazy Video 2-5 expect.</t>
+        </is>
+      </c>
       <c r="F65" s="521" t="n"/>
       <c r="G65" s="60" t="n"/>
       <c r="H65" s="60" t="inlineStr">
@@ -11435,7 +11611,11 @@
         </is>
       </c>
       <c r="D67" s="387" t="n"/>
-      <c r="E67" s="349" t="n"/>
+      <c r="E67" s="349" t="inlineStr">
+        <is>
+          <t>Partial: automated (flows/multimedia/lazy_video_03_download_and_play.yaml); a real network-download timing risk - the flow's extendedWaitUntil uses a generous 60s timeout, but a genuinely slow/stalled background download could still exceed it.</t>
+        </is>
+      </c>
       <c r="F67" s="521" t="n"/>
       <c r="G67" s="60" t="n"/>
       <c r="H67" s="60" t="inlineStr">
@@ -11739,7 +11919,11 @@
         </is>
       </c>
       <c r="D73" s="387" t="n"/>
-      <c r="E73" s="387" t="n"/>
+      <c r="E73" s="387" t="inlineStr">
+        <is>
+          <t>Partial: real camera capture confirmed flaky/unsupported on most BrowserStack device images - same caveat as Photo 1/Image Resize 25 (flows/multimedia/capture_03_04_take_and_remove_photo.yaml).</t>
+        </is>
+      </c>
       <c r="F73" s="521" t="n"/>
       <c r="G73" s="60" t="n"/>
       <c r="H73" s="60" t="inlineStr">
@@ -11795,7 +11979,11 @@
         </is>
       </c>
       <c r="D74" s="387" t="n"/>
-      <c r="E74" s="387" t="n"/>
+      <c r="E74" s="387" t="inlineStr">
+        <is>
+          <t>Partial: same real-camera-capture caveat as Capture 3 (flows/multimedia/capture_03_04_take_and_remove_photo.yaml).</t>
+        </is>
+      </c>
       <c r="F74" s="521" t="n"/>
       <c r="G74" s="60" t="n"/>
       <c r="H74" s="60" t="inlineStr">
@@ -11852,7 +12040,11 @@
         </is>
       </c>
       <c r="D75" s="387" t="n"/>
-      <c r="E75" s="387" t="n"/>
+      <c r="E75" s="387" t="inlineStr">
+        <is>
+          <t>Not automatable: requires real camera-hardware video recording - confirmed flaky/unsupported on most BrowserStack device images, same limitation as Photo 1/Image Resize 25.</t>
+        </is>
+      </c>
       <c r="F75" s="521" t="n"/>
       <c r="G75" s="60" t="n"/>
       <c r="H75" s="60" t="inlineStr">
@@ -11905,7 +12097,11 @@
         </is>
       </c>
       <c r="D76" s="387" t="n"/>
-      <c r="E76" s="387" t="n"/>
+      <c r="E76" s="387" t="inlineStr">
+        <is>
+          <t>Not automatable: requires real microphone-hardware audio recording and verifying playback fidelity - same class of real-capture-hardware limitation as video recording (Capture 5/Photo 1).</t>
+        </is>
+      </c>
       <c r="F76" s="521" t="n"/>
       <c r="G76" s="60" t="n"/>
       <c r="H76" s="60" t="inlineStr">
@@ -11957,7 +12153,11 @@
         </is>
       </c>
       <c r="D77" s="387" t="n"/>
-      <c r="E77" s="387" t="n"/>
+      <c r="E77" s="387" t="inlineStr">
+        <is>
+          <t>Not automatable: requires real microphone-hardware audio recording with a pause/resume mid-capture - same real-capture-hardware limitation as Capture 6.</t>
+        </is>
+      </c>
       <c r="F77" s="521" t="n"/>
       <c r="G77" s="60" t="n"/>
       <c r="H77" s="60" t="inlineStr">
@@ -12008,7 +12208,11 @@
         </is>
       </c>
       <c r="D78" s="387" t="n"/>
-      <c r="E78" s="387" t="n"/>
+      <c r="E78" s="387" t="inlineStr">
+        <is>
+          <t>Not automatable (not yet wired up): downloading and verifying Submit-History multimedia isn't corrupted is technically approachable via HQClient.get_form_attachments() (already proven for this tab's own Photo Verification/Image Resize 27-28 checks) but depends on Capture 5-7's own camera/mic captures having succeeded first, which they can't reliably on this device pool.</t>
+        </is>
+      </c>
       <c r="F78" s="521" t="n"/>
       <c r="G78" s="60" t="n"/>
       <c r="H78" s="60" t="inlineStr">
@@ -15704,7 +15908,11 @@
         </is>
       </c>
       <c r="D8" s="564" t="n"/>
-      <c r="E8" s="387" t="n"/>
+      <c r="E8" s="387" t="inlineStr">
+        <is>
+          <t>Not automatable: a one-time HQ environment precondition (confirm the app's own Build Settings &gt; CommCare Version is set correctly for the release under test), not a repeatable per-run test assertion - a human/QA-cycle-setup check, not wired into automation since it never needs to run per-dispatch.</t>
+        </is>
+      </c>
       <c r="F8" s="387" t="n"/>
       <c r="G8" s="382" t="n"/>
       <c r="H8" s="0" t="inlineStr">
@@ -15739,7 +15947,11 @@
         </is>
       </c>
       <c r="D9" s="564" t="n"/>
-      <c r="E9" s="387" t="n"/>
+      <c r="E9" s="387" t="inlineStr">
+        <is>
+          <t>Partial: hq_setup/prompted_updates/setup_02_mark_in_test.json automates un-releasing the newest build (mark_build_status), keeping the prior build Released; the on-device login half is flows/common/login.yaml, reused at the top of scenario_01/02/03. 'Install prior released build' itself is CCZ provisioning done before BrowserStack invokes any flow, per docs/FRAMEWORK.md's architecture.</t>
+        </is>
+      </c>
       <c r="F9" s="387" t="n"/>
       <c r="G9" s="382" t="n"/>
       <c r="H9" s="0" t="inlineStr">
@@ -15775,7 +15987,11 @@
         </is>
       </c>
       <c r="D10" s="564" t="n"/>
-      <c r="E10" s="387" t="n"/>
+      <c r="E10" s="387" t="inlineStr">
+        <is>
+          <t>Partial: hq_setup/prompted_updates/setup_03_prompts_on.json automates toggling Prompt Updates to CommCare/App to On via HQ's set_prompt_update_settings; no on-device step needed for this row.</t>
+        </is>
+      </c>
       <c r="F10" s="387" t="n"/>
       <c r="G10" s="382" t="n"/>
       <c r="H10" s="0" t="inlineStr">
@@ -15911,7 +16127,11 @@
         </is>
       </c>
       <c r="D13" s="564" t="n"/>
-      <c r="E13" s="387" t="n"/>
+      <c r="E13" s="387" t="inlineStr">
+        <is>
+          <t>Partial: the on-device navigation/assertion is fully automated (flows/prompted_updates/scenario_03_unstarred_build_no_prompt.yaml), but it needs an HQ pre-step (hq_setup/prompted_updates/scenario_03_unreleased_build.json creates a new build WITHOUT releasing it) run between this flow's own logout and relogin steps - not a single self-contained flow.</t>
+        </is>
+      </c>
       <c r="F13" s="387" t="n"/>
       <c r="G13" s="382" t="n"/>
       <c r="H13" s="0" t="inlineStr">
@@ -15963,7 +16183,11 @@
         </is>
       </c>
       <c r="D14" s="564" t="n"/>
-      <c r="E14" s="387" t="n"/>
+      <c r="E14" s="387" t="inlineStr">
+        <is>
+          <t>Not automatable: requires manually downloading an old CommCare APK from GitHub releases, then completing a real Google Play Store update flow on-device ('brought to the PlayStore page for CommCare', tap Update, wait for Play to install it) - this program has no real Play Store access, the same confirmed hard limit as the Updates tab's In-App Update rows.</t>
+        </is>
+      </c>
       <c r="F14" s="387" t="n"/>
       <c r="G14" s="382" t="n"/>
       <c r="H14" s="0" t="inlineStr">
@@ -17916,7 +18140,11 @@
         </is>
       </c>
       <c r="D7" s="399" t="n"/>
-      <c r="E7" s="399" t="n"/>
+      <c r="E7" s="399" t="inlineStr">
+        <is>
+          <t>Partial: out-of-band provisioning (download a build artifact from an internal Jenkins job, transfer it to a device) - not something Maestro can express. The resulting APK is now committed directly (resources/Mobile API Testing App-release.apk) and consumed via run_suite.py --other-app, so the automation works around this Setup step rather than performing it. See flows/externalapp_tests/README.md.</t>
+        </is>
+      </c>
       <c r="F7" s="410" t="n"/>
       <c r="H7" s="0" t="inlineStr">
         <is>
@@ -18034,7 +18262,11 @@
         </is>
       </c>
       <c r="D10" s="399" t="n"/>
-      <c r="E10" s="399" t="n"/>
+      <c r="E10" s="399" t="inlineStr">
+        <is>
+          <t>Partial: automated (flows/externalapp_tests/external_app_01_launch_and_verify_buttons.yaml), but the companion app's on-screen button text is UNVERIFIED - static APK analysis (aapt dump + dex string scan) found no literal matches for the sheet's documented button labels, so these flows match by the sheet's own wording without confirmation against a live render. See flows/externalapp_tests/README.md.</t>
+        </is>
+      </c>
       <c r="F10" s="410" t="n"/>
       <c r="H10" s="0" t="inlineStr">
         <is>
@@ -18072,7 +18304,11 @@
         </is>
       </c>
       <c r="D11" s="399" t="n"/>
-      <c r="E11" s="399" t="n"/>
+      <c r="E11" s="399" t="inlineStr">
+        <is>
+          <t>Partial: automated (flows/externalapp_tests/external_app_02_start_commcare_submit_form.yaml); same companion-app button-text caveat as External App 1 - see flows/externalapp_tests/README.md.</t>
+        </is>
+      </c>
       <c r="F11" s="410" t="n"/>
       <c r="H11" s="0" t="inlineStr">
         <is>
@@ -18110,7 +18346,11 @@
         </is>
       </c>
       <c r="D12" s="399" t="n"/>
-      <c r="E12" s="399" t="n"/>
+      <c r="E12" s="399" t="inlineStr">
+        <is>
+          <t>Partial: automated (flows/externalapp_tests/external_app_03_view_case_data.yaml); same companion-app button-text caveat as External App 1.</t>
+        </is>
+      </c>
       <c r="F12" s="410" t="n"/>
       <c r="H12" s="0" t="inlineStr">
         <is>
@@ -18149,7 +18389,11 @@
         </is>
       </c>
       <c r="D13" s="399" t="n"/>
-      <c r="E13" s="399" t="n"/>
+      <c r="E13" s="399" t="inlineStr">
+        <is>
+          <t>Partial: automated (flows/externalapp_tests/external_app_04_launch_update_form.yaml); same companion-app button-text caveat as External App 1.</t>
+        </is>
+      </c>
       <c r="F13" s="410" t="n"/>
       <c r="H13" s="0" t="inlineStr">
         <is>
@@ -18187,7 +18431,11 @@
         </is>
       </c>
       <c r="D14" s="399" t="n"/>
-      <c r="E14" s="399" t="n"/>
+      <c r="E14" s="399" t="inlineStr">
+        <is>
+          <t>Partial: automated (flows/externalapp_tests/external_app_05_view_fixture_data.yaml); same companion-app button-text caveat as External App 1.</t>
+        </is>
+      </c>
       <c r="F14" s="410" t="n"/>
       <c r="H14" s="0" t="inlineStr">
         <is>
@@ -18227,7 +18475,11 @@
         </is>
       </c>
       <c r="D15" s="399" t="n"/>
-      <c r="E15" s="399" t="n"/>
+      <c r="E15" s="399" t="inlineStr">
+        <is>
+          <t>Not automatable: combines the cross-app CommCare-key handshake with a real Android OS permission-grant dialog, confirmed to behave inconsistently across BrowserStack's device-farm Android versions - see flows/externalapp_tests/README.md.</t>
+        </is>
+      </c>
       <c r="F15" s="410" t="n"/>
       <c r="H15" s="0" t="inlineStr">
         <is>
@@ -18504,7 +18756,11 @@
         <v/>
       </c>
       <c r="D8" s="399" t="n"/>
-      <c r="E8" s="399" t="n"/>
+      <c r="E8" s="399" t="inlineStr">
+        <is>
+          <t>Partial: hq_setup/right_to_left_text/setup_01_publish_rtl_app.json automates marking the RTL-test app's latest build Released via HQ; the on-device install itself uses the same barcode-claim mechanism as Mobile Pins' own Setup 4, which stays a manual/Not-automatable step there too.</t>
+        </is>
+      </c>
       <c r="F8" s="399" t="n"/>
       <c r="G8" s="410" t="n"/>
       <c r="H8" s="410" t="inlineStr">
@@ -18546,7 +18802,11 @@
         </is>
       </c>
       <c r="D9" s="399" t="n"/>
-      <c r="E9" s="410" t="n"/>
+      <c r="E9" s="410" t="inlineStr">
+        <is>
+          <t>Partial: automates changing the device's SYSTEM language to Arabic via the real Android Settings app (flows/right_to_left_text/setup_02_change_device_language_to_arabic.yaml) - distinct from Setup 3's pure in-app language switch, which is separately automated.</t>
+        </is>
+      </c>
       <c r="F9" s="410" t="n"/>
       <c r="G9" s="410" t="n"/>
       <c r="H9" s="410" t="inlineStr">
@@ -20952,7 +21212,11 @@
       <c r="D25" s="428" t="n"/>
       <c r="E25" s="428" t="n"/>
       <c r="F25" s="428" t="n"/>
-      <c r="G25" s="428" t="n"/>
+      <c r="G25" s="428" t="inlineStr">
+        <is>
+          <t>Not automatable: a section-title/label row only (no Steps or Expected Result of its own) grouping the 'Master App' sub-scenario that follows - nothing to automate here beyond Installation 1/2 below.</t>
+        </is>
+      </c>
       <c r="I25" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
@@ -20982,7 +21246,11 @@
       <c r="D26" s="428" t="n"/>
       <c r="E26" s="428" t="n"/>
       <c r="F26" s="428" t="n"/>
-      <c r="G26" s="428" t="n"/>
+      <c r="G26" s="428" t="inlineStr">
+        <is>
+          <t>Not automatable: a section-title/label row only (no Steps or Expected Result of its own) grouping the 'Linked App' sub-scenario that follows - nothing to automate here beyond Installation 1/2 below.</t>
+        </is>
+      </c>
       <c r="I26" s="0" t="inlineStr">
         <is>
           <t>Not automatable</t>
@@ -21274,7 +21542,11 @@
       </c>
       <c r="E33" s="428" t="n"/>
       <c r="F33" s="428" t="n"/>
-      <c r="G33" s="428" t="n"/>
+      <c r="G33" s="428" t="inlineStr">
+        <is>
+          <t>Partial: installing the specific old CommCare 2.45 binary is a harness-level concern (run_suite.py's --release-tag/--apk resolves which APK to install for the whole dispatch), not something a Maestro flow file itself can express - resources/commcare_2.45_release.apk is the pinned old binary used for this scenario.</t>
+        </is>
+      </c>
       <c r="I33" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -23195,8 +23467,13 @@
         <v/>
       </c>
       <c r="D46" s="487" t="n"/>
-      <c r="E46" s="445" t="n"/>
+      <c r="E46" s="445" t="inlineStr">
+        <is>
+          <t>Partial: the old-CommCare-binary precondition (needs a real 2.45 APK on-device, which no HQ action or Maestro flow can produce by itself) is now resolved - resources/commcare_2.45_release.apk is committed and flows/recovery_measures/cc_reinstall_needed_01_trigger_on_old_client.yaml dispatches against it directly via --apk (requires_old_client_apk tag). See hq_setup/recovery_measures/cc_reinstall_needed_provisioning.json's own citation.</t>
+        </is>
+      </c>
       <c r="F46" s="445" t="n"/>
+      <c r="G46" s="0" t="n"/>
       <c r="H46" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -23232,8 +23509,13 @@
         </is>
       </c>
       <c r="D47" s="487" t="n"/>
-      <c r="E47" s="445" t="n"/>
+      <c r="E47" s="445" t="inlineStr">
+        <is>
+          <t>Partial: hq_setup/recovery_measures/cc_reinstall_needed_2_mark_released.json's mark_build_status covers the 'mark released' half only - getting the device into a genuine CC-Reinstall-pending state is actually gated on ccVersionMin/ccVersionMax served by a separate HQ 'recovery_measures' endpoint that hq_client.py has no wrapped action for (its own provenance research only covers releases.py/settings.py). Flagged as an open gap, not faked.</t>
+        </is>
+      </c>
       <c r="F47" s="445" t="n"/>
+      <c r="G47" s="0" t="n"/>
       <c r="H47" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -23447,8 +23729,13 @@
         <v/>
       </c>
       <c r="D53" s="487" t="n"/>
-      <c r="E53" s="445" t="n"/>
+      <c r="E53" s="445" t="inlineStr">
+        <is>
+          <t>Partial: same old-binary provisioning gap as row 46, now resolved via cc_update_needed_01_trigger_on_old_client.yaml + resources/commcare_2.45_release.apk. Note: this row's ID text ('CC Reinstall Needed 1') is reused from the earlier CC Reinstall Needed section above - it actually belongs to a separate CC Update Needed section per its own hq_setup file (cc_update_needed_provisioning.json), a labeling quirk in the sheet itself, not a duplicate test.</t>
+        </is>
+      </c>
       <c r="F53" s="445" t="n"/>
+      <c r="G53" s="0" t="n"/>
       <c r="H53" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -23484,8 +23771,13 @@
         </is>
       </c>
       <c r="D54" s="487" t="n"/>
-      <c r="E54" s="445" t="n"/>
+      <c r="E54" s="445" t="inlineStr">
+        <is>
+          <t>Partial: hq_setup/recovery_measures/cc_update_needed_2_mark_released.json's mark_build_status covers the 'mark released' half only. 'increment recovery Max Version by 1' has NO corresponding hq_client.py action at all (a genuinely separate ccVersionMax field on an unmapped HQ endpoint, not the same as set_prompt_update_settings' apk_version) - left undone rather than fabricating an unverified action. Same ID-reuse quirk as row 53 (belongs to CC Update Needed, not CC Reinstall Needed).</t>
+        </is>
+      </c>
       <c r="F54" s="445" t="n"/>
+      <c r="G54" s="0" t="n"/>
       <c r="H54" s="0" t="inlineStr">
         <is>
           <t>Partial</t>
@@ -24401,7 +24693,11 @@
         </is>
       </c>
       <c r="D12" s="387" t="n"/>
-      <c r="E12" s="387" t="n"/>
+      <c r="E12" s="387" t="inlineStr">
+        <is>
+          <t>Not automatable: a real-time performance-timing measurement ('time how long it takes...') meant for a human with a stopwatch, then routed to the QA team for subjective evaluation - no defined pass/fail SLA for Maestro to assert against.</t>
+        </is>
+      </c>
       <c r="F12" s="204" t="n"/>
       <c r="I12" s="0" t="inlineStr">
         <is>
@@ -24432,7 +24728,11 @@
         </is>
       </c>
       <c r="D13" s="387" t="n"/>
-      <c r="E13" s="387" t="n"/>
+      <c r="E13" s="387" t="inlineStr">
+        <is>
+          <t>Not automatable: same real-time human-timed performance measurement as 1MB Form 1, with no defined pass/fail threshold to assert against.</t>
+        </is>
+      </c>
       <c r="F13" s="204" t="n"/>
       <c r="I13" s="0" t="inlineStr">
         <is>
@@ -24551,7 +24851,11 @@
         </is>
       </c>
       <c r="D16" s="564" t="n"/>
-      <c r="E16" s="521" t="n"/>
+      <c r="E16" s="521" t="inlineStr">
+        <is>
+          <t>Partial: the sheet's own verification here is largely a VISUAL judgment call (a progress bar visibly shortening/lengthening, turning green) - Maestro can assert specific text is visible (automated in flows/form_submissions/repeat_groups_01_05_add_and_submit.yaml) but has no API to inspect a view's rendered length or color, same documented gap as Menu Badges 3/4.</t>
+        </is>
+      </c>
       <c r="F16" s="204" t="n"/>
       <c r="I16" s="0" t="inlineStr">
         <is>
@@ -24588,7 +24892,11 @@
         </is>
       </c>
       <c r="D17" s="564" t="n"/>
-      <c r="E17" s="521" t="n"/>
+      <c r="E17" s="521" t="inlineStr">
+        <is>
+          <t>Partial: same visual-progress-bar judgment gap as Repeat Groups 1 - flows/form_submissions/repeat_groups_01_05_add_and_submit.yaml covers the text-visible assertions.</t>
+        </is>
+      </c>
       <c r="F17" s="204" t="n"/>
       <c r="I17" s="0" t="inlineStr">
         <is>
@@ -24627,7 +24935,11 @@
         </is>
       </c>
       <c r="D18" s="564" t="n"/>
-      <c r="E18" s="521" t="n"/>
+      <c r="E18" s="521" t="inlineStr">
+        <is>
+          <t>Partial: same visual-progress-bar judgment gap as Repeat Groups 1; this row's own 'swipe backwards, verify the bar shortens' step is a pure navigation round-trip with no effect on submitted data, so it's covered without needing the visual assertion.</t>
+        </is>
+      </c>
       <c r="F18" s="204" t="n"/>
       <c r="I18" s="0" t="inlineStr">
         <is>
@@ -24665,7 +24977,11 @@
         </is>
       </c>
       <c r="D19" s="564" t="n"/>
-      <c r="E19" s="521" t="n"/>
+      <c r="E19" s="521" t="inlineStr">
+        <is>
+          <t>Partial: same visual-progress-bar judgment gap as Repeat Groups 1, for the final 'FINISH' text state - flows/form_submissions/repeat_groups_01_05_add_and_submit.yaml asserts the text, not the bar's color/length.</t>
+        </is>
+      </c>
       <c r="F19" s="204" t="n"/>
       <c r="I19" s="0" t="inlineStr">
         <is>
@@ -24792,7 +25108,11 @@
         </is>
       </c>
       <c r="D22" s="564" t="n"/>
-      <c r="E22" s="452" t="n"/>
+      <c r="E22" s="452" t="inlineStr">
+        <is>
+          <t>Not automatable: entirely an HQ web-UI task (browse Submit History, open Form Metadata, screenshot it for later comparison) - not an on-device mobile action, and the comparison itself is a manual screenshot-vs-screenshot judgment.</t>
+        </is>
+      </c>
       <c r="F22" s="204" t="n"/>
       <c r="I22" s="0" t="inlineStr">
         <is>
@@ -24826,7 +25146,11 @@
         </is>
       </c>
       <c r="D23" s="564" t="n"/>
-      <c r="E23" s="452" t="n"/>
+      <c r="E23" s="452" t="inlineStr">
+        <is>
+          <t>Not automatable: entirely an HQ web-UI task - editing a question in HQ's own Form Builder (Form Properties tab), not the CommCare Android app.</t>
+        </is>
+      </c>
       <c r="F23" s="204" t="n"/>
       <c r="I23" s="0" t="inlineStr">
         <is>
@@ -24859,7 +25183,11 @@
         </is>
       </c>
       <c r="D24" s="564" t="n"/>
-      <c r="E24" s="452" t="n"/>
+      <c r="E24" s="452" t="inlineStr">
+        <is>
+          <t>Not automatable: verifying Form Metadata's last-sync-token and timeStart/timeEnd values is another HQ web-UI comparison against the Clean Form Submission 1 screenshot - not an on-device action.</t>
+        </is>
+      </c>
       <c r="F24" s="454" t="inlineStr">
         <is>
           <t>This support FF will enable user to see the last sync token.</t>
@@ -24897,7 +25225,11 @@
         </is>
       </c>
       <c r="D25" s="564" t="n"/>
-      <c r="E25" s="204" t="n"/>
+      <c r="E25" s="204" t="inlineStr">
+        <is>
+          <t>Partial: the row's real point is 'verify default location values appear per question' - Maestro can assert that some text is visible (flows/form_submissions/locations_default_values_via_question_types.yaml) but has no way to know the CORRECT expected default value for each question without that expectation being specified anywhere in this repo.</t>
+        </is>
+      </c>
       <c r="F25" s="204" t="n"/>
       <c r="I25" s="0" t="inlineStr">
         <is>
@@ -24939,7 +25271,11 @@
         </is>
       </c>
       <c r="D26" s="564" t="n"/>
-      <c r="E26" s="456" t="n"/>
+      <c r="E26" s="456" t="inlineStr">
+        <is>
+          <t>Partial: the sheet's last step ('verify parent case properties update') needs opening a case-list/case-detail report to visually confirm updated values against this app's own configured display columns, which couldn't be verified against any source in this repo (no live device access) - flows/form_submissions/minimize_duplicate_create_subcase_update_case.yaml covers the create/update mechanics.</t>
+        </is>
+      </c>
       <c r="F26" s="204" t="n"/>
       <c r="I26" s="0" t="inlineStr">
         <is>
@@ -25299,7 +25635,11 @@
         </is>
       </c>
       <c r="D35" s="459" t="n"/>
-      <c r="E35" s="457" t="n"/>
+      <c r="E35" s="457" t="inlineStr">
+        <is>
+          <t>Not automatable: requires changing the device's SYSTEM CLOCK forward by 5 days - device-clock manipulation is a confirmed dead end on BrowserStack's real-device cloud (same limitation noted across the Non-Core workflow inventory).</t>
+        </is>
+      </c>
       <c r="F35" s="462" t="n"/>
       <c r="I35" s="0" t="inlineStr">
         <is>
@@ -25337,7 +25677,11 @@
         </is>
       </c>
       <c r="D36" s="459" t="n"/>
-      <c r="E36" s="457" t="n"/>
+      <c r="E36" s="457" t="inlineStr">
+        <is>
+          <t>Not automatable: depends on Unsent Form 1's own device-clock change, the same confirmed dead end.</t>
+        </is>
+      </c>
       <c r="F36" s="462" t="n"/>
       <c r="I36" s="0" t="inlineStr">
         <is>
@@ -25548,7 +25892,11 @@
         </is>
       </c>
       <c r="D43" s="564" t="n"/>
-      <c r="E43" s="457" t="n"/>
+      <c r="E43" s="457" t="inlineStr">
+        <is>
+          <t>Partial: flows/form_submissions/upload_test_01_specific_file_extensions.yaml covers the image/* upload questions via addMedia + the shared gallery-picker subflow. AUDIO questions are not coverable (no audio fixture file exists anywhere in this repo, and AudioWidget uses a plain file-browser intent, not the Photo Picker the image/video widgets use). VIDEO questions use the same Photo-Picker intent as images but have no video fixture committed either - both are marked PARTIAL/skipped for that reason, not a tooling limitation.</t>
+        </is>
+      </c>
       <c r="F43" s="564" t="inlineStr">
         <is>
           <t>NS: Check for all diff questions types and upload image, audio, video, document and signature. 
@@ -25742,7 +26090,11 @@
         </is>
       </c>
       <c r="D48" s="564" t="n"/>
-      <c r="E48" s="94" t="n"/>
+      <c r="E48" s="94" t="inlineStr">
+        <is>
+          <t>Not automatable: verifying a FLAG_SECURE-protected window renders blank requires a screenshot of the task-switcher/recent-apps preview - but FLAG_SECURE's whole purpose is blocking screenshot capture at the OS level, so any automated screenshot tool (Maestro's included) hits the same OS-level block a real screenshot would, leaving no way to programmatically confirm 'blank' versus 'not captured at all'.</t>
+        </is>
+      </c>
       <c r="F48" s="204" t="n"/>
       <c r="I48" s="0" t="inlineStr">
         <is>
@@ -25783,7 +26135,11 @@
         </is>
       </c>
       <c r="D49" s="485" t="n"/>
-      <c r="E49" s="486" t="n"/>
+      <c r="E49" s="486" t="inlineStr">
+        <is>
+          <t>Not automatable: requires a separate laptop running a third-party HTTPS-interception tool (Http Toolkit), paired to the test device via QR code to man-in-the-middle its traffic - inherently a two-machine, external-desktop-tool setup no single BrowserStack cloud device session can provide.</t>
+        </is>
+      </c>
       <c r="F49" s="484" t="n"/>
       <c r="I49" s="0" t="inlineStr">
         <is>
@@ -25818,7 +26174,11 @@
         </is>
       </c>
       <c r="D50" s="485" t="n"/>
-      <c r="E50" s="486" t="n"/>
+      <c r="E50" s="486" t="inlineStr">
+        <is>
+          <t>Not automatable: depends on Certificate Transparency 1's own two-machine Http Toolkit interception setup.</t>
+        </is>
+      </c>
       <c r="F50" s="484" t="n"/>
       <c r="I50" s="0" t="inlineStr">
         <is>
@@ -25859,7 +26219,11 @@
         </is>
       </c>
       <c r="D51" s="485" t="n"/>
-      <c r="E51" s="486" t="n"/>
+      <c r="E51" s="486" t="inlineStr">
+        <is>
+          <t>Not automatable: requires a separate, real third-party voice-recording app (e.g. Samsung Voice Recorder) installed and run concurrently with CommCare to test real hardware audio-focus arbitration - installing an arbitrary third-party app with no internal APK source is a confirmed hard limit of this pipeline (same class of gap as Third Party Scanner), compounded by device/OS-specific audio-focus behavior that's inherently flaky to assert on.</t>
+        </is>
+      </c>
       <c r="F51" s="484" t="n"/>
       <c r="I51" s="0" t="inlineStr">
         <is>
@@ -25904,7 +26268,11 @@
         </is>
       </c>
       <c r="D52" s="485" t="n"/>
-      <c r="E52" s="486" t="n"/>
+      <c r="E52" s="486" t="inlineStr">
+        <is>
+          <t>Not automatable: same third-party-voice-recorder-app limitation as Audio Recording 1, reversed direction (other app records while CommCare is active).</t>
+        </is>
+      </c>
       <c r="F52" s="484" t="n"/>
       <c r="I52" s="0" t="inlineStr">
         <is>
@@ -25947,7 +26315,11 @@
         </is>
       </c>
       <c r="D53" s="485" t="n"/>
-      <c r="E53" s="486" t="n"/>
+      <c r="E53" s="486" t="inlineStr">
+        <is>
+          <t>Not automatable: same third-party-voice-recorder-app limitation as Audio Recording 1, for Android 6 and earlier device images.</t>
+        </is>
+      </c>
       <c r="F53" s="484" t="n"/>
       <c r="I53" s="0" t="inlineStr">
         <is>
@@ -25991,7 +26363,11 @@
         </is>
       </c>
       <c r="D54" s="485" t="n"/>
-      <c r="E54" s="486" t="n"/>
+      <c r="E54" s="486" t="inlineStr">
+        <is>
+          <t>Not automatable: same third-party-voice-recorder-app limitation as Audio Recording 1, for Android 6 and earlier device images.</t>
+        </is>
+      </c>
       <c r="F54" s="484" t="n"/>
       <c r="I54" s="0" t="inlineStr">
         <is>
@@ -26028,7 +26404,11 @@
         </is>
       </c>
       <c r="D55" s="485" t="n"/>
-      <c r="E55" s="486" t="n"/>
+      <c r="E55" s="486" t="inlineStr">
+        <is>
+          <t>Not automatable (not yet wired up): configuring a Case Search property's checkbox/multi-select format lives in HQ's App Builder Case List UI, backed by the app's module/case_details XML - a materially more complex structure than the simple custom_properties key/value toggles hq_client.py already wraps (mark_build_status/set_custom_properties/etc.), so no existing action covers it.</t>
+        </is>
+      </c>
       <c r="F55" s="484" t="n"/>
       <c r="I55" s="0" t="inlineStr">
         <is>
@@ -26063,7 +26443,11 @@
         </is>
       </c>
       <c r="D56" s="485" t="n"/>
-      <c r="E56" s="486" t="n"/>
+      <c r="E56" s="486" t="inlineStr">
+        <is>
+          <t>Not automatable: depends on Casesearch Checkbox 1's own App Builder configuration existing first.</t>
+        </is>
+      </c>
       <c r="F56" s="484" t="n"/>
       <c r="I56" s="0" t="inlineStr">
         <is>
@@ -26098,7 +26482,11 @@
         </is>
       </c>
       <c r="D57" s="485" t="n"/>
-      <c r="E57" s="493" t="n"/>
+      <c r="E57" s="493" t="inlineStr">
+        <is>
+          <t>Partial in principle, not yet reachable: the precondition (custom property cc-auto-form-save-on-pause=yes) could be verified via HQ's get_custom_properties, the same pattern already proven for Support Menus' own precondition check. Simulating an actual app crash/force-stop and verifying draft recovery afterward is blocked by this repo's own confirmed dead end on terminateApp/backgroundApp/adb_shell-style forced termination on BrowserStack - Maestro's stop/kill primitives don't reproduce a genuine crash the way this row's own steps need.</t>
+        </is>
+      </c>
       <c r="F57" s="494" t="n"/>
       <c r="I57" s="0" t="inlineStr">
         <is>
@@ -26211,7 +26599,11 @@
         </is>
       </c>
       <c r="D60" s="485" t="n"/>
-      <c r="E60" s="493" t="n"/>
+      <c r="E60" s="493" t="inlineStr">
+        <is>
+          <t>Not automatable (not yet wired up): requires a pre-provisioned ACTIVE HQ mobile-worker/web-user account distinct from this program's own fixed test credentials, and hq_client.py has no wrapped action for creating/toggling user activation state - would need new HQClient development, not a hard technical block.</t>
+        </is>
+      </c>
       <c r="F60" s="494" t="n"/>
       <c r="I60" s="0" t="inlineStr">
         <is>
@@ -26244,7 +26636,11 @@
         </is>
       </c>
       <c r="D61" s="485" t="n"/>
-      <c r="E61" s="493" t="n"/>
+      <c r="E61" s="493" t="inlineStr">
+        <is>
+          <t>Not automatable (not yet wired up): same gap as Active users login, for a pre-provisioned INACTIVE account - no existing hq_client.py action manages user activation state.</t>
+        </is>
+      </c>
       <c r="F61" s="494" t="n"/>
       <c r="I61" s="0" t="inlineStr">
         <is>
@@ -26278,7 +26674,11 @@
         </is>
       </c>
       <c r="D62" s="500" t="n"/>
-      <c r="E62" s="493" t="n"/>
+      <c r="E62" s="493" t="inlineStr">
+        <is>
+          <t>Not automatable (not yet wired up): same gap as Active users login, plus a real-time deactivate/reactivate/deactivate cycle - no existing hq_client.py action manages user activation state.</t>
+        </is>
+      </c>
       <c r="F62" s="494" t="n"/>
       <c r="I62" s="0" t="inlineStr">
         <is>
@@ -28557,7 +28957,11 @@
         </is>
       </c>
       <c r="D9" s="387" t="n"/>
-      <c r="E9" s="387" t="n"/>
+      <c r="E9" s="387" t="inlineStr">
+        <is>
+          <t>Partial: hq_setup/trigger_device_logs/device_logs_1_feature_flag.json documents the one-time manual feature-flag toggle (not a repeatable HQ API call), and flows/trigger_device_logs/device_logs_1_submit_form.yaml automates the on-device install+login+submit+logout steps.</t>
+        </is>
+      </c>
       <c r="F9" s="521" t="n"/>
       <c r="G9" s="60" t="n"/>
       <c r="H9" s="60" t="inlineStr">
@@ -28681,7 +29085,11 @@
         <v/>
       </c>
       <c r="D12" s="387" t="n"/>
-      <c r="E12" s="387" t="n"/>
+      <c r="E12" s="387" t="inlineStr">
+        <is>
+          <t>Not automatable: validation happens entirely in Sumo Logic, a real external SaaS dashboard this program has no API access to - same class of gap as every other 'verify in a third-party system' row. Device Logs 3 (the on-device trigger action) is separately automated; this row is genuinely just the external-system check.</t>
+        </is>
+      </c>
       <c r="F12" s="521" t="n"/>
       <c r="G12" s="60" t="n"/>
       <c r="H12" s="60" t="inlineStr">
@@ -29061,7 +29469,11 @@
         </is>
       </c>
       <c r="D12" s="564" t="n"/>
-      <c r="E12" s="387" t="n"/>
+      <c r="E12" s="387" t="inlineStr">
+        <is>
+          <t>Not automatable: tests HQ's own Web Apps browser interface, not the CommCare Android app - this program automates the mobile app only (Maestro/Appium), with no web-browser automation tool (e.g. Selenium/Playwright) in its stack.</t>
+        </is>
+      </c>
       <c r="F12" s="204" t="n"/>
       <c r="H12" s="0" t="inlineStr">
         <is>
@@ -29093,7 +29505,11 @@
         </is>
       </c>
       <c r="D13" s="564" t="n"/>
-      <c r="E13" s="387" t="n"/>
+      <c r="E13" s="387" t="inlineStr">
+        <is>
+          <t>Not automatable: tests HQ's own App Preview browser interface, not the CommCare Android app - same reason as Rate limit 5, no web-browser automation in this program's stack.</t>
+        </is>
+      </c>
       <c r="F13" s="204" t="n"/>
       <c r="H13" s="0" t="inlineStr">
         <is>
@@ -29366,7 +29782,11 @@
         </is>
       </c>
       <c r="D20" s="564" t="n"/>
-      <c r="E20" s="539" t="n"/>
+      <c r="E20" s="539" t="inlineStr">
+        <is>
+          <t>Partial: hq_setup/updates_2_49/setup_02_commcare_version_plus_one.json automates setting Prompt Updates to CommCare/App On and CommCare Version one above the version under test, via HQ's set_prompt_update_settings.</t>
+        </is>
+      </c>
       <c r="F20" s="541" t="inlineStr">
         <is>
           <t>Only superusers are expected to see the non-released versions.</t>
@@ -29496,7 +29916,11 @@
         </is>
       </c>
       <c r="D23" s="564" t="n"/>
-      <c r="E23" s="539" t="n"/>
+      <c r="E23" s="539" t="inlineStr">
+        <is>
+          <t>Not automatable: requires a genuine 5-10 minute real-time wait between disabling the CommCare-version prompt and re-checking - impractical within CI's own build timeouts, same class of limitation as the Update tab's 'Reestablish connection' row.</t>
+        </is>
+      </c>
       <c r="F23" s="204" t="n"/>
       <c r="H23" s="0" t="inlineStr">
         <is>
@@ -29652,7 +30076,11 @@
         </is>
       </c>
       <c r="D27" s="564" t="n"/>
-      <c r="E27" s="539" t="n"/>
+      <c r="E27" s="539" t="inlineStr">
+        <is>
+          <t>Not automatable: requires following a real Google Play Store RC2 test-track link and interacting with the Play Store's own update button - no real Play Store access in this program, same confirmed hard limit as Prompted Update Scenario 4.</t>
+        </is>
+      </c>
       <c r="F27" s="204" t="n"/>
       <c r="H27" s="0" t="inlineStr">
         <is>
@@ -29686,7 +30114,11 @@
         </is>
       </c>
       <c r="D28" s="564" t="n"/>
-      <c r="E28" s="539" t="n"/>
+      <c r="E28" s="539" t="inlineStr">
+        <is>
+          <t>Not automatable: requires completing an in-app update via the real Play Store popup flow - same Play Store access limitation as In-App Update 3.</t>
+        </is>
+      </c>
       <c r="F28" s="204" t="n"/>
       <c r="H28" s="0" t="inlineStr">
         <is>
@@ -29753,7 +30185,11 @@
         </is>
       </c>
       <c r="D30" s="564" t="n"/>
-      <c r="E30" s="539" t="n"/>
+      <c r="E30" s="539" t="inlineStr">
+        <is>
+          <t>Not automatable: depends on In-App Update 3/4's real Play Store update having actually completed first - not reachable without that.</t>
+        </is>
+      </c>
       <c r="F30" s="204" t="n"/>
       <c r="H30" s="0" t="inlineStr">
         <is>
@@ -29790,7 +30226,11 @@
         </is>
       </c>
       <c r="D31" s="564" t="n"/>
-      <c r="E31" s="539" t="n"/>
+      <c r="E31" s="539" t="inlineStr">
+        <is>
+          <t>Not automatable: requires the real Play Store in-app-update popup across 5 repeated login cycles - same Play Store access limitation as In-App Update 3.</t>
+        </is>
+      </c>
       <c r="F31" s="204" t="n"/>
       <c r="H31" s="0" t="inlineStr">
         <is>
@@ -29822,7 +30262,11 @@
         </is>
       </c>
       <c r="D32" s="564" t="n"/>
-      <c r="E32" s="539" t="n"/>
+      <c r="E32" s="539" t="inlineStr">
+        <is>
+          <t>Not automatable: requires completing a real Play Store update via the options-menu path - same Play Store access limitation as In-App Update 3.</t>
+        </is>
+      </c>
       <c r="F32" s="204" t="n"/>
       <c r="H32" s="0" t="inlineStr">
         <is>
@@ -29853,7 +30297,11 @@
         </is>
       </c>
       <c r="D33" s="564" t="n"/>
-      <c r="E33" s="539" t="n"/>
+      <c r="E33" s="539" t="inlineStr">
+        <is>
+          <t>Not automatable: explicitly exploratory/unscripted per its own steps ('You can play with this here...') - not a fixed, repeatable assertion, and depends on the same real Play Store access as In-App Update 3.</t>
+        </is>
+      </c>
       <c r="F33" s="204" t="n"/>
       <c r="H33" s="0" t="inlineStr">
         <is>
@@ -29886,7 +30334,11 @@
         </is>
       </c>
       <c r="D34" s="564" t="n"/>
-      <c r="E34" s="539" t="n"/>
+      <c r="E34" s="539" t="inlineStr">
+        <is>
+          <t>Not automatable: explicitly exploratory (performance/lag observation over multiple sessions) and depends on the same real Play Store update flow as In-App Update 3 - neither a repeatable functional assertion nor something this stack can drive.</t>
+        </is>
+      </c>
       <c r="F34" s="204" t="n"/>
       <c r="H34" s="0" t="inlineStr">
         <is>
@@ -35163,7 +35615,11 @@
         </is>
       </c>
       <c r="F13" s="94" t="n"/>
-      <c r="G13" s="94" t="n"/>
+      <c r="G13" s="94" t="inlineStr">
+        <is>
+          <t>Partial: automated end-to-end using this program's own fixed HQ mobile-worker test credential (flows/install/install_07_install_as_mobile_user.yaml drives edit_username/edit_domain/edit_password, same as InstallFromListTest.kt) - covers the real install mechanics, not arbitrary/invalid-credential handling.</t>
+        </is>
+      </c>
       <c r="H13" s="106" t="n"/>
       <c r="I13" s="45" t="inlineStr">
         <is>
@@ -35220,7 +35676,11 @@
         </is>
       </c>
       <c r="F14" s="155" t="n"/>
-      <c r="G14" s="155" t="n"/>
+      <c r="G14" s="155" t="inlineStr">
+        <is>
+          <t>Partial: automated end-to-end using this program's own fixed HQ web-user test credential (flows/install/install_08_install_as_web_user.yaml) - covers the real install mechanics, not arbitrary/invalid-credential handling.</t>
+        </is>
+      </c>
       <c r="H14" s="106" t="n"/>
       <c r="I14" s="45" t="inlineStr">
         <is>
@@ -35798,7 +36258,11 @@
         </is>
       </c>
       <c r="D8" s="137" t="n"/>
-      <c r="E8" s="522" t="n"/>
+      <c r="E8" s="522" t="inlineStr">
+        <is>
+          <t>Partial: hq_setup/update/setup_make_new_version.json automates the unconditional 'create new version' HQ call, but the sheet's own logic is conditional (no-op if workspace was already clean vs. a real new build needing Release afterward) - today's hq_client.py has no if/then branching to detect which case happened and conditionally chain the Release step, so a human still confirms which branch applied. See that file's own _comment for the full citation.</t>
+        </is>
+      </c>
       <c r="F8" s="522" t="n"/>
       <c r="G8" s="150" t="n"/>
       <c r="H8" s="124" t="inlineStr">
@@ -35830,7 +36294,11 @@
         </is>
       </c>
       <c r="D9" s="137" t="n"/>
-      <c r="E9" s="522" t="n"/>
+      <c r="E9" s="522" t="inlineStr">
+        <is>
+          <t>Partial: hq_setup/update/install_mark_released.json automates marking the latest build Released (the 'star' action) via HQ; the on-device 'install latest build' half needs no new flow since it's already exercised by flows/install/install_07/08 and flows/update/update_target_developer_options_flow.yaml's own Update App step.</t>
+        </is>
+      </c>
       <c r="F9" s="522" t="n"/>
       <c r="G9" s="150" t="n"/>
       <c r="H9" s="124" t="inlineStr">
@@ -36155,7 +36623,11 @@
         </is>
       </c>
       <c r="D18" s="596" t="n"/>
-      <c r="E18" s="160" t="n"/>
+      <c r="E18" s="160" t="inlineStr">
+        <is>
+          <t>Not automatable: requires disabling airplane mode then waiting a real 10 minutes for a background update to resume - airplane-mode/network toggling was confirmed unreliable on BrowserStack's real-device cloud this session (same limitation documented on the Auto Form Submission tab), and a genuine 10-minute real-time wait is impractical within CI's own build timeouts regardless.</t>
+        </is>
+      </c>
       <c r="F18" s="160" t="n"/>
       <c r="G18" s="139" t="n"/>
       <c r="H18" s="124" t="inlineStr">
@@ -36229,7 +36701,11 @@
         </is>
       </c>
       <c r="D20" s="596" t="n"/>
-      <c r="E20" s="163" t="n"/>
+      <c r="E20" s="163" t="inlineStr">
+        <is>
+          <t>Not automatable: requires putting the device in airplane mode mid-update and verifying a specific Recheck button's enabled state while offline - same airplane-mode/network-toggle reliability limitation confirmed elsewhere this session on BrowserStack's real-device cloud (see Auto Form Submission tab).</t>
+        </is>
+      </c>
       <c r="F20" s="163" t="n"/>
       <c r="G20" s="139" t="n"/>
       <c r="H20" s="124" t="inlineStr">

--- a/docs/[Master] Mobile Plan (2026).xlsx
+++ b/docs/[Master] Mobile Plan (2026).xlsx
@@ -26046,18 +26046,18 @@
       <c r="D47" s="564" t="n"/>
       <c r="E47" s="94" t="inlineStr">
         <is>
-          <t>Steps 1-4 (submit a form, confirm a location value was captured) automated via scripts/verify_submission.py's new --require-location flag - checks the Submit History metadata tab's own 'location' field (which get_form_metadata() already surfaces) isn't the empty '---' placeholder. This flow reuses the shared 'Basic Form Tests &gt; Basic Form' form (same one device_logs_1_submit_form.yaml uses), so the breadcrumb alone can't disambiguate - pass --after &lt;a timestamp just before this flow runs&gt; alongside --form-path 'Basic Form' to target the right submission, not a bare form-path filter. Verified live 2026-08-27: correctly FAILED against a real submission with no captured location, confirming the check works (a submission with Auto Capture Location genuinely enabled wasn't available to confirm the positive case, same field-presence logic as the already-proven has_multimedia check). Steps 5-6 (cross-check the lat/long against a GPS converter site to confirm it matches the device's actual real-world location) remain a manual spot-check - out of scope for an automated assertion.</t>
+          <t>Partial, not currently wired into CI: scripts/verify_submission.py --require-location automates the check mechanism (confirmed working - it correctly detects the negative case), but a real check run on 2026-09-11 found this app build genuinely does not capture a location into the submission (metadata.location == "---"), same result as 2026-08-27. Held back from CI per direct user instruction until the underlying Auto Capture Location app/config gap is investigated, rather than wiring in a check that would always fail. Steps 5-6 (cross-check lat/long against a GPS converter site) remain a manual spot-check regardless.</t>
         </is>
       </c>
       <c r="F47" s="204" t="n"/>
       <c r="I47" s="0" t="inlineStr">
         <is>
-          <t>Automatable</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="J47" s="0" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K47" s="0" t="inlineStr">
